--- a/views/hakedisler/Hakedis.xlsx
+++ b/views/hakedisler/Hakedis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ersan_elk\views\hakedisler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F843B1-D99C-47B2-B1FE-BDAA284BA3B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A43A47-0F7D-4700-B27B-2D81558FBE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="918" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="918" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bilgiler" sheetId="1" r:id="rId1"/>
@@ -19063,15 +19063,11 @@
       <c r="E10" s="502"/>
       <c r="F10" s="502"/>
       <c r="G10" s="502"/>
-      <c r="H10" s="608">
-        <v>2025</v>
-      </c>
+      <c r="H10" s="608"/>
       <c r="I10" s="608"/>
       <c r="J10" s="608"/>
       <c r="K10" s="608"/>
-      <c r="L10" s="502">
-        <v>2026</v>
-      </c>
+      <c r="L10" s="502"/>
       <c r="M10" s="502"/>
       <c r="N10" s="502"/>
       <c r="O10" s="502"/>
@@ -19098,10 +19094,7 @@
       <c r="E11" s="602"/>
       <c r="F11" s="602"/>
       <c r="G11" s="602"/>
-      <c r="H11" s="531">
-        <f>'İş Takip-Ön Yüz'!G14</f>
-        <v>0</v>
-      </c>
+      <c r="H11" s="531"/>
       <c r="I11" s="498"/>
       <c r="J11" s="498"/>
       <c r="K11" s="498"/>
@@ -19132,10 +19125,7 @@
       <c r="E12" s="602"/>
       <c r="F12" s="602"/>
       <c r="G12" s="602"/>
-      <c r="H12" s="531">
-        <f>'Arka Kapak'!D4</f>
-        <v>0</v>
-      </c>
+      <c r="H12" s="531"/>
       <c r="I12" s="531"/>
       <c r="J12" s="531"/>
       <c r="K12" s="531"/>

--- a/views/hakedisler/Hakedis.xlsx
+++ b/views/hakedisler/Hakedis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ersan_elk\views\hakedisler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A43A47-0F7D-4700-B27B-2D81558FBE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6774FE25-0157-4B08-9FAF-99684B5F53AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="918" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="918" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bilgiler" sheetId="1" r:id="rId1"/>

--- a/views/hakedisler/Hakedis.xlsx
+++ b/views/hakedisler/Hakedis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ersan_elk\views\hakedisler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286C6B40-EE66-4E72-BF53-C8251A900AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CA1BA2B-DB3C-4642-853B-6CB22A50B3F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="918" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -119,7 +119,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="7">Çarşaf!$A$1:$BL$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Fiyat Farkı Tutanağı'!$A$1:$I$41</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">İcmal!$A$1:$BH$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'İş Takip Arka Yüz'!$A$1:$AA$86</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'İş Takip Arka Yüz'!$A:$AA</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'İş Takip-Ön Yüz'!$A$1:$AA$105</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Ön Kapak'!$A$1:$J$48</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">BFTC!$1:$4</definedName>
@@ -131,13 +131,13 @@
     <definedName name="Z_99F77AB9_FA43_4D4B_9896_F712C1493A3C_.wvu.PrintArea" localSheetId="2" hidden="1">BFTC!$A$1:$E$33</definedName>
     <definedName name="Z_99F77AB9_FA43_4D4B_9896_F712C1493A3C_.wvu.PrintArea" localSheetId="7" hidden="1">Çarşaf!$A$1:$BL$29</definedName>
     <definedName name="Z_99F77AB9_FA43_4D4B_9896_F712C1493A3C_.wvu.PrintArea" localSheetId="1" hidden="1">İcmal!$A$1:$BH$59</definedName>
-    <definedName name="Z_99F77AB9_FA43_4D4B_9896_F712C1493A3C_.wvu.PrintArea" localSheetId="6" hidden="1">'İş Takip Arka Yüz'!$A$1:$AA$86</definedName>
+    <definedName name="Z_99F77AB9_FA43_4D4B_9896_F712C1493A3C_.wvu.PrintArea" localSheetId="6" hidden="1">'İş Takip Arka Yüz'!$A$1:$AA$55</definedName>
     <definedName name="Z_99F77AB9_FA43_4D4B_9896_F712C1493A3C_.wvu.PrintArea" localSheetId="5" hidden="1">'İş Takip-Ön Yüz'!$A$1:$AA$105</definedName>
     <definedName name="Z_99F77AB9_FA43_4D4B_9896_F712C1493A3C_.wvu.PrintArea" localSheetId="3" hidden="1">'Ön Kapak'!$A$1:$J$48</definedName>
     <definedName name="Z_C8BAC6B5_86E1_4F54_AEAC_1412291311FD_.wvu.PrintArea" localSheetId="2" hidden="1">BFTC!$A$1:$E$33</definedName>
     <definedName name="Z_C8BAC6B5_86E1_4F54_AEAC_1412291311FD_.wvu.PrintArea" localSheetId="7" hidden="1">Çarşaf!$A$1:$BL$29</definedName>
     <definedName name="Z_C8BAC6B5_86E1_4F54_AEAC_1412291311FD_.wvu.PrintArea" localSheetId="1" hidden="1">İcmal!$A$1:$BH$59</definedName>
-    <definedName name="Z_C8BAC6B5_86E1_4F54_AEAC_1412291311FD_.wvu.PrintArea" localSheetId="6" hidden="1">'İş Takip Arka Yüz'!$A$1:$AA$86</definedName>
+    <definedName name="Z_C8BAC6B5_86E1_4F54_AEAC_1412291311FD_.wvu.PrintArea" localSheetId="6" hidden="1">'İş Takip Arka Yüz'!$A$1:$AA$55</definedName>
     <definedName name="Z_C8BAC6B5_86E1_4F54_AEAC_1412291311FD_.wvu.PrintArea" localSheetId="5" hidden="1">'İş Takip-Ön Yüz'!$A$1:$AA$105</definedName>
     <definedName name="Z_C8BAC6B5_86E1_4F54_AEAC_1412291311FD_.wvu.PrintArea" localSheetId="3" hidden="1">'Ön Kapak'!$A$1:$J$48</definedName>
   </definedNames>
@@ -3308,7 +3308,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="503">
+  <cellStyleXfs count="504">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="10" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0">
       <protection hidden="1"/>
@@ -4282,8 +4282,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="793">
+  <cellXfs count="795">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5991,6 +5992,12 @@
     <xf numFmtId="10" fontId="37" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="43" fontId="37" fillId="0" borderId="1" xfId="503" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="37" fillId="0" borderId="37" xfId="503" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6568,7 +6575,7 @@
     </xf>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="502"/>
   </cellXfs>
-  <cellStyles count="503">
+  <cellStyles count="504">
     <cellStyle name="0.000" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="1" xfId="118" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="1_6 - BİRİM FİYAT TEKLİF CETVELİ" xfId="119" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -7068,6 +7075,7 @@
     <cellStyle name="TON" xfId="287" xr:uid="{00000000-0005-0000-0000-0000F2010000}"/>
     <cellStyle name="Total" xfId="288" xr:uid="{00000000-0005-0000-0000-0000F3010000}"/>
     <cellStyle name="Undefiniert" xfId="289" xr:uid="{00000000-0005-0000-0000-0000F4010000}"/>
+    <cellStyle name="Virgül" xfId="503" builtinId="3"/>
     <cellStyle name="Virgül [0]_ Prestij HAK 5" xfId="108" xr:uid="{00000000-0005-0000-0000-0000F5010000}"/>
     <cellStyle name="Währung [0]_Software Project Status" xfId="290" xr:uid="{00000000-0005-0000-0000-0000F6010000}"/>
     <cellStyle name="Währung_Software Project Status" xfId="291" xr:uid="{00000000-0005-0000-0000-0000F7010000}"/>
@@ -9228,19 +9236,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="791" t="s">
+      <c r="A1" s="793" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="792"/>
-      <c r="C1" s="792"/>
-      <c r="D1" s="792"/>
-      <c r="E1" s="792"/>
-      <c r="F1" s="792"/>
-      <c r="G1" s="792"/>
-      <c r="H1" s="792"/>
-      <c r="I1" s="792"/>
-      <c r="J1" s="792"/>
-      <c r="K1" s="792"/>
+      <c r="B1" s="794"/>
+      <c r="C1" s="794"/>
+      <c r="D1" s="794"/>
+      <c r="E1" s="794"/>
+      <c r="F1" s="794"/>
+      <c r="G1" s="794"/>
+      <c r="H1" s="794"/>
+      <c r="I1" s="794"/>
+      <c r="J1" s="794"/>
+      <c r="K1" s="794"/>
     </row>
     <row r="3" spans="1:11" ht="61.9" customHeight="1">
       <c r="A3" s="163" t="s">
@@ -19376,26 +19384,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC87"/>
+  <dimension ref="A1:AC56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="7" width="3.85546875" customWidth="1"/>
     <col min="8" max="8" width="4.140625" customWidth="1"/>
-    <col min="9" max="10" width="2.85546875" customWidth="1"/>
-    <col min="11" max="11" width="3.5703125" customWidth="1"/>
-    <col min="12" max="19" width="3.42578125" customWidth="1"/>
-    <col min="20" max="23" width="3.140625" customWidth="1"/>
+    <col min="9" max="9" width="2.85546875" customWidth="1"/>
+    <col min="10" max="10" width="4.5703125" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" customWidth="1"/>
+    <col min="12" max="13" width="3.42578125" customWidth="1"/>
+    <col min="14" max="14" width="4.7109375" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
+    <col min="16" max="18" width="3.42578125" customWidth="1"/>
+    <col min="19" max="19" width="14.140625" customWidth="1"/>
+    <col min="20" max="22" width="3.140625" customWidth="1"/>
+    <col min="23" max="23" width="12.5703125" customWidth="1"/>
     <col min="24" max="26" width="2.85546875" customWidth="1"/>
-    <col min="27" max="27" width="6" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" customWidth="1"/>
     <col min="28" max="28" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="15" customHeight="1" thickTop="1">
-      <c r="A1" s="619"/>
-      <c r="B1" s="620"/>
-      <c r="C1" s="620"/>
-      <c r="D1" s="620"/>
+      <c r="A1" s="621"/>
+      <c r="B1" s="622"/>
+      <c r="C1" s="622"/>
+      <c r="D1" s="622"/>
       <c r="E1" s="557">
         <f>Bilgiler!D1</f>
         <v>0</v>
@@ -19418,11 +19433,11 @@
       <c r="U1" s="557"/>
       <c r="V1" s="557"/>
       <c r="W1" s="557"/>
-      <c r="X1" s="621" t="s">
+      <c r="X1" s="623" t="s">
         <v>18</v>
       </c>
-      <c r="Y1" s="621"/>
-      <c r="Z1" s="621"/>
+      <c r="Y1" s="623"/>
+      <c r="Z1" s="623"/>
       <c r="AA1" s="18">
         <v>2</v>
       </c>
@@ -19432,25 +19447,25 @@
       <c r="B2" s="435"/>
       <c r="C2" s="435"/>
       <c r="D2" s="435"/>
-      <c r="E2" s="610"/>
-      <c r="F2" s="610"/>
-      <c r="G2" s="610"/>
-      <c r="H2" s="610"/>
-      <c r="I2" s="610"/>
-      <c r="J2" s="610"/>
-      <c r="K2" s="610"/>
-      <c r="L2" s="610"/>
-      <c r="M2" s="610"/>
-      <c r="N2" s="610"/>
-      <c r="O2" s="610"/>
-      <c r="P2" s="610"/>
-      <c r="Q2" s="610"/>
-      <c r="R2" s="610"/>
-      <c r="S2" s="610"/>
-      <c r="T2" s="610"/>
-      <c r="U2" s="610"/>
-      <c r="V2" s="610"/>
-      <c r="W2" s="610"/>
+      <c r="E2" s="612"/>
+      <c r="F2" s="612"/>
+      <c r="G2" s="612"/>
+      <c r="H2" s="612"/>
+      <c r="I2" s="612"/>
+      <c r="J2" s="612"/>
+      <c r="K2" s="612"/>
+      <c r="L2" s="612"/>
+      <c r="M2" s="612"/>
+      <c r="N2" s="612"/>
+      <c r="O2" s="612"/>
+      <c r="P2" s="612"/>
+      <c r="Q2" s="612"/>
+      <c r="R2" s="612"/>
+      <c r="S2" s="612"/>
+      <c r="T2" s="612"/>
+      <c r="U2" s="612"/>
+      <c r="V2" s="612"/>
+      <c r="W2" s="612"/>
       <c r="AA2" s="19"/>
     </row>
     <row r="3" spans="1:28" ht="15" customHeight="1">
@@ -19458,188 +19473,188 @@
       <c r="B3" s="435"/>
       <c r="C3" s="435"/>
       <c r="D3" s="435"/>
-      <c r="E3" s="610"/>
-      <c r="F3" s="622"/>
-      <c r="G3" s="622"/>
-      <c r="H3" s="622"/>
-      <c r="I3" s="622"/>
-      <c r="J3" s="622"/>
-      <c r="K3" s="622"/>
-      <c r="L3" s="622"/>
-      <c r="M3" s="622"/>
-      <c r="N3" s="622"/>
-      <c r="O3" s="622"/>
-      <c r="P3" s="622"/>
-      <c r="Q3" s="622"/>
-      <c r="R3" s="622"/>
-      <c r="S3" s="622"/>
-      <c r="T3" s="622"/>
-      <c r="U3" s="622"/>
-      <c r="V3" s="622"/>
-      <c r="W3" s="622"/>
+      <c r="E3" s="612"/>
+      <c r="F3" s="624"/>
+      <c r="G3" s="624"/>
+      <c r="H3" s="624"/>
+      <c r="I3" s="624"/>
+      <c r="J3" s="624"/>
+      <c r="K3" s="624"/>
+      <c r="L3" s="624"/>
+      <c r="M3" s="624"/>
+      <c r="N3" s="624"/>
+      <c r="O3" s="624"/>
+      <c r="P3" s="624"/>
+      <c r="Q3" s="624"/>
+      <c r="R3" s="624"/>
+      <c r="S3" s="624"/>
+      <c r="T3" s="624"/>
+      <c r="U3" s="624"/>
+      <c r="V3" s="624"/>
+      <c r="W3" s="624"/>
       <c r="AA3" s="19"/>
     </row>
     <row r="4" spans="1:28" ht="23.25" customHeight="1">
-      <c r="A4" s="609" t="s">
+      <c r="A4" s="611" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="610"/>
-      <c r="C4" s="610"/>
-      <c r="D4" s="610"/>
-      <c r="E4" s="611">
+      <c r="B4" s="612"/>
+      <c r="C4" s="612"/>
+      <c r="D4" s="612"/>
+      <c r="E4" s="613">
         <f>Bilgiler!D2</f>
         <v>0</v>
       </c>
-      <c r="F4" s="611"/>
-      <c r="G4" s="611"/>
-      <c r="H4" s="611"/>
-      <c r="I4" s="611"/>
-      <c r="J4" s="611"/>
-      <c r="K4" s="611"/>
-      <c r="L4" s="611"/>
-      <c r="M4" s="611"/>
-      <c r="N4" s="611"/>
-      <c r="O4" s="611"/>
-      <c r="P4" s="611"/>
-      <c r="Q4" s="611"/>
-      <c r="R4" s="611"/>
-      <c r="S4" s="611"/>
-      <c r="T4" s="611"/>
-      <c r="U4" s="611"/>
-      <c r="V4" s="611"/>
-      <c r="W4" s="611"/>
-      <c r="X4" s="611"/>
-      <c r="Y4" s="611"/>
-      <c r="Z4" s="611"/>
-      <c r="AA4" s="612"/>
+      <c r="F4" s="613"/>
+      <c r="G4" s="613"/>
+      <c r="H4" s="613"/>
+      <c r="I4" s="613"/>
+      <c r="J4" s="613"/>
+      <c r="K4" s="613"/>
+      <c r="L4" s="613"/>
+      <c r="M4" s="613"/>
+      <c r="N4" s="613"/>
+      <c r="O4" s="613"/>
+      <c r="P4" s="613"/>
+      <c r="Q4" s="613"/>
+      <c r="R4" s="613"/>
+      <c r="S4" s="613"/>
+      <c r="T4" s="613"/>
+      <c r="U4" s="613"/>
+      <c r="V4" s="613"/>
+      <c r="W4" s="613"/>
+      <c r="X4" s="613"/>
+      <c r="Y4" s="613"/>
+      <c r="Z4" s="613"/>
+      <c r="AA4" s="614"/>
     </row>
     <row r="5" spans="1:28" ht="12" customHeight="1">
-      <c r="A5" s="613" t="s">
+      <c r="A5" s="615" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="614"/>
-      <c r="C5" s="614"/>
-      <c r="D5" s="614"/>
-      <c r="E5" s="614"/>
-      <c r="F5" s="614"/>
-      <c r="G5" s="614"/>
-      <c r="H5" s="614"/>
-      <c r="I5" s="614"/>
-      <c r="J5" s="614"/>
-      <c r="K5" s="615"/>
-      <c r="L5" s="616" t="s">
+      <c r="B5" s="616"/>
+      <c r="C5" s="616"/>
+      <c r="D5" s="616"/>
+      <c r="E5" s="616"/>
+      <c r="F5" s="616"/>
+      <c r="G5" s="616"/>
+      <c r="H5" s="616"/>
+      <c r="I5" s="616"/>
+      <c r="J5" s="616"/>
+      <c r="K5" s="617"/>
+      <c r="L5" s="618" t="s">
         <v>69</v>
       </c>
-      <c r="M5" s="614"/>
-      <c r="N5" s="614"/>
-      <c r="O5" s="614"/>
-      <c r="P5" s="614"/>
-      <c r="Q5" s="614"/>
-      <c r="R5" s="614"/>
-      <c r="S5" s="614"/>
-      <c r="T5" s="617"/>
-      <c r="U5" s="617"/>
-      <c r="V5" s="617"/>
-      <c r="W5" s="617"/>
-      <c r="X5" s="617"/>
-      <c r="Y5" s="617"/>
-      <c r="Z5" s="617"/>
-      <c r="AA5" s="618"/>
+      <c r="M5" s="616"/>
+      <c r="N5" s="616"/>
+      <c r="O5" s="616"/>
+      <c r="P5" s="616"/>
+      <c r="Q5" s="616"/>
+      <c r="R5" s="616"/>
+      <c r="S5" s="616"/>
+      <c r="T5" s="619"/>
+      <c r="U5" s="619"/>
+      <c r="V5" s="619"/>
+      <c r="W5" s="619"/>
+      <c r="X5" s="619"/>
+      <c r="Y5" s="619"/>
+      <c r="Z5" s="619"/>
+      <c r="AA5" s="620"/>
     </row>
     <row r="6" spans="1:28" ht="12" customHeight="1">
-      <c r="A6" s="603" t="s">
+      <c r="A6" s="605" t="s">
         <v>174</v>
       </c>
-      <c r="B6" s="604"/>
-      <c r="C6" s="604"/>
-      <c r="D6" s="604"/>
-      <c r="E6" s="604"/>
-      <c r="F6" s="604"/>
-      <c r="G6" s="604"/>
-      <c r="H6" s="604"/>
-      <c r="I6" s="605">
+      <c r="B6" s="606"/>
+      <c r="C6" s="606"/>
+      <c r="D6" s="606"/>
+      <c r="E6" s="606"/>
+      <c r="F6" s="606"/>
+      <c r="G6" s="606"/>
+      <c r="H6" s="606"/>
+      <c r="I6" s="607">
         <f>'İş Takip-Ön Yüz'!G14</f>
         <v>0</v>
       </c>
-      <c r="J6" s="606"/>
-      <c r="K6" s="606"/>
-      <c r="L6" s="606"/>
-      <c r="M6" s="606"/>
-      <c r="N6" s="606"/>
-      <c r="O6" s="606"/>
-      <c r="P6" s="606"/>
-      <c r="Q6" s="606"/>
-      <c r="R6" s="606"/>
-      <c r="S6" s="606"/>
-      <c r="T6" s="606"/>
-      <c r="U6" s="606"/>
-      <c r="V6" s="606"/>
-      <c r="W6" s="606"/>
-      <c r="X6" s="606"/>
-      <c r="Y6" s="606"/>
-      <c r="Z6" s="606"/>
-      <c r="AA6" s="607"/>
+      <c r="J6" s="608"/>
+      <c r="K6" s="608"/>
+      <c r="L6" s="608"/>
+      <c r="M6" s="608"/>
+      <c r="N6" s="608"/>
+      <c r="O6" s="608"/>
+      <c r="P6" s="608"/>
+      <c r="Q6" s="608"/>
+      <c r="R6" s="608"/>
+      <c r="S6" s="608"/>
+      <c r="T6" s="608"/>
+      <c r="U6" s="608"/>
+      <c r="V6" s="608"/>
+      <c r="W6" s="608"/>
+      <c r="X6" s="608"/>
+      <c r="Y6" s="608"/>
+      <c r="Z6" s="608"/>
+      <c r="AA6" s="609"/>
     </row>
     <row r="7" spans="1:28" ht="12" customHeight="1">
-      <c r="A7" s="608"/>
-      <c r="B7" s="606"/>
-      <c r="C7" s="606"/>
-      <c r="D7" s="606"/>
-      <c r="E7" s="606"/>
-      <c r="F7" s="606"/>
-      <c r="G7" s="606"/>
-      <c r="H7" s="606"/>
-      <c r="I7" s="606"/>
-      <c r="J7" s="606"/>
-      <c r="K7" s="606"/>
-      <c r="L7" s="606"/>
-      <c r="M7" s="606"/>
-      <c r="N7" s="606"/>
-      <c r="O7" s="606"/>
-      <c r="P7" s="606"/>
-      <c r="Q7" s="606"/>
-      <c r="R7" s="606"/>
-      <c r="S7" s="606"/>
-      <c r="T7" s="606"/>
-      <c r="U7" s="606"/>
-      <c r="V7" s="606"/>
-      <c r="W7" s="606"/>
-      <c r="X7" s="606"/>
-      <c r="Y7" s="606"/>
-      <c r="Z7" s="606"/>
-      <c r="AA7" s="607"/>
+      <c r="A7" s="610"/>
+      <c r="B7" s="608"/>
+      <c r="C7" s="608"/>
+      <c r="D7" s="608"/>
+      <c r="E7" s="608"/>
+      <c r="F7" s="608"/>
+      <c r="G7" s="608"/>
+      <c r="H7" s="608"/>
+      <c r="I7" s="608"/>
+      <c r="J7" s="608"/>
+      <c r="K7" s="608"/>
+      <c r="L7" s="608"/>
+      <c r="M7" s="608"/>
+      <c r="N7" s="608"/>
+      <c r="O7" s="608"/>
+      <c r="P7" s="608"/>
+      <c r="Q7" s="608"/>
+      <c r="R7" s="608"/>
+      <c r="S7" s="608"/>
+      <c r="T7" s="608"/>
+      <c r="U7" s="608"/>
+      <c r="V7" s="608"/>
+      <c r="W7" s="608"/>
+      <c r="X7" s="608"/>
+      <c r="Y7" s="608"/>
+      <c r="Z7" s="608"/>
+      <c r="AA7" s="609"/>
     </row>
     <row r="8" spans="1:28" ht="12" customHeight="1">
-      <c r="A8" s="597"/>
-      <c r="B8" s="598"/>
-      <c r="C8" s="598"/>
-      <c r="D8" s="598"/>
-      <c r="E8" s="598"/>
-      <c r="F8" s="598"/>
-      <c r="G8" s="598"/>
-      <c r="H8" s="598"/>
-      <c r="I8" s="598"/>
-      <c r="J8" s="598"/>
-      <c r="K8" s="598"/>
-      <c r="L8" s="598"/>
-      <c r="M8" s="598"/>
-      <c r="N8" s="598"/>
-      <c r="O8" s="598"/>
-      <c r="P8" s="598"/>
-      <c r="Q8" s="598"/>
-      <c r="R8" s="598"/>
-      <c r="S8" s="598"/>
-      <c r="T8" s="598"/>
-      <c r="U8" s="598"/>
-      <c r="V8" s="598"/>
-      <c r="W8" s="598"/>
-      <c r="X8" s="598"/>
-      <c r="Y8" s="598"/>
-      <c r="Z8" s="598"/>
-      <c r="AA8" s="599"/>
+      <c r="A8" s="599"/>
+      <c r="B8" s="600"/>
+      <c r="C8" s="600"/>
+      <c r="D8" s="600"/>
+      <c r="E8" s="600"/>
+      <c r="F8" s="600"/>
+      <c r="G8" s="600"/>
+      <c r="H8" s="600"/>
+      <c r="I8" s="600"/>
+      <c r="J8" s="600"/>
+      <c r="K8" s="600"/>
+      <c r="L8" s="600"/>
+      <c r="M8" s="600"/>
+      <c r="N8" s="600"/>
+      <c r="O8" s="600"/>
+      <c r="P8" s="600"/>
+      <c r="Q8" s="600"/>
+      <c r="R8" s="600"/>
+      <c r="S8" s="600"/>
+      <c r="T8" s="600"/>
+      <c r="U8" s="600"/>
+      <c r="V8" s="600"/>
+      <c r="W8" s="600"/>
+      <c r="X8" s="600"/>
+      <c r="Y8" s="600"/>
+      <c r="Z8" s="600"/>
+      <c r="AA8" s="601"/>
     </row>
     <row r="9" spans="1:28" ht="12" customHeight="1">
-      <c r="A9" s="600" t="s">
+      <c r="A9" s="602" t="s">
         <v>184</v>
       </c>
       <c r="B9" s="582"/>
@@ -19667,10 +19682,10 @@
       <c r="X9" s="582"/>
       <c r="Y9" s="582"/>
       <c r="Z9" s="582"/>
-      <c r="AA9" s="601"/>
+      <c r="AA9" s="603"/>
     </row>
     <row r="10" spans="1:28" ht="12" customHeight="1">
-      <c r="A10" s="600" t="s">
+      <c r="A10" s="602" t="s">
         <v>71</v>
       </c>
       <c r="B10" s="582"/>
@@ -19679,10 +19694,10 @@
       <c r="E10" s="582"/>
       <c r="F10" s="582"/>
       <c r="G10" s="582"/>
-      <c r="H10" s="602"/>
-      <c r="I10" s="602"/>
-      <c r="J10" s="602"/>
-      <c r="K10" s="602"/>
+      <c r="H10" s="604"/>
+      <c r="I10" s="604"/>
+      <c r="J10" s="604"/>
+      <c r="K10" s="604"/>
       <c r="L10" s="582"/>
       <c r="M10" s="582"/>
       <c r="N10" s="582"/>
@@ -19710,26 +19725,26 @@
       <c r="E11" s="595"/>
       <c r="F11" s="595"/>
       <c r="G11" s="595"/>
-      <c r="H11" s="549"/>
-      <c r="I11" s="532"/>
-      <c r="J11" s="532"/>
-      <c r="K11" s="532"/>
-      <c r="L11" s="532"/>
-      <c r="M11" s="532"/>
-      <c r="N11" s="532"/>
-      <c r="O11" s="532"/>
-      <c r="P11" s="532"/>
-      <c r="Q11" s="532"/>
-      <c r="R11" s="532"/>
-      <c r="S11" s="532"/>
-      <c r="T11" s="532"/>
-      <c r="U11" s="532"/>
-      <c r="V11" s="532"/>
-      <c r="W11" s="532"/>
-      <c r="X11" s="532"/>
-      <c r="Y11" s="532"/>
-      <c r="Z11" s="532"/>
-      <c r="AA11" s="533"/>
+      <c r="H11" s="597"/>
+      <c r="I11" s="597"/>
+      <c r="J11" s="597"/>
+      <c r="K11" s="597"/>
+      <c r="L11" s="597"/>
+      <c r="M11" s="597"/>
+      <c r="N11" s="597"/>
+      <c r="O11" s="597"/>
+      <c r="P11" s="597"/>
+      <c r="Q11" s="597"/>
+      <c r="R11" s="597"/>
+      <c r="S11" s="597"/>
+      <c r="T11" s="597"/>
+      <c r="U11" s="597"/>
+      <c r="V11" s="597"/>
+      <c r="W11" s="597"/>
+      <c r="X11" s="597"/>
+      <c r="Y11" s="597"/>
+      <c r="Z11" s="597"/>
+      <c r="AA11" s="598"/>
     </row>
     <row r="12" spans="1:28" ht="12" customHeight="1">
       <c r="A12" s="594" t="s">
@@ -19741,26 +19756,26 @@
       <c r="E12" s="595"/>
       <c r="F12" s="595"/>
       <c r="G12" s="595"/>
-      <c r="H12" s="549"/>
-      <c r="I12" s="549"/>
-      <c r="J12" s="549"/>
-      <c r="K12" s="549"/>
-      <c r="L12" s="532"/>
-      <c r="M12" s="532"/>
-      <c r="N12" s="532"/>
-      <c r="O12" s="532"/>
-      <c r="P12" s="532"/>
-      <c r="Q12" s="532"/>
-      <c r="R12" s="532"/>
-      <c r="S12" s="532"/>
-      <c r="T12" s="532"/>
-      <c r="U12" s="532"/>
-      <c r="V12" s="532"/>
-      <c r="W12" s="532"/>
-      <c r="X12" s="532"/>
-      <c r="Y12" s="532"/>
-      <c r="Z12" s="532"/>
-      <c r="AA12" s="533"/>
+      <c r="H12" s="597"/>
+      <c r="I12" s="597"/>
+      <c r="J12" s="597"/>
+      <c r="K12" s="597"/>
+      <c r="L12" s="597"/>
+      <c r="M12" s="597"/>
+      <c r="N12" s="597"/>
+      <c r="O12" s="597"/>
+      <c r="P12" s="597"/>
+      <c r="Q12" s="597"/>
+      <c r="R12" s="597"/>
+      <c r="S12" s="597"/>
+      <c r="T12" s="597"/>
+      <c r="U12" s="597"/>
+      <c r="V12" s="597"/>
+      <c r="W12" s="597"/>
+      <c r="X12" s="597"/>
+      <c r="Y12" s="597"/>
+      <c r="Z12" s="597"/>
+      <c r="AA12" s="598"/>
     </row>
     <row r="13" spans="1:28" ht="12" customHeight="1">
       <c r="A13" s="594" t="s">
@@ -20931,7 +20946,7 @@
       <c r="Z48" s="168"/>
       <c r="AA48" s="588"/>
     </row>
-    <row r="49" spans="1:27" ht="24" customHeight="1">
+    <row r="49" spans="1:29" ht="24" customHeight="1">
       <c r="A49" s="585"/>
       <c r="B49" s="586"/>
       <c r="C49" s="586"/>
@@ -20960,7 +20975,7 @@
       <c r="Z49" s="168"/>
       <c r="AA49" s="588"/>
     </row>
-    <row r="50" spans="1:27" ht="24" customHeight="1">
+    <row r="50" spans="1:29" ht="24" customHeight="1">
       <c r="A50" s="585"/>
       <c r="B50" s="586"/>
       <c r="C50" s="586"/>
@@ -20989,952 +21004,53 @@
       <c r="Z50" s="168"/>
       <c r="AA50" s="588"/>
     </row>
-    <row r="51" spans="1:27" ht="24" customHeight="1">
-      <c r="A51" s="585"/>
-      <c r="B51" s="586"/>
-      <c r="C51" s="586"/>
-      <c r="D51" s="586"/>
-      <c r="E51" s="586"/>
-      <c r="F51" s="586"/>
-      <c r="G51" s="586"/>
-      <c r="H51" s="586"/>
-      <c r="I51" s="586"/>
-      <c r="J51" s="586"/>
-      <c r="K51" s="587"/>
-      <c r="L51" s="422"/>
-      <c r="M51" s="168"/>
-      <c r="N51" s="168"/>
-      <c r="O51" s="168"/>
-      <c r="P51" s="422"/>
-      <c r="Q51" s="168"/>
-      <c r="R51" s="168"/>
-      <c r="S51" s="168"/>
-      <c r="T51" s="422"/>
-      <c r="U51" s="168"/>
-      <c r="V51" s="168"/>
-      <c r="W51" s="168"/>
-      <c r="X51" s="422"/>
-      <c r="Y51" s="168"/>
-      <c r="Z51" s="168"/>
-      <c r="AA51" s="588"/>
-    </row>
-    <row r="52" spans="1:27" ht="24" customHeight="1">
-      <c r="A52" s="585"/>
-      <c r="B52" s="586"/>
-      <c r="C52" s="586"/>
-      <c r="D52" s="586"/>
-      <c r="E52" s="586"/>
-      <c r="F52" s="586"/>
-      <c r="G52" s="586"/>
-      <c r="H52" s="586"/>
-      <c r="I52" s="586"/>
-      <c r="J52" s="586"/>
-      <c r="K52" s="587"/>
-      <c r="L52" s="422"/>
-      <c r="M52" s="168"/>
-      <c r="N52" s="168"/>
-      <c r="O52" s="168"/>
-      <c r="P52" s="422"/>
-      <c r="Q52" s="168"/>
-      <c r="R52" s="168"/>
-      <c r="S52" s="168"/>
-      <c r="T52" s="422"/>
-      <c r="U52" s="168"/>
-      <c r="V52" s="168"/>
-      <c r="W52" s="168"/>
-      <c r="X52" s="422"/>
-      <c r="Y52" s="168"/>
-      <c r="Z52" s="168"/>
-      <c r="AA52" s="588"/>
-    </row>
-    <row r="53" spans="1:27" ht="24" customHeight="1">
-      <c r="A53" s="585"/>
-      <c r="B53" s="586"/>
-      <c r="C53" s="586"/>
-      <c r="D53" s="586"/>
-      <c r="E53" s="586"/>
-      <c r="F53" s="586"/>
-      <c r="G53" s="586"/>
-      <c r="H53" s="586"/>
-      <c r="I53" s="586"/>
-      <c r="J53" s="586"/>
-      <c r="K53" s="587"/>
-      <c r="L53" s="422"/>
-      <c r="M53" s="168"/>
-      <c r="N53" s="168"/>
-      <c r="O53" s="168"/>
-      <c r="P53" s="422"/>
-      <c r="Q53" s="168"/>
-      <c r="R53" s="168"/>
-      <c r="S53" s="168"/>
-      <c r="T53" s="422"/>
-      <c r="U53" s="168"/>
-      <c r="V53" s="168"/>
-      <c r="W53" s="168"/>
-      <c r="X53" s="422"/>
-      <c r="Y53" s="168"/>
-      <c r="Z53" s="168"/>
-      <c r="AA53" s="588"/>
-    </row>
-    <row r="54" spans="1:27" ht="24" customHeight="1">
-      <c r="A54" s="585"/>
-      <c r="B54" s="586"/>
-      <c r="C54" s="586"/>
-      <c r="D54" s="586"/>
-      <c r="E54" s="586"/>
-      <c r="F54" s="586"/>
-      <c r="G54" s="586"/>
-      <c r="H54" s="586"/>
-      <c r="I54" s="586"/>
-      <c r="J54" s="586"/>
-      <c r="K54" s="587"/>
-      <c r="L54" s="422"/>
-      <c r="M54" s="168"/>
-      <c r="N54" s="168"/>
-      <c r="O54" s="168"/>
-      <c r="P54" s="422"/>
-      <c r="Q54" s="168"/>
-      <c r="R54" s="168"/>
-      <c r="S54" s="168"/>
-      <c r="T54" s="422"/>
-      <c r="U54" s="168"/>
-      <c r="V54" s="168"/>
-      <c r="W54" s="168"/>
-      <c r="X54" s="422"/>
-      <c r="Y54" s="168"/>
-      <c r="Z54" s="168"/>
-      <c r="AA54" s="588"/>
-    </row>
-    <row r="55" spans="1:27" ht="24" customHeight="1">
-      <c r="A55" s="585"/>
-      <c r="B55" s="586"/>
-      <c r="C55" s="586"/>
-      <c r="D55" s="586"/>
-      <c r="E55" s="586"/>
-      <c r="F55" s="586"/>
-      <c r="G55" s="586"/>
-      <c r="H55" s="586"/>
-      <c r="I55" s="586"/>
-      <c r="J55" s="586"/>
-      <c r="K55" s="587"/>
-      <c r="L55" s="422"/>
-      <c r="M55" s="168"/>
-      <c r="N55" s="168"/>
-      <c r="O55" s="168"/>
-      <c r="P55" s="422"/>
-      <c r="Q55" s="168"/>
-      <c r="R55" s="168"/>
-      <c r="S55" s="168"/>
-      <c r="T55" s="422"/>
-      <c r="U55" s="168"/>
-      <c r="V55" s="168"/>
-      <c r="W55" s="168"/>
-      <c r="X55" s="422"/>
-      <c r="Y55" s="168"/>
-      <c r="Z55" s="168"/>
-      <c r="AA55" s="588"/>
-    </row>
-    <row r="56" spans="1:27" ht="24" customHeight="1">
-      <c r="A56" s="585"/>
-      <c r="B56" s="586"/>
-      <c r="C56" s="586"/>
-      <c r="D56" s="586"/>
-      <c r="E56" s="586"/>
-      <c r="F56" s="586"/>
-      <c r="G56" s="586"/>
-      <c r="H56" s="586"/>
-      <c r="I56" s="586"/>
-      <c r="J56" s="586"/>
-      <c r="K56" s="587"/>
-      <c r="L56" s="422"/>
-      <c r="M56" s="168"/>
-      <c r="N56" s="168"/>
-      <c r="O56" s="168"/>
-      <c r="P56" s="422"/>
-      <c r="Q56" s="168"/>
-      <c r="R56" s="168"/>
-      <c r="S56" s="168"/>
-      <c r="T56" s="422"/>
-      <c r="U56" s="168"/>
-      <c r="V56" s="168"/>
-      <c r="W56" s="168"/>
-      <c r="X56" s="422"/>
-      <c r="Y56" s="168"/>
-      <c r="Z56" s="168"/>
-      <c r="AA56" s="588"/>
-    </row>
-    <row r="57" spans="1:27" ht="24" customHeight="1">
-      <c r="A57" s="585"/>
-      <c r="B57" s="586"/>
-      <c r="C57" s="586"/>
-      <c r="D57" s="586"/>
-      <c r="E57" s="586"/>
-      <c r="F57" s="586"/>
-      <c r="G57" s="586"/>
-      <c r="H57" s="586"/>
-      <c r="I57" s="586"/>
-      <c r="J57" s="586"/>
-      <c r="K57" s="587"/>
-      <c r="L57" s="422"/>
-      <c r="M57" s="168"/>
-      <c r="N57" s="168"/>
-      <c r="O57" s="168"/>
-      <c r="P57" s="422"/>
-      <c r="Q57" s="168"/>
-      <c r="R57" s="168"/>
-      <c r="S57" s="168"/>
-      <c r="T57" s="422"/>
-      <c r="U57" s="168"/>
-      <c r="V57" s="168"/>
-      <c r="W57" s="168"/>
-      <c r="X57" s="422"/>
-      <c r="Y57" s="168"/>
-      <c r="Z57" s="168"/>
-      <c r="AA57" s="588"/>
-    </row>
-    <row r="58" spans="1:27" ht="24" customHeight="1">
-      <c r="A58" s="585"/>
-      <c r="B58" s="586"/>
-      <c r="C58" s="586"/>
-      <c r="D58" s="586"/>
-      <c r="E58" s="586"/>
-      <c r="F58" s="586"/>
-      <c r="G58" s="586"/>
-      <c r="H58" s="586"/>
-      <c r="I58" s="586"/>
-      <c r="J58" s="586"/>
-      <c r="K58" s="587"/>
-      <c r="L58" s="422"/>
-      <c r="M58" s="168"/>
-      <c r="N58" s="168"/>
-      <c r="O58" s="168"/>
-      <c r="P58" s="422"/>
-      <c r="Q58" s="168"/>
-      <c r="R58" s="168"/>
-      <c r="S58" s="168"/>
-      <c r="T58" s="422"/>
-      <c r="U58" s="168"/>
-      <c r="V58" s="168"/>
-      <c r="W58" s="168"/>
-      <c r="X58" s="422"/>
-      <c r="Y58" s="168"/>
-      <c r="Z58" s="168"/>
-      <c r="AA58" s="588"/>
-    </row>
-    <row r="59" spans="1:27" ht="24" customHeight="1">
-      <c r="A59" s="585"/>
-      <c r="B59" s="586"/>
-      <c r="C59" s="586"/>
-      <c r="D59" s="586"/>
-      <c r="E59" s="586"/>
-      <c r="F59" s="586"/>
-      <c r="G59" s="586"/>
-      <c r="H59" s="586"/>
-      <c r="I59" s="586"/>
-      <c r="J59" s="586"/>
-      <c r="K59" s="587"/>
-      <c r="L59" s="422"/>
-      <c r="M59" s="168"/>
-      <c r="N59" s="168"/>
-      <c r="O59" s="168"/>
-      <c r="P59" s="422"/>
-      <c r="Q59" s="168"/>
-      <c r="R59" s="168"/>
-      <c r="S59" s="168"/>
-      <c r="T59" s="422"/>
-      <c r="U59" s="168"/>
-      <c r="V59" s="168"/>
-      <c r="W59" s="168"/>
-      <c r="X59" s="422"/>
-      <c r="Y59" s="168"/>
-      <c r="Z59" s="168"/>
-      <c r="AA59" s="588"/>
-    </row>
-    <row r="60" spans="1:27" ht="24" customHeight="1">
-      <c r="A60" s="585"/>
-      <c r="B60" s="586"/>
-      <c r="C60" s="586"/>
-      <c r="D60" s="586"/>
-      <c r="E60" s="586"/>
-      <c r="F60" s="586"/>
-      <c r="G60" s="586"/>
-      <c r="H60" s="586"/>
-      <c r="I60" s="586"/>
-      <c r="J60" s="586"/>
-      <c r="K60" s="587"/>
-      <c r="L60" s="422"/>
-      <c r="M60" s="168"/>
-      <c r="N60" s="168"/>
-      <c r="O60" s="168"/>
-      <c r="P60" s="422"/>
-      <c r="Q60" s="168"/>
-      <c r="R60" s="168"/>
-      <c r="S60" s="168"/>
-      <c r="T60" s="422"/>
-      <c r="U60" s="168"/>
-      <c r="V60" s="168"/>
-      <c r="W60" s="168"/>
-      <c r="X60" s="422"/>
-      <c r="Y60" s="168"/>
-      <c r="Z60" s="168"/>
-      <c r="AA60" s="588"/>
-    </row>
-    <row r="61" spans="1:27" ht="24" customHeight="1">
-      <c r="A61" s="585"/>
-      <c r="B61" s="586"/>
-      <c r="C61" s="586"/>
-      <c r="D61" s="586"/>
-      <c r="E61" s="586"/>
-      <c r="F61" s="586"/>
-      <c r="G61" s="586"/>
-      <c r="H61" s="586"/>
-      <c r="I61" s="586"/>
-      <c r="J61" s="586"/>
-      <c r="K61" s="587"/>
-      <c r="L61" s="422"/>
-      <c r="M61" s="168"/>
-      <c r="N61" s="168"/>
-      <c r="O61" s="168"/>
-      <c r="P61" s="422"/>
-      <c r="Q61" s="168"/>
-      <c r="R61" s="168"/>
-      <c r="S61" s="168"/>
-      <c r="T61" s="422"/>
-      <c r="U61" s="168"/>
-      <c r="V61" s="168"/>
-      <c r="W61" s="168"/>
-      <c r="X61" s="422"/>
-      <c r="Y61" s="168"/>
-      <c r="Z61" s="168"/>
-      <c r="AA61" s="588"/>
-    </row>
-    <row r="62" spans="1:27" ht="24" customHeight="1">
-      <c r="A62" s="585"/>
-      <c r="B62" s="586"/>
-      <c r="C62" s="586"/>
-      <c r="D62" s="586"/>
-      <c r="E62" s="586"/>
-      <c r="F62" s="586"/>
-      <c r="G62" s="586"/>
-      <c r="H62" s="586"/>
-      <c r="I62" s="586"/>
-      <c r="J62" s="586"/>
-      <c r="K62" s="587"/>
-      <c r="L62" s="422"/>
-      <c r="M62" s="168"/>
-      <c r="N62" s="168"/>
-      <c r="O62" s="168"/>
-      <c r="P62" s="422"/>
-      <c r="Q62" s="168"/>
-      <c r="R62" s="168"/>
-      <c r="S62" s="168"/>
-      <c r="T62" s="422"/>
-      <c r="U62" s="168"/>
-      <c r="V62" s="168"/>
-      <c r="W62" s="168"/>
-      <c r="X62" s="422"/>
-      <c r="Y62" s="168"/>
-      <c r="Z62" s="168"/>
-      <c r="AA62" s="588"/>
-    </row>
-    <row r="63" spans="1:27" ht="24" customHeight="1">
-      <c r="A63" s="585"/>
-      <c r="B63" s="586"/>
-      <c r="C63" s="586"/>
-      <c r="D63" s="586"/>
-      <c r="E63" s="586"/>
-      <c r="F63" s="586"/>
-      <c r="G63" s="586"/>
-      <c r="H63" s="586"/>
-      <c r="I63" s="586"/>
-      <c r="J63" s="586"/>
-      <c r="K63" s="587"/>
-      <c r="L63" s="422"/>
-      <c r="M63" s="168"/>
-      <c r="N63" s="168"/>
-      <c r="O63" s="168"/>
-      <c r="P63" s="422"/>
-      <c r="Q63" s="168"/>
-      <c r="R63" s="168"/>
-      <c r="S63" s="168"/>
-      <c r="T63" s="422"/>
-      <c r="U63" s="168"/>
-      <c r="V63" s="168"/>
-      <c r="W63" s="168"/>
-      <c r="X63" s="422"/>
-      <c r="Y63" s="168"/>
-      <c r="Z63" s="168"/>
-      <c r="AA63" s="588"/>
-    </row>
-    <row r="64" spans="1:27" ht="24" customHeight="1">
-      <c r="A64" s="585"/>
-      <c r="B64" s="586"/>
-      <c r="C64" s="586"/>
-      <c r="D64" s="586"/>
-      <c r="E64" s="586"/>
-      <c r="F64" s="586"/>
-      <c r="G64" s="586"/>
-      <c r="H64" s="586"/>
-      <c r="I64" s="586"/>
-      <c r="J64" s="586"/>
-      <c r="K64" s="587"/>
-      <c r="L64" s="422"/>
-      <c r="M64" s="168"/>
-      <c r="N64" s="168"/>
-      <c r="O64" s="168"/>
-      <c r="P64" s="422"/>
-      <c r="Q64" s="168"/>
-      <c r="R64" s="168"/>
-      <c r="S64" s="168"/>
-      <c r="T64" s="422"/>
-      <c r="U64" s="168"/>
-      <c r="V64" s="168"/>
-      <c r="W64" s="168"/>
-      <c r="X64" s="422"/>
-      <c r="Y64" s="168"/>
-      <c r="Z64" s="168"/>
-      <c r="AA64" s="588"/>
-    </row>
-    <row r="65" spans="1:27" ht="24" customHeight="1">
-      <c r="A65" s="585"/>
-      <c r="B65" s="586"/>
-      <c r="C65" s="586"/>
-      <c r="D65" s="586"/>
-      <c r="E65" s="586"/>
-      <c r="F65" s="586"/>
-      <c r="G65" s="586"/>
-      <c r="H65" s="586"/>
-      <c r="I65" s="586"/>
-      <c r="J65" s="586"/>
-      <c r="K65" s="587"/>
-      <c r="L65" s="422"/>
-      <c r="M65" s="168"/>
-      <c r="N65" s="168"/>
-      <c r="O65" s="168"/>
-      <c r="P65" s="422"/>
-      <c r="Q65" s="168"/>
-      <c r="R65" s="168"/>
-      <c r="S65" s="168"/>
-      <c r="T65" s="422"/>
-      <c r="U65" s="168"/>
-      <c r="V65" s="168"/>
-      <c r="W65" s="168"/>
-      <c r="X65" s="422"/>
-      <c r="Y65" s="168"/>
-      <c r="Z65" s="168"/>
-      <c r="AA65" s="588"/>
-    </row>
-    <row r="66" spans="1:27" ht="24" customHeight="1">
-      <c r="A66" s="585"/>
-      <c r="B66" s="586"/>
-      <c r="C66" s="586"/>
-      <c r="D66" s="586"/>
-      <c r="E66" s="586"/>
-      <c r="F66" s="586"/>
-      <c r="G66" s="586"/>
-      <c r="H66" s="586"/>
-      <c r="I66" s="586"/>
-      <c r="J66" s="586"/>
-      <c r="K66" s="587"/>
-      <c r="L66" s="422"/>
-      <c r="M66" s="168"/>
-      <c r="N66" s="168"/>
-      <c r="O66" s="168"/>
-      <c r="P66" s="422"/>
-      <c r="Q66" s="168"/>
-      <c r="R66" s="168"/>
-      <c r="S66" s="168"/>
-      <c r="T66" s="422"/>
-      <c r="U66" s="168"/>
-      <c r="V66" s="168"/>
-      <c r="W66" s="168"/>
-      <c r="X66" s="422"/>
-      <c r="Y66" s="168"/>
-      <c r="Z66" s="168"/>
-      <c r="AA66" s="588"/>
-    </row>
-    <row r="67" spans="1:27" ht="24" customHeight="1">
-      <c r="A67" s="585"/>
-      <c r="B67" s="586"/>
-      <c r="C67" s="586"/>
-      <c r="D67" s="586"/>
-      <c r="E67" s="586"/>
-      <c r="F67" s="586"/>
-      <c r="G67" s="586"/>
-      <c r="H67" s="586"/>
-      <c r="I67" s="586"/>
-      <c r="J67" s="586"/>
-      <c r="K67" s="587"/>
-      <c r="L67" s="422"/>
-      <c r="M67" s="168"/>
-      <c r="N67" s="168"/>
-      <c r="O67" s="168"/>
-      <c r="P67" s="422"/>
-      <c r="Q67" s="168"/>
-      <c r="R67" s="168"/>
-      <c r="S67" s="168"/>
-      <c r="T67" s="422"/>
-      <c r="U67" s="168"/>
-      <c r="V67" s="168"/>
-      <c r="W67" s="168"/>
-      <c r="X67" s="422"/>
-      <c r="Y67" s="168"/>
-      <c r="Z67" s="168"/>
-      <c r="AA67" s="588"/>
-    </row>
-    <row r="68" spans="1:27" ht="24" customHeight="1">
-      <c r="A68" s="585"/>
-      <c r="B68" s="586"/>
-      <c r="C68" s="586"/>
-      <c r="D68" s="586"/>
-      <c r="E68" s="586"/>
-      <c r="F68" s="586"/>
-      <c r="G68" s="586"/>
-      <c r="H68" s="586"/>
-      <c r="I68" s="586"/>
-      <c r="J68" s="586"/>
-      <c r="K68" s="587"/>
-      <c r="L68" s="422"/>
-      <c r="M68" s="168"/>
-      <c r="N68" s="168"/>
-      <c r="O68" s="168"/>
-      <c r="P68" s="422"/>
-      <c r="Q68" s="168"/>
-      <c r="R68" s="168"/>
-      <c r="S68" s="168"/>
-      <c r="T68" s="422"/>
-      <c r="U68" s="168"/>
-      <c r="V68" s="168"/>
-      <c r="W68" s="168"/>
-      <c r="X68" s="422"/>
-      <c r="Y68" s="168"/>
-      <c r="Z68" s="168"/>
-      <c r="AA68" s="588"/>
-    </row>
-    <row r="69" spans="1:27" ht="24" customHeight="1">
-      <c r="A69" s="585"/>
-      <c r="B69" s="586"/>
-      <c r="C69" s="586"/>
-      <c r="D69" s="586"/>
-      <c r="E69" s="586"/>
-      <c r="F69" s="586"/>
-      <c r="G69" s="586"/>
-      <c r="H69" s="586"/>
-      <c r="I69" s="586"/>
-      <c r="J69" s="586"/>
-      <c r="K69" s="587"/>
-      <c r="L69" s="422"/>
-      <c r="M69" s="168"/>
-      <c r="N69" s="168"/>
-      <c r="O69" s="168"/>
-      <c r="P69" s="422"/>
-      <c r="Q69" s="168"/>
-      <c r="R69" s="168"/>
-      <c r="S69" s="168"/>
-      <c r="T69" s="422"/>
-      <c r="U69" s="168"/>
-      <c r="V69" s="168"/>
-      <c r="W69" s="168"/>
-      <c r="X69" s="422"/>
-      <c r="Y69" s="168"/>
-      <c r="Z69" s="168"/>
-      <c r="AA69" s="588"/>
-    </row>
-    <row r="70" spans="1:27" ht="24" customHeight="1">
-      <c r="A70" s="585"/>
-      <c r="B70" s="586"/>
-      <c r="C70" s="586"/>
-      <c r="D70" s="586"/>
-      <c r="E70" s="586"/>
-      <c r="F70" s="586"/>
-      <c r="G70" s="586"/>
-      <c r="H70" s="586"/>
-      <c r="I70" s="586"/>
-      <c r="J70" s="586"/>
-      <c r="K70" s="587"/>
-      <c r="L70" s="422"/>
-      <c r="M70" s="168"/>
-      <c r="N70" s="168"/>
-      <c r="O70" s="168"/>
-      <c r="P70" s="422"/>
-      <c r="Q70" s="168"/>
-      <c r="R70" s="168"/>
-      <c r="S70" s="168"/>
-      <c r="T70" s="422"/>
-      <c r="U70" s="168"/>
-      <c r="V70" s="168"/>
-      <c r="W70" s="168"/>
-      <c r="X70" s="422"/>
-      <c r="Y70" s="168"/>
-      <c r="Z70" s="168"/>
-      <c r="AA70" s="588"/>
-    </row>
-    <row r="71" spans="1:27" ht="24" customHeight="1">
-      <c r="A71" s="585"/>
-      <c r="B71" s="586"/>
-      <c r="C71" s="586"/>
-      <c r="D71" s="586"/>
-      <c r="E71" s="586"/>
-      <c r="F71" s="586"/>
-      <c r="G71" s="586"/>
-      <c r="H71" s="586"/>
-      <c r="I71" s="586"/>
-      <c r="J71" s="586"/>
-      <c r="K71" s="587"/>
-      <c r="L71" s="422"/>
-      <c r="M71" s="168"/>
-      <c r="N71" s="168"/>
-      <c r="O71" s="168"/>
-      <c r="P71" s="422"/>
-      <c r="Q71" s="168"/>
-      <c r="R71" s="168"/>
-      <c r="S71" s="168"/>
-      <c r="T71" s="422"/>
-      <c r="U71" s="168"/>
-      <c r="V71" s="168"/>
-      <c r="W71" s="168"/>
-      <c r="X71" s="422"/>
-      <c r="Y71" s="168"/>
-      <c r="Z71" s="168"/>
-      <c r="AA71" s="588"/>
-    </row>
-    <row r="72" spans="1:27" ht="24" customHeight="1">
-      <c r="A72" s="585"/>
-      <c r="B72" s="586"/>
-      <c r="C72" s="586"/>
-      <c r="D72" s="586"/>
-      <c r="E72" s="586"/>
-      <c r="F72" s="586"/>
-      <c r="G72" s="586"/>
-      <c r="H72" s="586"/>
-      <c r="I72" s="586"/>
-      <c r="J72" s="586"/>
-      <c r="K72" s="587"/>
-      <c r="L72" s="422"/>
-      <c r="M72" s="168"/>
-      <c r="N72" s="168"/>
-      <c r="O72" s="168"/>
-      <c r="P72" s="422"/>
-      <c r="Q72" s="168"/>
-      <c r="R72" s="168"/>
-      <c r="S72" s="168"/>
-      <c r="T72" s="422"/>
-      <c r="U72" s="168"/>
-      <c r="V72" s="168"/>
-      <c r="W72" s="168"/>
-      <c r="X72" s="422"/>
-      <c r="Y72" s="168"/>
-      <c r="Z72" s="168"/>
-      <c r="AA72" s="588"/>
-    </row>
-    <row r="73" spans="1:27" ht="24" customHeight="1">
-      <c r="A73" s="585"/>
-      <c r="B73" s="586"/>
-      <c r="C73" s="586"/>
-      <c r="D73" s="586"/>
-      <c r="E73" s="586"/>
-      <c r="F73" s="586"/>
-      <c r="G73" s="586"/>
-      <c r="H73" s="586"/>
-      <c r="I73" s="586"/>
-      <c r="J73" s="586"/>
-      <c r="K73" s="587"/>
-      <c r="L73" s="422"/>
-      <c r="M73" s="168"/>
-      <c r="N73" s="168"/>
-      <c r="O73" s="168"/>
-      <c r="P73" s="422"/>
-      <c r="Q73" s="168"/>
-      <c r="R73" s="168"/>
-      <c r="S73" s="168"/>
-      <c r="T73" s="422"/>
-      <c r="U73" s="168"/>
-      <c r="V73" s="168"/>
-      <c r="W73" s="168"/>
-      <c r="X73" s="422"/>
-      <c r="Y73" s="168"/>
-      <c r="Z73" s="168"/>
-      <c r="AA73" s="588"/>
-    </row>
-    <row r="74" spans="1:27" ht="24" customHeight="1">
-      <c r="A74" s="585"/>
-      <c r="B74" s="586"/>
-      <c r="C74" s="586"/>
-      <c r="D74" s="586"/>
-      <c r="E74" s="586"/>
-      <c r="F74" s="586"/>
-      <c r="G74" s="586"/>
-      <c r="H74" s="586"/>
-      <c r="I74" s="586"/>
-      <c r="J74" s="586"/>
-      <c r="K74" s="587"/>
-      <c r="L74" s="422"/>
-      <c r="M74" s="168"/>
-      <c r="N74" s="168"/>
-      <c r="O74" s="168"/>
-      <c r="P74" s="422"/>
-      <c r="Q74" s="168"/>
-      <c r="R74" s="168"/>
-      <c r="S74" s="168"/>
-      <c r="T74" s="422"/>
-      <c r="U74" s="168"/>
-      <c r="V74" s="168"/>
-      <c r="W74" s="168"/>
-      <c r="X74" s="422"/>
-      <c r="Y74" s="168"/>
-      <c r="Z74" s="168"/>
-      <c r="AA74" s="588"/>
-    </row>
-    <row r="75" spans="1:27" ht="24" customHeight="1">
-      <c r="A75" s="585"/>
-      <c r="B75" s="586"/>
-      <c r="C75" s="586"/>
-      <c r="D75" s="586"/>
-      <c r="E75" s="586"/>
-      <c r="F75" s="586"/>
-      <c r="G75" s="586"/>
-      <c r="H75" s="586"/>
-      <c r="I75" s="586"/>
-      <c r="J75" s="586"/>
-      <c r="K75" s="587"/>
-      <c r="L75" s="422"/>
-      <c r="M75" s="168"/>
-      <c r="N75" s="168"/>
-      <c r="O75" s="168"/>
-      <c r="P75" s="422"/>
-      <c r="Q75" s="168"/>
-      <c r="R75" s="168"/>
-      <c r="S75" s="168"/>
-      <c r="T75" s="422"/>
-      <c r="U75" s="168"/>
-      <c r="V75" s="168"/>
-      <c r="W75" s="168"/>
-      <c r="X75" s="422"/>
-      <c r="Y75" s="168"/>
-      <c r="Z75" s="168"/>
-      <c r="AA75" s="588"/>
-    </row>
-    <row r="76" spans="1:27" ht="24" customHeight="1">
-      <c r="A76" s="585"/>
-      <c r="B76" s="586"/>
-      <c r="C76" s="586"/>
-      <c r="D76" s="586"/>
-      <c r="E76" s="586"/>
-      <c r="F76" s="586"/>
-      <c r="G76" s="586"/>
-      <c r="H76" s="586"/>
-      <c r="I76" s="586"/>
-      <c r="J76" s="586"/>
-      <c r="K76" s="587"/>
-      <c r="L76" s="422"/>
-      <c r="M76" s="168"/>
-      <c r="N76" s="168"/>
-      <c r="O76" s="168"/>
-      <c r="P76" s="422"/>
-      <c r="Q76" s="168"/>
-      <c r="R76" s="168"/>
-      <c r="S76" s="168"/>
-      <c r="T76" s="422"/>
-      <c r="U76" s="168"/>
-      <c r="V76" s="168"/>
-      <c r="W76" s="168"/>
-      <c r="X76" s="422"/>
-      <c r="Y76" s="168"/>
-      <c r="Z76" s="168"/>
-      <c r="AA76" s="588"/>
-    </row>
-    <row r="77" spans="1:27" ht="24" customHeight="1">
-      <c r="A77" s="585"/>
-      <c r="B77" s="586"/>
-      <c r="C77" s="586"/>
-      <c r="D77" s="586"/>
-      <c r="E77" s="586"/>
-      <c r="F77" s="586"/>
-      <c r="G77" s="586"/>
-      <c r="H77" s="586"/>
-      <c r="I77" s="586"/>
-      <c r="J77" s="586"/>
-      <c r="K77" s="587"/>
-      <c r="L77" s="422"/>
-      <c r="M77" s="168"/>
-      <c r="N77" s="168"/>
-      <c r="O77" s="168"/>
-      <c r="P77" s="422"/>
-      <c r="Q77" s="168"/>
-      <c r="R77" s="168"/>
-      <c r="S77" s="168"/>
-      <c r="T77" s="422"/>
-      <c r="U77" s="168"/>
-      <c r="V77" s="168"/>
-      <c r="W77" s="168"/>
-      <c r="X77" s="422"/>
-      <c r="Y77" s="168"/>
-      <c r="Z77" s="168"/>
-      <c r="AA77" s="588"/>
-    </row>
-    <row r="78" spans="1:27" ht="24" customHeight="1">
-      <c r="A78" s="585"/>
-      <c r="B78" s="586"/>
-      <c r="C78" s="586"/>
-      <c r="D78" s="586"/>
-      <c r="E78" s="586"/>
-      <c r="F78" s="586"/>
-      <c r="G78" s="586"/>
-      <c r="H78" s="586"/>
-      <c r="I78" s="586"/>
-      <c r="J78" s="586"/>
-      <c r="K78" s="587"/>
-      <c r="L78" s="422"/>
-      <c r="M78" s="168"/>
-      <c r="N78" s="168"/>
-      <c r="O78" s="168"/>
-      <c r="P78" s="422"/>
-      <c r="Q78" s="168"/>
-      <c r="R78" s="168"/>
-      <c r="S78" s="168"/>
-      <c r="T78" s="422"/>
-      <c r="U78" s="168"/>
-      <c r="V78" s="168"/>
-      <c r="W78" s="168"/>
-      <c r="X78" s="422"/>
-      <c r="Y78" s="168"/>
-      <c r="Z78" s="168"/>
-      <c r="AA78" s="588"/>
-    </row>
-    <row r="79" spans="1:27" ht="24" customHeight="1">
-      <c r="A79" s="585"/>
-      <c r="B79" s="586"/>
-      <c r="C79" s="586"/>
-      <c r="D79" s="586"/>
-      <c r="E79" s="586"/>
-      <c r="F79" s="586"/>
-      <c r="G79" s="586"/>
-      <c r="H79" s="586"/>
-      <c r="I79" s="586"/>
-      <c r="J79" s="586"/>
-      <c r="K79" s="587"/>
-      <c r="L79" s="422"/>
-      <c r="M79" s="168"/>
-      <c r="N79" s="168"/>
-      <c r="O79" s="168"/>
-      <c r="P79" s="422"/>
-      <c r="Q79" s="168"/>
-      <c r="R79" s="168"/>
-      <c r="S79" s="168"/>
-      <c r="T79" s="422"/>
-      <c r="U79" s="168"/>
-      <c r="V79" s="168"/>
-      <c r="W79" s="168"/>
-      <c r="X79" s="422"/>
-      <c r="Y79" s="168"/>
-      <c r="Z79" s="168"/>
-      <c r="AA79" s="588"/>
-    </row>
-    <row r="80" spans="1:27" ht="24" customHeight="1">
-      <c r="A80" s="585"/>
-      <c r="B80" s="586"/>
-      <c r="C80" s="586"/>
-      <c r="D80" s="586"/>
-      <c r="E80" s="586"/>
-      <c r="F80" s="586"/>
-      <c r="G80" s="586"/>
-      <c r="H80" s="586"/>
-      <c r="I80" s="586"/>
-      <c r="J80" s="586"/>
-      <c r="K80" s="587"/>
-      <c r="L80" s="422"/>
-      <c r="M80" s="168"/>
-      <c r="N80" s="168"/>
-      <c r="O80" s="168"/>
-      <c r="P80" s="422"/>
-      <c r="Q80" s="168"/>
-      <c r="R80" s="168"/>
-      <c r="S80" s="168"/>
-      <c r="T80" s="422"/>
-      <c r="U80" s="168"/>
-      <c r="V80" s="168"/>
-      <c r="W80" s="168"/>
-      <c r="X80" s="422"/>
-      <c r="Y80" s="168"/>
-      <c r="Z80" s="168"/>
-      <c r="AA80" s="588"/>
-    </row>
-    <row r="81" spans="1:29" ht="24" customHeight="1">
-      <c r="A81" s="585"/>
-      <c r="B81" s="586"/>
-      <c r="C81" s="586"/>
-      <c r="D81" s="586"/>
-      <c r="E81" s="586"/>
-      <c r="F81" s="586"/>
-      <c r="G81" s="586"/>
-      <c r="H81" s="586"/>
-      <c r="I81" s="586"/>
-      <c r="J81" s="586"/>
-      <c r="K81" s="587"/>
-      <c r="L81" s="422"/>
-      <c r="M81" s="168"/>
-      <c r="N81" s="168"/>
-      <c r="O81" s="168"/>
-      <c r="P81" s="422"/>
-      <c r="Q81" s="168"/>
-      <c r="R81" s="168"/>
-      <c r="S81" s="168"/>
-      <c r="T81" s="422"/>
-      <c r="U81" s="168"/>
-      <c r="V81" s="168"/>
-      <c r="W81" s="168"/>
-      <c r="X81" s="422"/>
-      <c r="Y81" s="168"/>
-      <c r="Z81" s="168"/>
-      <c r="AA81" s="588"/>
-    </row>
-    <row r="82" spans="1:29" ht="12.75" customHeight="1">
-      <c r="A82" s="22"/>
-      <c r="AA82" s="19"/>
-    </row>
-    <row r="83" spans="1:29" ht="12.75" customHeight="1">
-      <c r="A83" s="22"/>
-      <c r="AA83" s="19"/>
-    </row>
-    <row r="84" spans="1:29" ht="12.75" customHeight="1">
-      <c r="A84" s="22"/>
-      <c r="AA84" s="19"/>
-    </row>
-    <row r="85" spans="1:29" ht="12.75" customHeight="1">
-      <c r="A85" s="22"/>
-      <c r="AA85" s="19"/>
-    </row>
-    <row r="86" spans="1:29" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A86" s="23"/>
-      <c r="B86" s="24"/>
-      <c r="C86" s="24"/>
-      <c r="D86" s="24"/>
-      <c r="E86" s="24"/>
-      <c r="F86" s="24"/>
-      <c r="G86" s="24"/>
-      <c r="H86" s="24"/>
-      <c r="I86" s="24"/>
-      <c r="J86" s="24"/>
-      <c r="K86" s="24"/>
-      <c r="L86" s="24"/>
-      <c r="M86" s="24"/>
-      <c r="N86" s="24"/>
-      <c r="O86" s="24"/>
-      <c r="P86" s="24"/>
-      <c r="Q86" s="24"/>
-      <c r="R86" s="24"/>
-      <c r="S86" s="24"/>
-      <c r="T86" s="24"/>
-      <c r="U86" s="24"/>
-      <c r="V86" s="24"/>
-      <c r="W86" s="24"/>
-      <c r="X86" s="24"/>
-      <c r="Y86" s="24"/>
-      <c r="Z86" s="24"/>
-      <c r="AA86" s="25"/>
-      <c r="AC86" s="2"/>
-    </row>
-    <row r="87" spans="1:29" ht="15.75" thickTop="1"/>
+    <row r="51" spans="1:29" ht="12.75" customHeight="1">
+      <c r="A51" s="22"/>
+      <c r="AA51" s="19"/>
+    </row>
+    <row r="52" spans="1:29" ht="12.75" customHeight="1">
+      <c r="A52" s="22"/>
+      <c r="AA52" s="19"/>
+    </row>
+    <row r="53" spans="1:29" ht="12.75" customHeight="1">
+      <c r="A53" s="22"/>
+      <c r="AA53" s="19"/>
+    </row>
+    <row r="54" spans="1:29" ht="12.75" customHeight="1">
+      <c r="A54" s="22"/>
+      <c r="AA54" s="19"/>
+    </row>
+    <row r="55" spans="1:29" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A55" s="23"/>
+      <c r="B55" s="24"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="24"/>
+      <c r="J55" s="24"/>
+      <c r="K55" s="24"/>
+      <c r="L55" s="24"/>
+      <c r="M55" s="24"/>
+      <c r="N55" s="24"/>
+      <c r="O55" s="24"/>
+      <c r="P55" s="24"/>
+      <c r="Q55" s="24"/>
+      <c r="R55" s="24"/>
+      <c r="S55" s="24"/>
+      <c r="T55" s="24"/>
+      <c r="U55" s="24"/>
+      <c r="V55" s="24"/>
+      <c r="W55" s="24"/>
+      <c r="X55" s="24"/>
+      <c r="Y55" s="24"/>
+      <c r="Z55" s="24"/>
+      <c r="AA55" s="25"/>
+      <c r="AC55" s="2"/>
+    </row>
+    <row r="56" spans="1:29" ht="15.75" thickTop="1"/>
   </sheetData>
   <customSheetViews>
     <customSheetView guid="{99F77AB9-FA43-4D4B-9896-F712C1493A3C}" scale="130" showPageBreaks="1" printArea="1" view="pageBreakPreview">
@@ -21948,124 +21064,15 @@
       <pageSetup paperSize="9" orientation="portrait" verticalDpi="200" r:id="rId2"/>
     </customSheetView>
   </customSheetViews>
-  <mergeCells count="387">
-    <mergeCell ref="P61:S61"/>
-    <mergeCell ref="T61:W61"/>
-    <mergeCell ref="X61:AA61"/>
-    <mergeCell ref="L62:O62"/>
-    <mergeCell ref="P62:S62"/>
-    <mergeCell ref="T62:W62"/>
-    <mergeCell ref="X62:AA62"/>
-    <mergeCell ref="P58:S58"/>
-    <mergeCell ref="T58:W58"/>
-    <mergeCell ref="X58:AA58"/>
-    <mergeCell ref="L59:O59"/>
-    <mergeCell ref="P59:S59"/>
-    <mergeCell ref="T59:W59"/>
-    <mergeCell ref="X59:AA59"/>
-    <mergeCell ref="L60:O60"/>
-    <mergeCell ref="P60:S60"/>
-    <mergeCell ref="T60:W60"/>
-    <mergeCell ref="X60:AA60"/>
-    <mergeCell ref="P55:S55"/>
-    <mergeCell ref="T55:W55"/>
-    <mergeCell ref="X55:AA55"/>
-    <mergeCell ref="L56:O56"/>
-    <mergeCell ref="P56:S56"/>
-    <mergeCell ref="T56:W56"/>
-    <mergeCell ref="X56:AA56"/>
-    <mergeCell ref="L57:O57"/>
-    <mergeCell ref="P57:S57"/>
-    <mergeCell ref="T57:W57"/>
-    <mergeCell ref="X57:AA57"/>
-    <mergeCell ref="P52:S52"/>
-    <mergeCell ref="T52:W52"/>
-    <mergeCell ref="X52:AA52"/>
-    <mergeCell ref="L53:O53"/>
-    <mergeCell ref="P53:S53"/>
-    <mergeCell ref="T53:W53"/>
-    <mergeCell ref="X53:AA53"/>
-    <mergeCell ref="L54:O54"/>
-    <mergeCell ref="P54:S54"/>
-    <mergeCell ref="T54:W54"/>
-    <mergeCell ref="X54:AA54"/>
-    <mergeCell ref="P49:S49"/>
-    <mergeCell ref="T49:W49"/>
-    <mergeCell ref="X49:AA49"/>
-    <mergeCell ref="L50:O50"/>
-    <mergeCell ref="P50:S50"/>
-    <mergeCell ref="T50:W50"/>
-    <mergeCell ref="X50:AA50"/>
-    <mergeCell ref="L51:O51"/>
-    <mergeCell ref="P51:S51"/>
-    <mergeCell ref="T51:W51"/>
-    <mergeCell ref="X51:AA51"/>
-    <mergeCell ref="P46:S46"/>
-    <mergeCell ref="T46:W46"/>
-    <mergeCell ref="X46:AA46"/>
-    <mergeCell ref="L47:O47"/>
-    <mergeCell ref="P47:S47"/>
-    <mergeCell ref="T47:W47"/>
-    <mergeCell ref="X47:AA47"/>
-    <mergeCell ref="L48:O48"/>
-    <mergeCell ref="P48:S48"/>
-    <mergeCell ref="T48:W48"/>
-    <mergeCell ref="X48:AA48"/>
-    <mergeCell ref="P43:S43"/>
-    <mergeCell ref="T43:W43"/>
-    <mergeCell ref="X43:AA43"/>
-    <mergeCell ref="L44:O44"/>
-    <mergeCell ref="P44:S44"/>
-    <mergeCell ref="T44:W44"/>
-    <mergeCell ref="X44:AA44"/>
-    <mergeCell ref="L45:O45"/>
-    <mergeCell ref="P45:S45"/>
-    <mergeCell ref="T45:W45"/>
-    <mergeCell ref="X45:AA45"/>
-    <mergeCell ref="P40:S40"/>
-    <mergeCell ref="T40:W40"/>
-    <mergeCell ref="X40:AA40"/>
-    <mergeCell ref="L41:O41"/>
-    <mergeCell ref="P41:S41"/>
-    <mergeCell ref="T41:W41"/>
-    <mergeCell ref="X41:AA41"/>
-    <mergeCell ref="L42:O42"/>
-    <mergeCell ref="P42:S42"/>
-    <mergeCell ref="T42:W42"/>
-    <mergeCell ref="X42:AA42"/>
-    <mergeCell ref="P37:S37"/>
-    <mergeCell ref="T37:W37"/>
-    <mergeCell ref="X37:AA37"/>
-    <mergeCell ref="L38:O38"/>
-    <mergeCell ref="P38:S38"/>
-    <mergeCell ref="T38:W38"/>
-    <mergeCell ref="X38:AA38"/>
-    <mergeCell ref="L39:O39"/>
-    <mergeCell ref="P39:S39"/>
-    <mergeCell ref="T39:W39"/>
-    <mergeCell ref="X39:AA39"/>
-    <mergeCell ref="P34:S34"/>
-    <mergeCell ref="T34:W34"/>
-    <mergeCell ref="X34:AA34"/>
-    <mergeCell ref="L35:O35"/>
-    <mergeCell ref="P35:S35"/>
-    <mergeCell ref="T35:W35"/>
-    <mergeCell ref="X35:AA35"/>
-    <mergeCell ref="L36:O36"/>
-    <mergeCell ref="P36:S36"/>
-    <mergeCell ref="T36:W36"/>
-    <mergeCell ref="X36:AA36"/>
+  <mergeCells count="232">
+    <mergeCell ref="P30:S30"/>
+    <mergeCell ref="T30:W30"/>
+    <mergeCell ref="X30:AA30"/>
+    <mergeCell ref="L31:O31"/>
     <mergeCell ref="P31:S31"/>
     <mergeCell ref="T31:W31"/>
     <mergeCell ref="X31:AA31"/>
-    <mergeCell ref="L32:O32"/>
-    <mergeCell ref="P32:S32"/>
-    <mergeCell ref="T32:W32"/>
-    <mergeCell ref="X32:AA32"/>
-    <mergeCell ref="L33:O33"/>
-    <mergeCell ref="P33:S33"/>
-    <mergeCell ref="T33:W33"/>
-    <mergeCell ref="X33:AA33"/>
+    <mergeCell ref="L28:O28"/>
     <mergeCell ref="P28:S28"/>
     <mergeCell ref="T28:W28"/>
     <mergeCell ref="X28:AA28"/>
@@ -22073,65 +21080,48 @@
     <mergeCell ref="P29:S29"/>
     <mergeCell ref="T29:W29"/>
     <mergeCell ref="X29:AA29"/>
+    <mergeCell ref="L26:O26"/>
+    <mergeCell ref="P26:S26"/>
+    <mergeCell ref="T26:W26"/>
+    <mergeCell ref="X26:AA26"/>
+    <mergeCell ref="L27:O27"/>
+    <mergeCell ref="P27:S27"/>
+    <mergeCell ref="T27:W27"/>
+    <mergeCell ref="X27:AA27"/>
+    <mergeCell ref="P25:S25"/>
+    <mergeCell ref="T25:W25"/>
+    <mergeCell ref="X25:AA25"/>
+    <mergeCell ref="L23:O23"/>
+    <mergeCell ref="P23:S23"/>
+    <mergeCell ref="T23:W23"/>
+    <mergeCell ref="X23:AA23"/>
+    <mergeCell ref="L24:O24"/>
+    <mergeCell ref="P24:S24"/>
+    <mergeCell ref="T24:W24"/>
+    <mergeCell ref="X24:AA24"/>
+    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="A31:K31"/>
+    <mergeCell ref="L25:O25"/>
     <mergeCell ref="L30:O30"/>
-    <mergeCell ref="P30:S30"/>
-    <mergeCell ref="T30:W30"/>
-    <mergeCell ref="X30:AA30"/>
-    <mergeCell ref="A55:K55"/>
-    <mergeCell ref="A56:K56"/>
-    <mergeCell ref="A57:K57"/>
-    <mergeCell ref="A58:K58"/>
-    <mergeCell ref="A59:K59"/>
-    <mergeCell ref="A60:K60"/>
-    <mergeCell ref="A61:K61"/>
-    <mergeCell ref="A62:K62"/>
-    <mergeCell ref="L28:O28"/>
-    <mergeCell ref="L31:O31"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="L36:O36"/>
+    <mergeCell ref="P36:S36"/>
+    <mergeCell ref="T36:W36"/>
+    <mergeCell ref="X36:AA36"/>
+    <mergeCell ref="A34:K34"/>
     <mergeCell ref="L34:O34"/>
-    <mergeCell ref="L37:O37"/>
-    <mergeCell ref="L40:O40"/>
-    <mergeCell ref="L43:O43"/>
-    <mergeCell ref="L46:O46"/>
-    <mergeCell ref="L49:O49"/>
-    <mergeCell ref="L52:O52"/>
-    <mergeCell ref="L55:O55"/>
-    <mergeCell ref="L58:O58"/>
-    <mergeCell ref="L61:O61"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="A47:K47"/>
-    <mergeCell ref="A48:K48"/>
-    <mergeCell ref="A49:K49"/>
+    <mergeCell ref="P34:S34"/>
+    <mergeCell ref="T34:W34"/>
+    <mergeCell ref="X34:AA34"/>
     <mergeCell ref="A35:K35"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="A50:K50"/>
-    <mergeCell ref="A51:K51"/>
-    <mergeCell ref="A52:K52"/>
-    <mergeCell ref="A53:K53"/>
-    <mergeCell ref="A54:K54"/>
-    <mergeCell ref="A37:K37"/>
-    <mergeCell ref="A38:K38"/>
-    <mergeCell ref="A39:K39"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="A41:K41"/>
-    <mergeCell ref="A42:K42"/>
-    <mergeCell ref="A43:K43"/>
-    <mergeCell ref="A44:K44"/>
-    <mergeCell ref="A45:K45"/>
-    <mergeCell ref="A67:K67"/>
-    <mergeCell ref="L67:O67"/>
-    <mergeCell ref="P67:S67"/>
-    <mergeCell ref="T67:W67"/>
-    <mergeCell ref="X67:AA67"/>
-    <mergeCell ref="A65:K65"/>
-    <mergeCell ref="L65:O65"/>
-    <mergeCell ref="P65:S65"/>
-    <mergeCell ref="T65:W65"/>
-    <mergeCell ref="X65:AA65"/>
-    <mergeCell ref="A66:K66"/>
-    <mergeCell ref="L66:O66"/>
-    <mergeCell ref="P66:S66"/>
-    <mergeCell ref="T66:W66"/>
-    <mergeCell ref="X66:AA66"/>
+    <mergeCell ref="L35:O35"/>
+    <mergeCell ref="P35:S35"/>
+    <mergeCell ref="T35:W35"/>
+    <mergeCell ref="X35:AA35"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="E4:AA4"/>
     <mergeCell ref="A5:K5"/>
@@ -22213,132 +21203,103 @@
     <mergeCell ref="A21:K21"/>
     <mergeCell ref="L21:O21"/>
     <mergeCell ref="P21:S21"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="L32:O32"/>
+    <mergeCell ref="P32:S32"/>
+    <mergeCell ref="T32:W32"/>
+    <mergeCell ref="X32:AA32"/>
     <mergeCell ref="A23:K23"/>
-    <mergeCell ref="L23:O23"/>
-    <mergeCell ref="P23:S23"/>
-    <mergeCell ref="T23:W23"/>
-    <mergeCell ref="X23:AA23"/>
     <mergeCell ref="A24:K24"/>
-    <mergeCell ref="L24:O24"/>
-    <mergeCell ref="P24:S24"/>
-    <mergeCell ref="T24:W24"/>
-    <mergeCell ref="X24:AA24"/>
-    <mergeCell ref="T27:W27"/>
-    <mergeCell ref="X27:AA27"/>
-    <mergeCell ref="A63:K63"/>
-    <mergeCell ref="L63:O63"/>
-    <mergeCell ref="P63:S63"/>
-    <mergeCell ref="T63:W63"/>
-    <mergeCell ref="X63:AA63"/>
     <mergeCell ref="A25:K25"/>
-    <mergeCell ref="L25:O25"/>
-    <mergeCell ref="P25:S25"/>
-    <mergeCell ref="T25:W25"/>
-    <mergeCell ref="X25:AA25"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="L26:O26"/>
-    <mergeCell ref="P26:S26"/>
-    <mergeCell ref="T26:W26"/>
-    <mergeCell ref="X26:AA26"/>
-    <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A29:K29"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="A31:K31"/>
-    <mergeCell ref="A32:K32"/>
-    <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A34:K34"/>
     <mergeCell ref="X16:AA16"/>
     <mergeCell ref="A17:K17"/>
     <mergeCell ref="L17:O17"/>
     <mergeCell ref="P17:S17"/>
     <mergeCell ref="T17:W17"/>
     <mergeCell ref="X17:AA17"/>
-    <mergeCell ref="A68:K68"/>
-    <mergeCell ref="L68:O68"/>
-    <mergeCell ref="P68:S68"/>
-    <mergeCell ref="T68:W68"/>
-    <mergeCell ref="X68:AA68"/>
-    <mergeCell ref="A64:K64"/>
-    <mergeCell ref="L64:O64"/>
-    <mergeCell ref="P64:S64"/>
-    <mergeCell ref="T64:W64"/>
-    <mergeCell ref="X64:AA64"/>
+    <mergeCell ref="A37:K37"/>
+    <mergeCell ref="L37:O37"/>
+    <mergeCell ref="P37:S37"/>
+    <mergeCell ref="T37:W37"/>
+    <mergeCell ref="X37:AA37"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="L33:O33"/>
+    <mergeCell ref="P33:S33"/>
+    <mergeCell ref="T33:W33"/>
+    <mergeCell ref="X33:AA33"/>
     <mergeCell ref="A18:K18"/>
     <mergeCell ref="L18:O18"/>
     <mergeCell ref="P18:S18"/>
     <mergeCell ref="T18:W18"/>
     <mergeCell ref="X18:AA18"/>
-    <mergeCell ref="A27:K27"/>
-    <mergeCell ref="L27:O27"/>
-    <mergeCell ref="P27:S27"/>
-    <mergeCell ref="A69:K69"/>
-    <mergeCell ref="L69:O69"/>
-    <mergeCell ref="P69:S69"/>
-    <mergeCell ref="T69:W69"/>
-    <mergeCell ref="X69:AA69"/>
-    <mergeCell ref="A70:K70"/>
-    <mergeCell ref="L70:O70"/>
-    <mergeCell ref="P70:S70"/>
-    <mergeCell ref="T70:W70"/>
-    <mergeCell ref="X70:AA70"/>
-    <mergeCell ref="A71:K71"/>
-    <mergeCell ref="L71:O71"/>
-    <mergeCell ref="P71:S71"/>
-    <mergeCell ref="T71:W71"/>
-    <mergeCell ref="X71:AA71"/>
-    <mergeCell ref="A72:K72"/>
-    <mergeCell ref="L72:O72"/>
-    <mergeCell ref="P72:S72"/>
-    <mergeCell ref="T72:W72"/>
-    <mergeCell ref="X72:AA72"/>
-    <mergeCell ref="A73:K73"/>
-    <mergeCell ref="L73:O73"/>
-    <mergeCell ref="P73:S73"/>
-    <mergeCell ref="T73:W73"/>
-    <mergeCell ref="X73:AA73"/>
-    <mergeCell ref="A74:K74"/>
-    <mergeCell ref="L74:O74"/>
-    <mergeCell ref="P74:S74"/>
-    <mergeCell ref="T74:W74"/>
-    <mergeCell ref="X74:AA74"/>
-    <mergeCell ref="A75:K75"/>
-    <mergeCell ref="L75:O75"/>
-    <mergeCell ref="P75:S75"/>
-    <mergeCell ref="T75:W75"/>
-    <mergeCell ref="X75:AA75"/>
-    <mergeCell ref="A76:K76"/>
-    <mergeCell ref="L76:O76"/>
-    <mergeCell ref="P76:S76"/>
-    <mergeCell ref="T76:W76"/>
-    <mergeCell ref="X76:AA76"/>
-    <mergeCell ref="A77:K77"/>
-    <mergeCell ref="L77:O77"/>
-    <mergeCell ref="P77:S77"/>
-    <mergeCell ref="T77:W77"/>
-    <mergeCell ref="X77:AA77"/>
-    <mergeCell ref="A78:K78"/>
-    <mergeCell ref="L78:O78"/>
-    <mergeCell ref="P78:S78"/>
-    <mergeCell ref="T78:W78"/>
-    <mergeCell ref="X78:AA78"/>
-    <mergeCell ref="A81:K81"/>
-    <mergeCell ref="L81:O81"/>
-    <mergeCell ref="P81:S81"/>
-    <mergeCell ref="T81:W81"/>
-    <mergeCell ref="X81:AA81"/>
-    <mergeCell ref="A79:K79"/>
-    <mergeCell ref="L79:O79"/>
-    <mergeCell ref="P79:S79"/>
-    <mergeCell ref="T79:W79"/>
-    <mergeCell ref="X79:AA79"/>
-    <mergeCell ref="A80:K80"/>
-    <mergeCell ref="L80:O80"/>
-    <mergeCell ref="P80:S80"/>
-    <mergeCell ref="T80:W80"/>
-    <mergeCell ref="X80:AA80"/>
+    <mergeCell ref="A38:K38"/>
+    <mergeCell ref="L38:O38"/>
+    <mergeCell ref="P38:S38"/>
+    <mergeCell ref="T38:W38"/>
+    <mergeCell ref="X38:AA38"/>
+    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="L39:O39"/>
+    <mergeCell ref="P39:S39"/>
+    <mergeCell ref="T39:W39"/>
+    <mergeCell ref="X39:AA39"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="L40:O40"/>
+    <mergeCell ref="P40:S40"/>
+    <mergeCell ref="T40:W40"/>
+    <mergeCell ref="X40:AA40"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="L41:O41"/>
+    <mergeCell ref="P41:S41"/>
+    <mergeCell ref="T41:W41"/>
+    <mergeCell ref="X41:AA41"/>
+    <mergeCell ref="A42:K42"/>
+    <mergeCell ref="L42:O42"/>
+    <mergeCell ref="P42:S42"/>
+    <mergeCell ref="T42:W42"/>
+    <mergeCell ref="X42:AA42"/>
+    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="L43:O43"/>
+    <mergeCell ref="P43:S43"/>
+    <mergeCell ref="T43:W43"/>
+    <mergeCell ref="X43:AA43"/>
+    <mergeCell ref="A44:K44"/>
+    <mergeCell ref="L44:O44"/>
+    <mergeCell ref="P44:S44"/>
+    <mergeCell ref="T44:W44"/>
+    <mergeCell ref="X44:AA44"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="L45:O45"/>
+    <mergeCell ref="P45:S45"/>
+    <mergeCell ref="T45:W45"/>
+    <mergeCell ref="X45:AA45"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="L46:O46"/>
+    <mergeCell ref="P46:S46"/>
+    <mergeCell ref="T46:W46"/>
+    <mergeCell ref="X46:AA46"/>
+    <mergeCell ref="A47:K47"/>
+    <mergeCell ref="L47:O47"/>
+    <mergeCell ref="P47:S47"/>
+    <mergeCell ref="T47:W47"/>
+    <mergeCell ref="X47:AA47"/>
+    <mergeCell ref="A50:K50"/>
+    <mergeCell ref="L50:O50"/>
+    <mergeCell ref="P50:S50"/>
+    <mergeCell ref="T50:W50"/>
+    <mergeCell ref="X50:AA50"/>
+    <mergeCell ref="A48:K48"/>
+    <mergeCell ref="L48:O48"/>
+    <mergeCell ref="P48:S48"/>
+    <mergeCell ref="T48:W48"/>
+    <mergeCell ref="X48:AA48"/>
+    <mergeCell ref="A49:K49"/>
+    <mergeCell ref="L49:O49"/>
+    <mergeCell ref="P49:S49"/>
+    <mergeCell ref="T49:W49"/>
+    <mergeCell ref="X49:AA49"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.36" top="0.4" bottom="0.28000000000000003" header="0.3" footer="0.24"/>
-  <pageSetup paperSize="9" scale="58" orientation="portrait" verticalDpi="200" r:id="rId3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="67" fitToHeight="0" orientation="portrait" verticalDpi="200" r:id="rId3"/>
   <drawing r:id="rId4"/>
 </worksheet>
 </file>
@@ -22374,555 +21335,555 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:64" ht="12.75" customHeight="1" thickTop="1">
-      <c r="A1" s="657"/>
-      <c r="B1" s="658"/>
-      <c r="C1" s="658"/>
-      <c r="D1" s="658"/>
-      <c r="E1" s="658"/>
-      <c r="F1" s="659"/>
-      <c r="G1" s="669">
+      <c r="A1" s="659"/>
+      <c r="B1" s="660"/>
+      <c r="C1" s="660"/>
+      <c r="D1" s="660"/>
+      <c r="E1" s="660"/>
+      <c r="F1" s="661"/>
+      <c r="G1" s="671">
         <f>Bilgiler!D1</f>
         <v>0</v>
       </c>
-      <c r="H1" s="670"/>
-      <c r="I1" s="670"/>
-      <c r="J1" s="670"/>
-      <c r="K1" s="670"/>
-      <c r="L1" s="670"/>
-      <c r="M1" s="670"/>
-      <c r="N1" s="670"/>
-      <c r="O1" s="670"/>
-      <c r="P1" s="670"/>
-      <c r="Q1" s="670"/>
-      <c r="R1" s="670"/>
-      <c r="S1" s="670"/>
-      <c r="T1" s="670"/>
-      <c r="U1" s="671"/>
-      <c r="V1" s="678">
+      <c r="H1" s="672"/>
+      <c r="I1" s="672"/>
+      <c r="J1" s="672"/>
+      <c r="K1" s="672"/>
+      <c r="L1" s="672"/>
+      <c r="M1" s="672"/>
+      <c r="N1" s="672"/>
+      <c r="O1" s="672"/>
+      <c r="P1" s="672"/>
+      <c r="Q1" s="672"/>
+      <c r="R1" s="672"/>
+      <c r="S1" s="672"/>
+      <c r="T1" s="672"/>
+      <c r="U1" s="673"/>
+      <c r="V1" s="680">
         <f>Bilgiler!D2</f>
         <v>0</v>
       </c>
-      <c r="W1" s="679"/>
-      <c r="X1" s="679"/>
-      <c r="Y1" s="679"/>
-      <c r="Z1" s="679"/>
-      <c r="AA1" s="679"/>
-      <c r="AB1" s="679"/>
-      <c r="AC1" s="679"/>
-      <c r="AD1" s="679"/>
-      <c r="AE1" s="679"/>
-      <c r="AF1" s="679"/>
-      <c r="AG1" s="679"/>
-      <c r="AH1" s="679"/>
-      <c r="AI1" s="679"/>
-      <c r="AJ1" s="679"/>
-      <c r="AK1" s="679"/>
-      <c r="AL1" s="679"/>
-      <c r="AM1" s="679"/>
-      <c r="AN1" s="679"/>
-      <c r="AO1" s="679"/>
-      <c r="AP1" s="679"/>
-      <c r="AQ1" s="679"/>
-      <c r="AR1" s="679"/>
-      <c r="AS1" s="679"/>
-      <c r="AT1" s="679"/>
-      <c r="AU1" s="679"/>
-      <c r="AV1" s="679"/>
-      <c r="AW1" s="679"/>
-      <c r="AX1" s="679"/>
-      <c r="AY1" s="679"/>
-      <c r="AZ1" s="679"/>
-      <c r="BA1" s="679"/>
-      <c r="BB1" s="679"/>
-      <c r="BC1" s="679"/>
-      <c r="BD1" s="679"/>
-      <c r="BE1" s="679"/>
-      <c r="BF1" s="679"/>
-      <c r="BG1" s="679"/>
-      <c r="BH1" s="679"/>
-      <c r="BI1" s="679"/>
-      <c r="BJ1" s="679"/>
-      <c r="BK1" s="679"/>
-      <c r="BL1" s="680"/>
+      <c r="W1" s="681"/>
+      <c r="X1" s="681"/>
+      <c r="Y1" s="681"/>
+      <c r="Z1" s="681"/>
+      <c r="AA1" s="681"/>
+      <c r="AB1" s="681"/>
+      <c r="AC1" s="681"/>
+      <c r="AD1" s="681"/>
+      <c r="AE1" s="681"/>
+      <c r="AF1" s="681"/>
+      <c r="AG1" s="681"/>
+      <c r="AH1" s="681"/>
+      <c r="AI1" s="681"/>
+      <c r="AJ1" s="681"/>
+      <c r="AK1" s="681"/>
+      <c r="AL1" s="681"/>
+      <c r="AM1" s="681"/>
+      <c r="AN1" s="681"/>
+      <c r="AO1" s="681"/>
+      <c r="AP1" s="681"/>
+      <c r="AQ1" s="681"/>
+      <c r="AR1" s="681"/>
+      <c r="AS1" s="681"/>
+      <c r="AT1" s="681"/>
+      <c r="AU1" s="681"/>
+      <c r="AV1" s="681"/>
+      <c r="AW1" s="681"/>
+      <c r="AX1" s="681"/>
+      <c r="AY1" s="681"/>
+      <c r="AZ1" s="681"/>
+      <c r="BA1" s="681"/>
+      <c r="BB1" s="681"/>
+      <c r="BC1" s="681"/>
+      <c r="BD1" s="681"/>
+      <c r="BE1" s="681"/>
+      <c r="BF1" s="681"/>
+      <c r="BG1" s="681"/>
+      <c r="BH1" s="681"/>
+      <c r="BI1" s="681"/>
+      <c r="BJ1" s="681"/>
+      <c r="BK1" s="681"/>
+      <c r="BL1" s="682"/>
     </row>
     <row r="2" spans="1:64" ht="12.75" customHeight="1">
-      <c r="A2" s="660"/>
-      <c r="B2" s="661"/>
-      <c r="C2" s="661"/>
-      <c r="D2" s="661"/>
-      <c r="E2" s="661"/>
-      <c r="F2" s="662"/>
-      <c r="G2" s="672"/>
-      <c r="H2" s="673"/>
-      <c r="I2" s="673"/>
-      <c r="J2" s="673"/>
-      <c r="K2" s="673"/>
-      <c r="L2" s="673"/>
-      <c r="M2" s="673"/>
-      <c r="N2" s="673"/>
-      <c r="O2" s="673"/>
-      <c r="P2" s="673"/>
-      <c r="Q2" s="673"/>
-      <c r="R2" s="673"/>
-      <c r="S2" s="673"/>
-      <c r="T2" s="673"/>
-      <c r="U2" s="674"/>
-      <c r="V2" s="681"/>
-      <c r="W2" s="682"/>
-      <c r="X2" s="682"/>
-      <c r="Y2" s="682"/>
-      <c r="Z2" s="682"/>
-      <c r="AA2" s="682"/>
-      <c r="AB2" s="682"/>
-      <c r="AC2" s="682"/>
-      <c r="AD2" s="682"/>
-      <c r="AE2" s="682"/>
-      <c r="AF2" s="682"/>
-      <c r="AG2" s="682"/>
-      <c r="AH2" s="682"/>
-      <c r="AI2" s="682"/>
-      <c r="AJ2" s="682"/>
-      <c r="AK2" s="682"/>
-      <c r="AL2" s="682"/>
-      <c r="AM2" s="682"/>
-      <c r="AN2" s="682"/>
-      <c r="AO2" s="682"/>
-      <c r="AP2" s="682"/>
-      <c r="AQ2" s="682"/>
-      <c r="AR2" s="682"/>
-      <c r="AS2" s="682"/>
-      <c r="AT2" s="682"/>
-      <c r="AU2" s="682"/>
-      <c r="AV2" s="682"/>
-      <c r="AW2" s="682"/>
-      <c r="AX2" s="682"/>
-      <c r="AY2" s="682"/>
-      <c r="AZ2" s="682"/>
-      <c r="BA2" s="682"/>
-      <c r="BB2" s="682"/>
-      <c r="BC2" s="682"/>
-      <c r="BD2" s="682"/>
-      <c r="BE2" s="682"/>
-      <c r="BF2" s="682"/>
-      <c r="BG2" s="682"/>
-      <c r="BH2" s="682"/>
-      <c r="BI2" s="682"/>
-      <c r="BJ2" s="682"/>
-      <c r="BK2" s="682"/>
-      <c r="BL2" s="683"/>
+      <c r="A2" s="662"/>
+      <c r="B2" s="663"/>
+      <c r="C2" s="663"/>
+      <c r="D2" s="663"/>
+      <c r="E2" s="663"/>
+      <c r="F2" s="664"/>
+      <c r="G2" s="674"/>
+      <c r="H2" s="675"/>
+      <c r="I2" s="675"/>
+      <c r="J2" s="675"/>
+      <c r="K2" s="675"/>
+      <c r="L2" s="675"/>
+      <c r="M2" s="675"/>
+      <c r="N2" s="675"/>
+      <c r="O2" s="675"/>
+      <c r="P2" s="675"/>
+      <c r="Q2" s="675"/>
+      <c r="R2" s="675"/>
+      <c r="S2" s="675"/>
+      <c r="T2" s="675"/>
+      <c r="U2" s="676"/>
+      <c r="V2" s="683"/>
+      <c r="W2" s="684"/>
+      <c r="X2" s="684"/>
+      <c r="Y2" s="684"/>
+      <c r="Z2" s="684"/>
+      <c r="AA2" s="684"/>
+      <c r="AB2" s="684"/>
+      <c r="AC2" s="684"/>
+      <c r="AD2" s="684"/>
+      <c r="AE2" s="684"/>
+      <c r="AF2" s="684"/>
+      <c r="AG2" s="684"/>
+      <c r="AH2" s="684"/>
+      <c r="AI2" s="684"/>
+      <c r="AJ2" s="684"/>
+      <c r="AK2" s="684"/>
+      <c r="AL2" s="684"/>
+      <c r="AM2" s="684"/>
+      <c r="AN2" s="684"/>
+      <c r="AO2" s="684"/>
+      <c r="AP2" s="684"/>
+      <c r="AQ2" s="684"/>
+      <c r="AR2" s="684"/>
+      <c r="AS2" s="684"/>
+      <c r="AT2" s="684"/>
+      <c r="AU2" s="684"/>
+      <c r="AV2" s="684"/>
+      <c r="AW2" s="684"/>
+      <c r="AX2" s="684"/>
+      <c r="AY2" s="684"/>
+      <c r="AZ2" s="684"/>
+      <c r="BA2" s="684"/>
+      <c r="BB2" s="684"/>
+      <c r="BC2" s="684"/>
+      <c r="BD2" s="684"/>
+      <c r="BE2" s="684"/>
+      <c r="BF2" s="684"/>
+      <c r="BG2" s="684"/>
+      <c r="BH2" s="684"/>
+      <c r="BI2" s="684"/>
+      <c r="BJ2" s="684"/>
+      <c r="BK2" s="684"/>
+      <c r="BL2" s="685"/>
     </row>
     <row r="3" spans="1:64" ht="12.75" customHeight="1">
-      <c r="A3" s="660"/>
-      <c r="B3" s="661"/>
-      <c r="C3" s="661"/>
-      <c r="D3" s="661"/>
-      <c r="E3" s="661"/>
-      <c r="F3" s="662"/>
-      <c r="G3" s="672"/>
-      <c r="H3" s="673"/>
-      <c r="I3" s="673"/>
-      <c r="J3" s="673"/>
-      <c r="K3" s="673"/>
-      <c r="L3" s="673"/>
-      <c r="M3" s="673"/>
-      <c r="N3" s="673"/>
-      <c r="O3" s="673"/>
-      <c r="P3" s="673"/>
-      <c r="Q3" s="673"/>
-      <c r="R3" s="673"/>
-      <c r="S3" s="673"/>
-      <c r="T3" s="673"/>
-      <c r="U3" s="674"/>
-      <c r="V3" s="681"/>
-      <c r="W3" s="682"/>
-      <c r="X3" s="682"/>
-      <c r="Y3" s="682"/>
-      <c r="Z3" s="682"/>
-      <c r="AA3" s="682"/>
-      <c r="AB3" s="682"/>
-      <c r="AC3" s="682"/>
-      <c r="AD3" s="682"/>
-      <c r="AE3" s="682"/>
-      <c r="AF3" s="682"/>
-      <c r="AG3" s="682"/>
-      <c r="AH3" s="682"/>
-      <c r="AI3" s="682"/>
-      <c r="AJ3" s="682"/>
-      <c r="AK3" s="682"/>
-      <c r="AL3" s="682"/>
-      <c r="AM3" s="682"/>
-      <c r="AN3" s="682"/>
-      <c r="AO3" s="682"/>
-      <c r="AP3" s="682"/>
-      <c r="AQ3" s="682"/>
-      <c r="AR3" s="682"/>
-      <c r="AS3" s="682"/>
-      <c r="AT3" s="682"/>
-      <c r="AU3" s="682"/>
-      <c r="AV3" s="682"/>
-      <c r="AW3" s="682"/>
-      <c r="AX3" s="682"/>
-      <c r="AY3" s="682"/>
-      <c r="AZ3" s="682"/>
-      <c r="BA3" s="682"/>
-      <c r="BB3" s="682"/>
-      <c r="BC3" s="682"/>
-      <c r="BD3" s="682"/>
-      <c r="BE3" s="682"/>
-      <c r="BF3" s="682"/>
-      <c r="BG3" s="682"/>
-      <c r="BH3" s="682"/>
-      <c r="BI3" s="682"/>
-      <c r="BJ3" s="682"/>
-      <c r="BK3" s="682"/>
-      <c r="BL3" s="683"/>
+      <c r="A3" s="662"/>
+      <c r="B3" s="663"/>
+      <c r="C3" s="663"/>
+      <c r="D3" s="663"/>
+      <c r="E3" s="663"/>
+      <c r="F3" s="664"/>
+      <c r="G3" s="674"/>
+      <c r="H3" s="675"/>
+      <c r="I3" s="675"/>
+      <c r="J3" s="675"/>
+      <c r="K3" s="675"/>
+      <c r="L3" s="675"/>
+      <c r="M3" s="675"/>
+      <c r="N3" s="675"/>
+      <c r="O3" s="675"/>
+      <c r="P3" s="675"/>
+      <c r="Q3" s="675"/>
+      <c r="R3" s="675"/>
+      <c r="S3" s="675"/>
+      <c r="T3" s="675"/>
+      <c r="U3" s="676"/>
+      <c r="V3" s="683"/>
+      <c r="W3" s="684"/>
+      <c r="X3" s="684"/>
+      <c r="Y3" s="684"/>
+      <c r="Z3" s="684"/>
+      <c r="AA3" s="684"/>
+      <c r="AB3" s="684"/>
+      <c r="AC3" s="684"/>
+      <c r="AD3" s="684"/>
+      <c r="AE3" s="684"/>
+      <c r="AF3" s="684"/>
+      <c r="AG3" s="684"/>
+      <c r="AH3" s="684"/>
+      <c r="AI3" s="684"/>
+      <c r="AJ3" s="684"/>
+      <c r="AK3" s="684"/>
+      <c r="AL3" s="684"/>
+      <c r="AM3" s="684"/>
+      <c r="AN3" s="684"/>
+      <c r="AO3" s="684"/>
+      <c r="AP3" s="684"/>
+      <c r="AQ3" s="684"/>
+      <c r="AR3" s="684"/>
+      <c r="AS3" s="684"/>
+      <c r="AT3" s="684"/>
+      <c r="AU3" s="684"/>
+      <c r="AV3" s="684"/>
+      <c r="AW3" s="684"/>
+      <c r="AX3" s="684"/>
+      <c r="AY3" s="684"/>
+      <c r="AZ3" s="684"/>
+      <c r="BA3" s="684"/>
+      <c r="BB3" s="684"/>
+      <c r="BC3" s="684"/>
+      <c r="BD3" s="684"/>
+      <c r="BE3" s="684"/>
+      <c r="BF3" s="684"/>
+      <c r="BG3" s="684"/>
+      <c r="BH3" s="684"/>
+      <c r="BI3" s="684"/>
+      <c r="BJ3" s="684"/>
+      <c r="BK3" s="684"/>
+      <c r="BL3" s="685"/>
     </row>
     <row r="4" spans="1:64" ht="12.75" customHeight="1">
-      <c r="A4" s="660"/>
-      <c r="B4" s="661"/>
-      <c r="C4" s="661"/>
-      <c r="D4" s="661"/>
-      <c r="E4" s="661"/>
-      <c r="F4" s="662"/>
-      <c r="G4" s="672"/>
-      <c r="H4" s="673"/>
-      <c r="I4" s="673"/>
-      <c r="J4" s="673"/>
-      <c r="K4" s="673"/>
-      <c r="L4" s="673"/>
-      <c r="M4" s="673"/>
-      <c r="N4" s="673"/>
-      <c r="O4" s="673"/>
-      <c r="P4" s="673"/>
-      <c r="Q4" s="673"/>
-      <c r="R4" s="673"/>
-      <c r="S4" s="673"/>
-      <c r="T4" s="673"/>
-      <c r="U4" s="674"/>
-      <c r="V4" s="681">
+      <c r="A4" s="662"/>
+      <c r="B4" s="663"/>
+      <c r="C4" s="663"/>
+      <c r="D4" s="663"/>
+      <c r="E4" s="663"/>
+      <c r="F4" s="664"/>
+      <c r="G4" s="674"/>
+      <c r="H4" s="675"/>
+      <c r="I4" s="675"/>
+      <c r="J4" s="675"/>
+      <c r="K4" s="675"/>
+      <c r="L4" s="675"/>
+      <c r="M4" s="675"/>
+      <c r="N4" s="675"/>
+      <c r="O4" s="675"/>
+      <c r="P4" s="675"/>
+      <c r="Q4" s="675"/>
+      <c r="R4" s="675"/>
+      <c r="S4" s="675"/>
+      <c r="T4" s="675"/>
+      <c r="U4" s="676"/>
+      <c r="V4" s="683">
         <f>Bilgiler!D3</f>
         <v>0</v>
       </c>
-      <c r="W4" s="682"/>
-      <c r="X4" s="682"/>
-      <c r="Y4" s="682"/>
-      <c r="Z4" s="682"/>
-      <c r="AA4" s="682"/>
-      <c r="AB4" s="682"/>
-      <c r="AC4" s="682"/>
-      <c r="AD4" s="682"/>
-      <c r="AE4" s="682"/>
-      <c r="AF4" s="682"/>
-      <c r="AG4" s="682"/>
-      <c r="AH4" s="682"/>
-      <c r="AI4" s="682"/>
-      <c r="AJ4" s="682"/>
-      <c r="AK4" s="682"/>
-      <c r="AL4" s="682"/>
-      <c r="AM4" s="682"/>
-      <c r="AN4" s="682"/>
-      <c r="AO4" s="682"/>
-      <c r="AP4" s="682"/>
-      <c r="AQ4" s="682"/>
-      <c r="AR4" s="682"/>
-      <c r="AS4" s="682"/>
-      <c r="AT4" s="682"/>
-      <c r="AU4" s="682"/>
-      <c r="AV4" s="682"/>
-      <c r="AW4" s="682"/>
-      <c r="AX4" s="682"/>
-      <c r="AY4" s="682"/>
-      <c r="AZ4" s="682"/>
-      <c r="BA4" s="682"/>
-      <c r="BB4" s="682"/>
-      <c r="BC4" s="682"/>
-      <c r="BD4" s="682"/>
-      <c r="BE4" s="682"/>
-      <c r="BF4" s="682"/>
-      <c r="BG4" s="682"/>
-      <c r="BH4" s="682"/>
-      <c r="BI4" s="682"/>
-      <c r="BJ4" s="682"/>
-      <c r="BK4" s="682"/>
-      <c r="BL4" s="683"/>
+      <c r="W4" s="684"/>
+      <c r="X4" s="684"/>
+      <c r="Y4" s="684"/>
+      <c r="Z4" s="684"/>
+      <c r="AA4" s="684"/>
+      <c r="AB4" s="684"/>
+      <c r="AC4" s="684"/>
+      <c r="AD4" s="684"/>
+      <c r="AE4" s="684"/>
+      <c r="AF4" s="684"/>
+      <c r="AG4" s="684"/>
+      <c r="AH4" s="684"/>
+      <c r="AI4" s="684"/>
+      <c r="AJ4" s="684"/>
+      <c r="AK4" s="684"/>
+      <c r="AL4" s="684"/>
+      <c r="AM4" s="684"/>
+      <c r="AN4" s="684"/>
+      <c r="AO4" s="684"/>
+      <c r="AP4" s="684"/>
+      <c r="AQ4" s="684"/>
+      <c r="AR4" s="684"/>
+      <c r="AS4" s="684"/>
+      <c r="AT4" s="684"/>
+      <c r="AU4" s="684"/>
+      <c r="AV4" s="684"/>
+      <c r="AW4" s="684"/>
+      <c r="AX4" s="684"/>
+      <c r="AY4" s="684"/>
+      <c r="AZ4" s="684"/>
+      <c r="BA4" s="684"/>
+      <c r="BB4" s="684"/>
+      <c r="BC4" s="684"/>
+      <c r="BD4" s="684"/>
+      <c r="BE4" s="684"/>
+      <c r="BF4" s="684"/>
+      <c r="BG4" s="684"/>
+      <c r="BH4" s="684"/>
+      <c r="BI4" s="684"/>
+      <c r="BJ4" s="684"/>
+      <c r="BK4" s="684"/>
+      <c r="BL4" s="685"/>
     </row>
     <row r="5" spans="1:64" ht="12.75" customHeight="1">
-      <c r="A5" s="660"/>
-      <c r="B5" s="661"/>
-      <c r="C5" s="661"/>
-      <c r="D5" s="661"/>
-      <c r="E5" s="661"/>
-      <c r="F5" s="662"/>
-      <c r="G5" s="672"/>
-      <c r="H5" s="673"/>
-      <c r="I5" s="673"/>
-      <c r="J5" s="673"/>
-      <c r="K5" s="673"/>
-      <c r="L5" s="673"/>
-      <c r="M5" s="673"/>
-      <c r="N5" s="673"/>
-      <c r="O5" s="673"/>
-      <c r="P5" s="673"/>
-      <c r="Q5" s="673"/>
-      <c r="R5" s="673"/>
-      <c r="S5" s="673"/>
-      <c r="T5" s="673"/>
-      <c r="U5" s="674"/>
-      <c r="V5" s="681"/>
-      <c r="W5" s="682"/>
-      <c r="X5" s="682"/>
-      <c r="Y5" s="682"/>
-      <c r="Z5" s="682"/>
-      <c r="AA5" s="682"/>
-      <c r="AB5" s="682"/>
-      <c r="AC5" s="682"/>
-      <c r="AD5" s="682"/>
-      <c r="AE5" s="682"/>
-      <c r="AF5" s="682"/>
-      <c r="AG5" s="682"/>
-      <c r="AH5" s="682"/>
-      <c r="AI5" s="682"/>
-      <c r="AJ5" s="682"/>
-      <c r="AK5" s="682"/>
-      <c r="AL5" s="682"/>
-      <c r="AM5" s="682"/>
-      <c r="AN5" s="682"/>
-      <c r="AO5" s="682"/>
-      <c r="AP5" s="682"/>
-      <c r="AQ5" s="682"/>
-      <c r="AR5" s="682"/>
-      <c r="AS5" s="682"/>
-      <c r="AT5" s="682"/>
-      <c r="AU5" s="682"/>
-      <c r="AV5" s="682"/>
-      <c r="AW5" s="682"/>
-      <c r="AX5" s="682"/>
-      <c r="AY5" s="682"/>
-      <c r="AZ5" s="682"/>
-      <c r="BA5" s="682"/>
-      <c r="BB5" s="682"/>
-      <c r="BC5" s="682"/>
-      <c r="BD5" s="682"/>
-      <c r="BE5" s="682"/>
-      <c r="BF5" s="682"/>
-      <c r="BG5" s="682"/>
-      <c r="BH5" s="682"/>
-      <c r="BI5" s="682"/>
-      <c r="BJ5" s="682"/>
-      <c r="BK5" s="682"/>
-      <c r="BL5" s="683"/>
+      <c r="A5" s="662"/>
+      <c r="B5" s="663"/>
+      <c r="C5" s="663"/>
+      <c r="D5" s="663"/>
+      <c r="E5" s="663"/>
+      <c r="F5" s="664"/>
+      <c r="G5" s="674"/>
+      <c r="H5" s="675"/>
+      <c r="I5" s="675"/>
+      <c r="J5" s="675"/>
+      <c r="K5" s="675"/>
+      <c r="L5" s="675"/>
+      <c r="M5" s="675"/>
+      <c r="N5" s="675"/>
+      <c r="O5" s="675"/>
+      <c r="P5" s="675"/>
+      <c r="Q5" s="675"/>
+      <c r="R5" s="675"/>
+      <c r="S5" s="675"/>
+      <c r="T5" s="675"/>
+      <c r="U5" s="676"/>
+      <c r="V5" s="683"/>
+      <c r="W5" s="684"/>
+      <c r="X5" s="684"/>
+      <c r="Y5" s="684"/>
+      <c r="Z5" s="684"/>
+      <c r="AA5" s="684"/>
+      <c r="AB5" s="684"/>
+      <c r="AC5" s="684"/>
+      <c r="AD5" s="684"/>
+      <c r="AE5" s="684"/>
+      <c r="AF5" s="684"/>
+      <c r="AG5" s="684"/>
+      <c r="AH5" s="684"/>
+      <c r="AI5" s="684"/>
+      <c r="AJ5" s="684"/>
+      <c r="AK5" s="684"/>
+      <c r="AL5" s="684"/>
+      <c r="AM5" s="684"/>
+      <c r="AN5" s="684"/>
+      <c r="AO5" s="684"/>
+      <c r="AP5" s="684"/>
+      <c r="AQ5" s="684"/>
+      <c r="AR5" s="684"/>
+      <c r="AS5" s="684"/>
+      <c r="AT5" s="684"/>
+      <c r="AU5" s="684"/>
+      <c r="AV5" s="684"/>
+      <c r="AW5" s="684"/>
+      <c r="AX5" s="684"/>
+      <c r="AY5" s="684"/>
+      <c r="AZ5" s="684"/>
+      <c r="BA5" s="684"/>
+      <c r="BB5" s="684"/>
+      <c r="BC5" s="684"/>
+      <c r="BD5" s="684"/>
+      <c r="BE5" s="684"/>
+      <c r="BF5" s="684"/>
+      <c r="BG5" s="684"/>
+      <c r="BH5" s="684"/>
+      <c r="BI5" s="684"/>
+      <c r="BJ5" s="684"/>
+      <c r="BK5" s="684"/>
+      <c r="BL5" s="685"/>
     </row>
     <row r="6" spans="1:64" ht="12.75" customHeight="1">
-      <c r="A6" s="660"/>
-      <c r="B6" s="661"/>
-      <c r="C6" s="661"/>
-      <c r="D6" s="661"/>
-      <c r="E6" s="661"/>
-      <c r="F6" s="662"/>
-      <c r="G6" s="672"/>
-      <c r="H6" s="673"/>
-      <c r="I6" s="673"/>
-      <c r="J6" s="673"/>
-      <c r="K6" s="673"/>
-      <c r="L6" s="673"/>
-      <c r="M6" s="673"/>
-      <c r="N6" s="673"/>
-      <c r="O6" s="673"/>
-      <c r="P6" s="673"/>
-      <c r="Q6" s="673"/>
-      <c r="R6" s="673"/>
-      <c r="S6" s="673"/>
-      <c r="T6" s="673"/>
-      <c r="U6" s="674"/>
-      <c r="V6" s="684"/>
-      <c r="W6" s="685"/>
-      <c r="X6" s="685"/>
-      <c r="Y6" s="685"/>
-      <c r="Z6" s="685"/>
-      <c r="AA6" s="685"/>
-      <c r="AB6" s="685"/>
-      <c r="AC6" s="685"/>
-      <c r="AD6" s="685"/>
-      <c r="AE6" s="685"/>
-      <c r="AF6" s="685"/>
-      <c r="AG6" s="685"/>
-      <c r="AH6" s="685"/>
-      <c r="AI6" s="685"/>
-      <c r="AJ6" s="685"/>
-      <c r="AK6" s="685"/>
-      <c r="AL6" s="685"/>
-      <c r="AM6" s="685"/>
-      <c r="AN6" s="685"/>
-      <c r="AO6" s="685"/>
-      <c r="AP6" s="685"/>
-      <c r="AQ6" s="685"/>
-      <c r="AR6" s="685"/>
-      <c r="AS6" s="685"/>
-      <c r="AT6" s="685"/>
-      <c r="AU6" s="685"/>
-      <c r="AV6" s="685"/>
-      <c r="AW6" s="685"/>
-      <c r="AX6" s="685"/>
-      <c r="AY6" s="685"/>
-      <c r="AZ6" s="685"/>
-      <c r="BA6" s="685"/>
-      <c r="BB6" s="685"/>
-      <c r="BC6" s="685"/>
-      <c r="BD6" s="685"/>
-      <c r="BE6" s="685"/>
-      <c r="BF6" s="685"/>
-      <c r="BG6" s="685"/>
-      <c r="BH6" s="685"/>
-      <c r="BI6" s="685"/>
-      <c r="BJ6" s="685"/>
-      <c r="BK6" s="685"/>
-      <c r="BL6" s="686"/>
+      <c r="A6" s="662"/>
+      <c r="B6" s="663"/>
+      <c r="C6" s="663"/>
+      <c r="D6" s="663"/>
+      <c r="E6" s="663"/>
+      <c r="F6" s="664"/>
+      <c r="G6" s="674"/>
+      <c r="H6" s="675"/>
+      <c r="I6" s="675"/>
+      <c r="J6" s="675"/>
+      <c r="K6" s="675"/>
+      <c r="L6" s="675"/>
+      <c r="M6" s="675"/>
+      <c r="N6" s="675"/>
+      <c r="O6" s="675"/>
+      <c r="P6" s="675"/>
+      <c r="Q6" s="675"/>
+      <c r="R6" s="675"/>
+      <c r="S6" s="675"/>
+      <c r="T6" s="675"/>
+      <c r="U6" s="676"/>
+      <c r="V6" s="686"/>
+      <c r="W6" s="687"/>
+      <c r="X6" s="687"/>
+      <c r="Y6" s="687"/>
+      <c r="Z6" s="687"/>
+      <c r="AA6" s="687"/>
+      <c r="AB6" s="687"/>
+      <c r="AC6" s="687"/>
+      <c r="AD6" s="687"/>
+      <c r="AE6" s="687"/>
+      <c r="AF6" s="687"/>
+      <c r="AG6" s="687"/>
+      <c r="AH6" s="687"/>
+      <c r="AI6" s="687"/>
+      <c r="AJ6" s="687"/>
+      <c r="AK6" s="687"/>
+      <c r="AL6" s="687"/>
+      <c r="AM6" s="687"/>
+      <c r="AN6" s="687"/>
+      <c r="AO6" s="687"/>
+      <c r="AP6" s="687"/>
+      <c r="AQ6" s="687"/>
+      <c r="AR6" s="687"/>
+      <c r="AS6" s="687"/>
+      <c r="AT6" s="687"/>
+      <c r="AU6" s="687"/>
+      <c r="AV6" s="687"/>
+      <c r="AW6" s="687"/>
+      <c r="AX6" s="687"/>
+      <c r="AY6" s="687"/>
+      <c r="AZ6" s="687"/>
+      <c r="BA6" s="687"/>
+      <c r="BB6" s="687"/>
+      <c r="BC6" s="687"/>
+      <c r="BD6" s="687"/>
+      <c r="BE6" s="687"/>
+      <c r="BF6" s="687"/>
+      <c r="BG6" s="687"/>
+      <c r="BH6" s="687"/>
+      <c r="BI6" s="687"/>
+      <c r="BJ6" s="687"/>
+      <c r="BK6" s="687"/>
+      <c r="BL6" s="688"/>
     </row>
     <row r="7" spans="1:64" ht="12.75" customHeight="1">
-      <c r="A7" s="660"/>
-      <c r="B7" s="661"/>
-      <c r="C7" s="661"/>
-      <c r="D7" s="661"/>
-      <c r="E7" s="661"/>
-      <c r="F7" s="662"/>
-      <c r="G7" s="672"/>
-      <c r="H7" s="673"/>
-      <c r="I7" s="673"/>
-      <c r="J7" s="673"/>
-      <c r="K7" s="673"/>
-      <c r="L7" s="673"/>
-      <c r="M7" s="673"/>
-      <c r="N7" s="673"/>
-      <c r="O7" s="673"/>
-      <c r="P7" s="673"/>
-      <c r="Q7" s="673"/>
-      <c r="R7" s="673"/>
-      <c r="S7" s="673"/>
-      <c r="T7" s="673"/>
-      <c r="U7" s="674"/>
-      <c r="V7" s="643" t="s">
+      <c r="A7" s="662"/>
+      <c r="B7" s="663"/>
+      <c r="C7" s="663"/>
+      <c r="D7" s="663"/>
+      <c r="E7" s="663"/>
+      <c r="F7" s="664"/>
+      <c r="G7" s="674"/>
+      <c r="H7" s="675"/>
+      <c r="I7" s="675"/>
+      <c r="J7" s="675"/>
+      <c r="K7" s="675"/>
+      <c r="L7" s="675"/>
+      <c r="M7" s="675"/>
+      <c r="N7" s="675"/>
+      <c r="O7" s="675"/>
+      <c r="P7" s="675"/>
+      <c r="Q7" s="675"/>
+      <c r="R7" s="675"/>
+      <c r="S7" s="675"/>
+      <c r="T7" s="675"/>
+      <c r="U7" s="676"/>
+      <c r="V7" s="645" t="s">
         <v>108</v>
       </c>
-      <c r="W7" s="644"/>
-      <c r="X7" s="644"/>
-      <c r="Y7" s="644"/>
-      <c r="Z7" s="644"/>
-      <c r="AA7" s="644"/>
-      <c r="AB7" s="644"/>
-      <c r="AC7" s="644"/>
-      <c r="AD7" s="644"/>
-      <c r="AE7" s="644"/>
-      <c r="AF7" s="644"/>
-      <c r="AG7" s="644"/>
-      <c r="AH7" s="644"/>
-      <c r="AI7" s="644"/>
-      <c r="AJ7" s="644"/>
-      <c r="AK7" s="644"/>
-      <c r="AL7" s="644"/>
-      <c r="AM7" s="644"/>
-      <c r="AN7" s="644"/>
-      <c r="AO7" s="644"/>
-      <c r="AP7" s="644"/>
-      <c r="AQ7" s="644"/>
-      <c r="AR7" s="644"/>
-      <c r="AS7" s="644"/>
-      <c r="AT7" s="644"/>
-      <c r="AU7" s="644"/>
-      <c r="AV7" s="644"/>
-      <c r="AW7" s="644"/>
-      <c r="AX7" s="645"/>
-      <c r="AY7" s="649" t="s">
+      <c r="W7" s="646"/>
+      <c r="X7" s="646"/>
+      <c r="Y7" s="646"/>
+      <c r="Z7" s="646"/>
+      <c r="AA7" s="646"/>
+      <c r="AB7" s="646"/>
+      <c r="AC7" s="646"/>
+      <c r="AD7" s="646"/>
+      <c r="AE7" s="646"/>
+      <c r="AF7" s="646"/>
+      <c r="AG7" s="646"/>
+      <c r="AH7" s="646"/>
+      <c r="AI7" s="646"/>
+      <c r="AJ7" s="646"/>
+      <c r="AK7" s="646"/>
+      <c r="AL7" s="646"/>
+      <c r="AM7" s="646"/>
+      <c r="AN7" s="646"/>
+      <c r="AO7" s="646"/>
+      <c r="AP7" s="646"/>
+      <c r="AQ7" s="646"/>
+      <c r="AR7" s="646"/>
+      <c r="AS7" s="646"/>
+      <c r="AT7" s="646"/>
+      <c r="AU7" s="646"/>
+      <c r="AV7" s="646"/>
+      <c r="AW7" s="646"/>
+      <c r="AX7" s="647"/>
+      <c r="AY7" s="651" t="s">
         <v>8</v>
       </c>
-      <c r="AZ7" s="649"/>
-      <c r="BA7" s="649"/>
-      <c r="BB7" s="649"/>
-      <c r="BC7" s="649"/>
-      <c r="BD7" s="649"/>
-      <c r="BE7" s="649"/>
-      <c r="BF7" s="650">
+      <c r="AZ7" s="651"/>
+      <c r="BA7" s="651"/>
+      <c r="BB7" s="651"/>
+      <c r="BC7" s="651"/>
+      <c r="BD7" s="651"/>
+      <c r="BE7" s="651"/>
+      <c r="BF7" s="652">
         <f>Bilgiler!D12</f>
         <v>0</v>
       </c>
-      <c r="BG7" s="650"/>
-      <c r="BH7" s="650"/>
-      <c r="BI7" s="650"/>
-      <c r="BJ7" s="650"/>
-      <c r="BK7" s="650"/>
-      <c r="BL7" s="651"/>
+      <c r="BG7" s="652"/>
+      <c r="BH7" s="652"/>
+      <c r="BI7" s="652"/>
+      <c r="BJ7" s="652"/>
+      <c r="BK7" s="652"/>
+      <c r="BL7" s="653"/>
     </row>
     <row r="8" spans="1:64" ht="12.75" customHeight="1">
-      <c r="A8" s="663"/>
-      <c r="B8" s="664"/>
-      <c r="C8" s="664"/>
-      <c r="D8" s="664"/>
-      <c r="E8" s="664"/>
-      <c r="F8" s="665"/>
-      <c r="G8" s="675"/>
-      <c r="H8" s="676"/>
-      <c r="I8" s="676"/>
-      <c r="J8" s="676"/>
-      <c r="K8" s="676"/>
-      <c r="L8" s="676"/>
-      <c r="M8" s="676"/>
-      <c r="N8" s="676"/>
-      <c r="O8" s="676"/>
-      <c r="P8" s="676"/>
-      <c r="Q8" s="676"/>
-      <c r="R8" s="676"/>
-      <c r="S8" s="676"/>
-      <c r="T8" s="676"/>
-      <c r="U8" s="677"/>
-      <c r="V8" s="646"/>
-      <c r="W8" s="647"/>
-      <c r="X8" s="647"/>
-      <c r="Y8" s="647"/>
-      <c r="Z8" s="647"/>
-      <c r="AA8" s="647"/>
-      <c r="AB8" s="647"/>
-      <c r="AC8" s="647"/>
-      <c r="AD8" s="647"/>
-      <c r="AE8" s="647"/>
-      <c r="AF8" s="647"/>
-      <c r="AG8" s="647"/>
-      <c r="AH8" s="647"/>
-      <c r="AI8" s="647"/>
-      <c r="AJ8" s="647"/>
-      <c r="AK8" s="647"/>
-      <c r="AL8" s="647"/>
-      <c r="AM8" s="647"/>
-      <c r="AN8" s="647"/>
-      <c r="AO8" s="647"/>
-      <c r="AP8" s="647"/>
-      <c r="AQ8" s="647"/>
-      <c r="AR8" s="647"/>
-      <c r="AS8" s="647"/>
-      <c r="AT8" s="647"/>
-      <c r="AU8" s="647"/>
-      <c r="AV8" s="647"/>
-      <c r="AW8" s="647"/>
-      <c r="AX8" s="648"/>
-      <c r="AY8" s="649" t="s">
+      <c r="A8" s="665"/>
+      <c r="B8" s="666"/>
+      <c r="C8" s="666"/>
+      <c r="D8" s="666"/>
+      <c r="E8" s="666"/>
+      <c r="F8" s="667"/>
+      <c r="G8" s="677"/>
+      <c r="H8" s="678"/>
+      <c r="I8" s="678"/>
+      <c r="J8" s="678"/>
+      <c r="K8" s="678"/>
+      <c r="L8" s="678"/>
+      <c r="M8" s="678"/>
+      <c r="N8" s="678"/>
+      <c r="O8" s="678"/>
+      <c r="P8" s="678"/>
+      <c r="Q8" s="678"/>
+      <c r="R8" s="678"/>
+      <c r="S8" s="678"/>
+      <c r="T8" s="678"/>
+      <c r="U8" s="679"/>
+      <c r="V8" s="648"/>
+      <c r="W8" s="649"/>
+      <c r="X8" s="649"/>
+      <c r="Y8" s="649"/>
+      <c r="Z8" s="649"/>
+      <c r="AA8" s="649"/>
+      <c r="AB8" s="649"/>
+      <c r="AC8" s="649"/>
+      <c r="AD8" s="649"/>
+      <c r="AE8" s="649"/>
+      <c r="AF8" s="649"/>
+      <c r="AG8" s="649"/>
+      <c r="AH8" s="649"/>
+      <c r="AI8" s="649"/>
+      <c r="AJ8" s="649"/>
+      <c r="AK8" s="649"/>
+      <c r="AL8" s="649"/>
+      <c r="AM8" s="649"/>
+      <c r="AN8" s="649"/>
+      <c r="AO8" s="649"/>
+      <c r="AP8" s="649"/>
+      <c r="AQ8" s="649"/>
+      <c r="AR8" s="649"/>
+      <c r="AS8" s="649"/>
+      <c r="AT8" s="649"/>
+      <c r="AU8" s="649"/>
+      <c r="AV8" s="649"/>
+      <c r="AW8" s="649"/>
+      <c r="AX8" s="650"/>
+      <c r="AY8" s="651" t="s">
         <v>18</v>
       </c>
-      <c r="AZ8" s="649"/>
-      <c r="BA8" s="649"/>
-      <c r="BB8" s="649"/>
-      <c r="BC8" s="649"/>
-      <c r="BD8" s="649"/>
-      <c r="BE8" s="649"/>
-      <c r="BF8" s="650">
+      <c r="AZ8" s="651"/>
+      <c r="BA8" s="651"/>
+      <c r="BB8" s="651"/>
+      <c r="BC8" s="651"/>
+      <c r="BD8" s="651"/>
+      <c r="BE8" s="651"/>
+      <c r="BF8" s="652">
         <v>1</v>
       </c>
-      <c r="BG8" s="650"/>
-      <c r="BH8" s="650"/>
-      <c r="BI8" s="650"/>
-      <c r="BJ8" s="650"/>
-      <c r="BK8" s="650"/>
-      <c r="BL8" s="651"/>
+      <c r="BG8" s="652"/>
+      <c r="BH8" s="652"/>
+      <c r="BI8" s="652"/>
+      <c r="BJ8" s="652"/>
+      <c r="BK8" s="652"/>
+      <c r="BL8" s="653"/>
     </row>
     <row r="9" spans="1:64" ht="15.75" customHeight="1">
-      <c r="A9" s="687" t="s">
+      <c r="A9" s="689" t="s">
         <v>46</v>
       </c>
       <c r="B9" s="511"/>
@@ -22946,75 +21907,75 @@
       <c r="R9" s="511"/>
       <c r="S9" s="511"/>
       <c r="T9" s="511"/>
-      <c r="U9" s="695" t="s">
+      <c r="U9" s="697" t="s">
         <v>110</v>
       </c>
-      <c r="V9" s="695"/>
-      <c r="W9" s="666" t="s">
+      <c r="V9" s="697"/>
+      <c r="W9" s="668" t="s">
         <v>111</v>
       </c>
-      <c r="X9" s="666"/>
-      <c r="Y9" s="666"/>
-      <c r="Z9" s="666"/>
-      <c r="AA9" s="666" t="s">
+      <c r="X9" s="668"/>
+      <c r="Y9" s="668"/>
+      <c r="Z9" s="668"/>
+      <c r="AA9" s="668" t="s">
         <v>112</v>
       </c>
-      <c r="AB9" s="666"/>
-      <c r="AC9" s="666"/>
-      <c r="AD9" s="666"/>
-      <c r="AE9" s="666" t="s">
+      <c r="AB9" s="668"/>
+      <c r="AC9" s="668"/>
+      <c r="AD9" s="668"/>
+      <c r="AE9" s="668" t="s">
         <v>29</v>
       </c>
-      <c r="AF9" s="666"/>
-      <c r="AG9" s="666"/>
-      <c r="AH9" s="666"/>
-      <c r="AI9" s="666"/>
-      <c r="AJ9" s="666" t="s">
+      <c r="AF9" s="668"/>
+      <c r="AG9" s="668"/>
+      <c r="AH9" s="668"/>
+      <c r="AI9" s="668"/>
+      <c r="AJ9" s="668" t="s">
         <v>113</v>
       </c>
-      <c r="AK9" s="666"/>
-      <c r="AL9" s="666"/>
-      <c r="AM9" s="666"/>
+      <c r="AK9" s="668"/>
+      <c r="AL9" s="668"/>
+      <c r="AM9" s="668"/>
       <c r="AN9" s="177" t="s">
         <v>147</v>
       </c>
-      <c r="AO9" s="689"/>
-      <c r="AP9" s="689"/>
+      <c r="AO9" s="691"/>
+      <c r="AP9" s="691"/>
       <c r="AQ9" s="178"/>
       <c r="AR9" s="177" t="s">
         <v>148</v>
       </c>
-      <c r="AS9" s="689"/>
-      <c r="AT9" s="689"/>
+      <c r="AS9" s="691"/>
+      <c r="AT9" s="691"/>
       <c r="AU9" s="178"/>
       <c r="AV9" s="177" t="s">
         <v>149</v>
       </c>
-      <c r="AW9" s="689"/>
-      <c r="AX9" s="689"/>
+      <c r="AW9" s="691"/>
+      <c r="AX9" s="691"/>
       <c r="AY9" s="178"/>
-      <c r="AZ9" s="666" t="s">
+      <c r="AZ9" s="668" t="s">
         <v>114</v>
       </c>
-      <c r="BA9" s="666"/>
-      <c r="BB9" s="666"/>
-      <c r="BC9" s="666"/>
-      <c r="BD9" s="666" t="s">
+      <c r="BA9" s="668"/>
+      <c r="BB9" s="668"/>
+      <c r="BC9" s="668"/>
+      <c r="BD9" s="668" t="s">
         <v>156</v>
       </c>
-      <c r="BE9" s="666"/>
-      <c r="BF9" s="666"/>
-      <c r="BG9" s="666"/>
-      <c r="BH9" s="666"/>
-      <c r="BI9" s="666" t="s">
+      <c r="BE9" s="668"/>
+      <c r="BF9" s="668"/>
+      <c r="BG9" s="668"/>
+      <c r="BH9" s="668"/>
+      <c r="BI9" s="668" t="s">
         <v>115</v>
       </c>
-      <c r="BJ9" s="666"/>
-      <c r="BK9" s="666"/>
-      <c r="BL9" s="688"/>
+      <c r="BJ9" s="668"/>
+      <c r="BK9" s="668"/>
+      <c r="BL9" s="690"/>
     </row>
     <row r="10" spans="1:64" ht="15.75" customHeight="1">
-      <c r="A10" s="687"/>
+      <c r="A10" s="689"/>
       <c r="B10" s="511"/>
       <c r="C10" s="511"/>
       <c r="D10" s="511"/>
@@ -23034,53 +21995,53 @@
       <c r="R10" s="511"/>
       <c r="S10" s="511"/>
       <c r="T10" s="511"/>
-      <c r="U10" s="695"/>
-      <c r="V10" s="695"/>
-      <c r="W10" s="666"/>
-      <c r="X10" s="666"/>
-      <c r="Y10" s="666"/>
-      <c r="Z10" s="666"/>
-      <c r="AA10" s="666"/>
-      <c r="AB10" s="666"/>
-      <c r="AC10" s="666"/>
-      <c r="AD10" s="666"/>
-      <c r="AE10" s="666"/>
-      <c r="AF10" s="666"/>
-      <c r="AG10" s="666"/>
-      <c r="AH10" s="666"/>
-      <c r="AI10" s="666"/>
-      <c r="AJ10" s="666"/>
-      <c r="AK10" s="666"/>
-      <c r="AL10" s="666"/>
-      <c r="AM10" s="666"/>
-      <c r="AN10" s="690"/>
-      <c r="AO10" s="691"/>
-      <c r="AP10" s="691"/>
-      <c r="AQ10" s="692"/>
-      <c r="AR10" s="690"/>
-      <c r="AS10" s="691"/>
-      <c r="AT10" s="691"/>
-      <c r="AU10" s="692"/>
-      <c r="AV10" s="690"/>
-      <c r="AW10" s="691"/>
-      <c r="AX10" s="691"/>
-      <c r="AY10" s="692"/>
-      <c r="AZ10" s="666"/>
-      <c r="BA10" s="666"/>
-      <c r="BB10" s="666"/>
-      <c r="BC10" s="666"/>
-      <c r="BD10" s="666"/>
-      <c r="BE10" s="666"/>
-      <c r="BF10" s="666"/>
-      <c r="BG10" s="666"/>
-      <c r="BH10" s="666"/>
-      <c r="BI10" s="666"/>
-      <c r="BJ10" s="666"/>
-      <c r="BK10" s="666"/>
-      <c r="BL10" s="688"/>
+      <c r="U10" s="697"/>
+      <c r="V10" s="697"/>
+      <c r="W10" s="668"/>
+      <c r="X10" s="668"/>
+      <c r="Y10" s="668"/>
+      <c r="Z10" s="668"/>
+      <c r="AA10" s="668"/>
+      <c r="AB10" s="668"/>
+      <c r="AC10" s="668"/>
+      <c r="AD10" s="668"/>
+      <c r="AE10" s="668"/>
+      <c r="AF10" s="668"/>
+      <c r="AG10" s="668"/>
+      <c r="AH10" s="668"/>
+      <c r="AI10" s="668"/>
+      <c r="AJ10" s="668"/>
+      <c r="AK10" s="668"/>
+      <c r="AL10" s="668"/>
+      <c r="AM10" s="668"/>
+      <c r="AN10" s="692"/>
+      <c r="AO10" s="693"/>
+      <c r="AP10" s="693"/>
+      <c r="AQ10" s="694"/>
+      <c r="AR10" s="692"/>
+      <c r="AS10" s="693"/>
+      <c r="AT10" s="693"/>
+      <c r="AU10" s="694"/>
+      <c r="AV10" s="692"/>
+      <c r="AW10" s="693"/>
+      <c r="AX10" s="693"/>
+      <c r="AY10" s="694"/>
+      <c r="AZ10" s="668"/>
+      <c r="BA10" s="668"/>
+      <c r="BB10" s="668"/>
+      <c r="BC10" s="668"/>
+      <c r="BD10" s="668"/>
+      <c r="BE10" s="668"/>
+      <c r="BF10" s="668"/>
+      <c r="BG10" s="668"/>
+      <c r="BH10" s="668"/>
+      <c r="BI10" s="668"/>
+      <c r="BJ10" s="668"/>
+      <c r="BK10" s="668"/>
+      <c r="BL10" s="690"/>
     </row>
     <row r="11" spans="1:64" ht="15.75" customHeight="1">
-      <c r="A11" s="687"/>
+      <c r="A11" s="689"/>
       <c r="B11" s="511"/>
       <c r="C11" s="511"/>
       <c r="D11" s="511"/>
@@ -23100,53 +22061,53 @@
       <c r="R11" s="511"/>
       <c r="S11" s="511"/>
       <c r="T11" s="511"/>
-      <c r="U11" s="695"/>
-      <c r="V11" s="695"/>
-      <c r="W11" s="666"/>
-      <c r="X11" s="666"/>
-      <c r="Y11" s="666"/>
-      <c r="Z11" s="666"/>
-      <c r="AA11" s="666"/>
-      <c r="AB11" s="666"/>
-      <c r="AC11" s="666"/>
-      <c r="AD11" s="666"/>
-      <c r="AE11" s="666"/>
-      <c r="AF11" s="666"/>
-      <c r="AG11" s="666"/>
-      <c r="AH11" s="666"/>
-      <c r="AI11" s="666"/>
-      <c r="AJ11" s="666"/>
-      <c r="AK11" s="666"/>
-      <c r="AL11" s="666"/>
-      <c r="AM11" s="666"/>
-      <c r="AN11" s="690"/>
-      <c r="AO11" s="691"/>
-      <c r="AP11" s="691"/>
-      <c r="AQ11" s="692"/>
-      <c r="AR11" s="690"/>
-      <c r="AS11" s="691"/>
-      <c r="AT11" s="691"/>
-      <c r="AU11" s="692"/>
-      <c r="AV11" s="690"/>
-      <c r="AW11" s="691"/>
-      <c r="AX11" s="691"/>
-      <c r="AY11" s="692"/>
-      <c r="AZ11" s="666"/>
-      <c r="BA11" s="666"/>
-      <c r="BB11" s="666"/>
-      <c r="BC11" s="666"/>
-      <c r="BD11" s="666"/>
-      <c r="BE11" s="666"/>
-      <c r="BF11" s="666"/>
-      <c r="BG11" s="666"/>
-      <c r="BH11" s="666"/>
-      <c r="BI11" s="666"/>
-      <c r="BJ11" s="666"/>
-      <c r="BK11" s="666"/>
-      <c r="BL11" s="688"/>
+      <c r="U11" s="697"/>
+      <c r="V11" s="697"/>
+      <c r="W11" s="668"/>
+      <c r="X11" s="668"/>
+      <c r="Y11" s="668"/>
+      <c r="Z11" s="668"/>
+      <c r="AA11" s="668"/>
+      <c r="AB11" s="668"/>
+      <c r="AC11" s="668"/>
+      <c r="AD11" s="668"/>
+      <c r="AE11" s="668"/>
+      <c r="AF11" s="668"/>
+      <c r="AG11" s="668"/>
+      <c r="AH11" s="668"/>
+      <c r="AI11" s="668"/>
+      <c r="AJ11" s="668"/>
+      <c r="AK11" s="668"/>
+      <c r="AL11" s="668"/>
+      <c r="AM11" s="668"/>
+      <c r="AN11" s="692"/>
+      <c r="AO11" s="693"/>
+      <c r="AP11" s="693"/>
+      <c r="AQ11" s="694"/>
+      <c r="AR11" s="692"/>
+      <c r="AS11" s="693"/>
+      <c r="AT11" s="693"/>
+      <c r="AU11" s="694"/>
+      <c r="AV11" s="692"/>
+      <c r="AW11" s="693"/>
+      <c r="AX11" s="693"/>
+      <c r="AY11" s="694"/>
+      <c r="AZ11" s="668"/>
+      <c r="BA11" s="668"/>
+      <c r="BB11" s="668"/>
+      <c r="BC11" s="668"/>
+      <c r="BD11" s="668"/>
+      <c r="BE11" s="668"/>
+      <c r="BF11" s="668"/>
+      <c r="BG11" s="668"/>
+      <c r="BH11" s="668"/>
+      <c r="BI11" s="668"/>
+      <c r="BJ11" s="668"/>
+      <c r="BK11" s="668"/>
+      <c r="BL11" s="690"/>
     </row>
     <row r="12" spans="1:64" ht="15.75" customHeight="1">
-      <c r="A12" s="687"/>
+      <c r="A12" s="689"/>
       <c r="B12" s="511"/>
       <c r="C12" s="511"/>
       <c r="D12" s="511"/>
@@ -23166,74 +22127,74 @@
       <c r="R12" s="511"/>
       <c r="S12" s="511"/>
       <c r="T12" s="511"/>
-      <c r="U12" s="695"/>
-      <c r="V12" s="695"/>
-      <c r="W12" s="666"/>
-      <c r="X12" s="666"/>
-      <c r="Y12" s="666"/>
-      <c r="Z12" s="666"/>
-      <c r="AA12" s="666"/>
-      <c r="AB12" s="666"/>
-      <c r="AC12" s="666"/>
-      <c r="AD12" s="666"/>
-      <c r="AE12" s="666"/>
-      <c r="AF12" s="666"/>
-      <c r="AG12" s="666"/>
-      <c r="AH12" s="666"/>
-      <c r="AI12" s="666"/>
-      <c r="AJ12" s="666"/>
-      <c r="AK12" s="666"/>
-      <c r="AL12" s="666"/>
-      <c r="AM12" s="666"/>
+      <c r="U12" s="697"/>
+      <c r="V12" s="697"/>
+      <c r="W12" s="668"/>
+      <c r="X12" s="668"/>
+      <c r="Y12" s="668"/>
+      <c r="Z12" s="668"/>
+      <c r="AA12" s="668"/>
+      <c r="AB12" s="668"/>
+      <c r="AC12" s="668"/>
+      <c r="AD12" s="668"/>
+      <c r="AE12" s="668"/>
+      <c r="AF12" s="668"/>
+      <c r="AG12" s="668"/>
+      <c r="AH12" s="668"/>
+      <c r="AI12" s="668"/>
+      <c r="AJ12" s="668"/>
+      <c r="AK12" s="668"/>
+      <c r="AL12" s="668"/>
+      <c r="AM12" s="668"/>
       <c r="AN12" s="179"/>
-      <c r="AO12" s="693"/>
-      <c r="AP12" s="693"/>
+      <c r="AO12" s="695"/>
+      <c r="AP12" s="695"/>
       <c r="AQ12" s="180"/>
       <c r="AR12" s="179"/>
-      <c r="AS12" s="693"/>
-      <c r="AT12" s="693"/>
+      <c r="AS12" s="695"/>
+      <c r="AT12" s="695"/>
       <c r="AU12" s="180"/>
       <c r="AV12" s="179"/>
-      <c r="AW12" s="693"/>
-      <c r="AX12" s="693"/>
+      <c r="AW12" s="695"/>
+      <c r="AX12" s="695"/>
       <c r="AY12" s="180"/>
-      <c r="AZ12" s="666"/>
-      <c r="BA12" s="666"/>
-      <c r="BB12" s="666"/>
-      <c r="BC12" s="666"/>
-      <c r="BD12" s="666"/>
-      <c r="BE12" s="666"/>
-      <c r="BF12" s="666"/>
-      <c r="BG12" s="666"/>
-      <c r="BH12" s="666"/>
-      <c r="BI12" s="666"/>
-      <c r="BJ12" s="666"/>
-      <c r="BK12" s="666"/>
-      <c r="BL12" s="688"/>
+      <c r="AZ12" s="668"/>
+      <c r="BA12" s="668"/>
+      <c r="BB12" s="668"/>
+      <c r="BC12" s="668"/>
+      <c r="BD12" s="668"/>
+      <c r="BE12" s="668"/>
+      <c r="BF12" s="668"/>
+      <c r="BG12" s="668"/>
+      <c r="BH12" s="668"/>
+      <c r="BI12" s="668"/>
+      <c r="BJ12" s="668"/>
+      <c r="BK12" s="668"/>
+      <c r="BL12" s="690"/>
     </row>
     <row r="13" spans="1:64" ht="16.5" customHeight="1">
-      <c r="A13" s="667"/>
-      <c r="B13" s="668"/>
-      <c r="C13" s="668"/>
-      <c r="D13" s="668"/>
-      <c r="E13" s="668"/>
-      <c r="F13" s="668"/>
-      <c r="G13" s="668"/>
-      <c r="H13" s="668"/>
-      <c r="I13" s="668"/>
-      <c r="J13" s="668"/>
-      <c r="K13" s="668"/>
-      <c r="L13" s="668"/>
-      <c r="M13" s="668"/>
-      <c r="N13" s="668"/>
-      <c r="O13" s="668"/>
-      <c r="P13" s="668"/>
-      <c r="Q13" s="668"/>
-      <c r="R13" s="668"/>
-      <c r="S13" s="668"/>
-      <c r="T13" s="668"/>
-      <c r="U13" s="668"/>
-      <c r="V13" s="668"/>
+      <c r="A13" s="669"/>
+      <c r="B13" s="670"/>
+      <c r="C13" s="670"/>
+      <c r="D13" s="670"/>
+      <c r="E13" s="670"/>
+      <c r="F13" s="670"/>
+      <c r="G13" s="670"/>
+      <c r="H13" s="670"/>
+      <c r="I13" s="670"/>
+      <c r="J13" s="670"/>
+      <c r="K13" s="670"/>
+      <c r="L13" s="670"/>
+      <c r="M13" s="670"/>
+      <c r="N13" s="670"/>
+      <c r="O13" s="670"/>
+      <c r="P13" s="670"/>
+      <c r="Q13" s="670"/>
+      <c r="R13" s="670"/>
+      <c r="S13" s="670"/>
+      <c r="T13" s="670"/>
+      <c r="U13" s="670"/>
+      <c r="V13" s="670"/>
       <c r="W13" s="511">
         <v>1</v>
       </c>
@@ -23259,24 +22220,24 @@
       <c r="AK13" s="511"/>
       <c r="AL13" s="511"/>
       <c r="AM13" s="511"/>
-      <c r="AN13" s="655">
+      <c r="AN13" s="657">
         <v>5</v>
       </c>
       <c r="AO13" s="510"/>
       <c r="AP13" s="510"/>
-      <c r="AQ13" s="656"/>
-      <c r="AR13" s="655" t="s">
+      <c r="AQ13" s="658"/>
+      <c r="AR13" s="657" t="s">
         <v>150</v>
       </c>
       <c r="AS13" s="510"/>
       <c r="AT13" s="510"/>
-      <c r="AU13" s="656"/>
-      <c r="AV13" s="655" t="s">
+      <c r="AU13" s="658"/>
+      <c r="AV13" s="657" t="s">
         <v>151</v>
       </c>
       <c r="AW13" s="510"/>
       <c r="AX13" s="510"/>
-      <c r="AY13" s="656"/>
+      <c r="AY13" s="658"/>
       <c r="AZ13" s="511" t="s">
         <v>157</v>
       </c>
@@ -23290,1080 +22251,1080 @@
       <c r="BF13" s="511"/>
       <c r="BG13" s="511"/>
       <c r="BH13" s="511"/>
-      <c r="BI13" s="668"/>
-      <c r="BJ13" s="668"/>
-      <c r="BK13" s="668"/>
-      <c r="BL13" s="694"/>
+      <c r="BI13" s="670"/>
+      <c r="BJ13" s="670"/>
+      <c r="BK13" s="670"/>
+      <c r="BL13" s="696"/>
     </row>
     <row r="14" spans="1:64" ht="45" customHeight="1">
-      <c r="A14" s="628" t="str">
+      <c r="A14" s="630" t="str">
         <f>BFTC!B5</f>
         <v>KASKİ-01</v>
       </c>
-      <c r="B14" s="629"/>
-      <c r="C14" s="629"/>
-      <c r="D14" s="630"/>
-      <c r="E14" s="631">
+      <c r="B14" s="631"/>
+      <c r="C14" s="631"/>
+      <c r="D14" s="632"/>
+      <c r="E14" s="633">
         <f>BFTC!C5</f>
         <v>0</v>
       </c>
-      <c r="F14" s="632"/>
-      <c r="G14" s="632"/>
-      <c r="H14" s="632"/>
-      <c r="I14" s="632"/>
-      <c r="J14" s="632"/>
-      <c r="K14" s="632"/>
-      <c r="L14" s="632"/>
-      <c r="M14" s="632"/>
-      <c r="N14" s="632"/>
-      <c r="O14" s="632"/>
-      <c r="P14" s="632"/>
-      <c r="Q14" s="632"/>
-      <c r="R14" s="632"/>
-      <c r="S14" s="632"/>
-      <c r="T14" s="633"/>
-      <c r="U14" s="634">
+      <c r="F14" s="634"/>
+      <c r="G14" s="634"/>
+      <c r="H14" s="634"/>
+      <c r="I14" s="634"/>
+      <c r="J14" s="634"/>
+      <c r="K14" s="634"/>
+      <c r="L14" s="634"/>
+      <c r="M14" s="634"/>
+      <c r="N14" s="634"/>
+      <c r="O14" s="634"/>
+      <c r="P14" s="634"/>
+      <c r="Q14" s="634"/>
+      <c r="R14" s="634"/>
+      <c r="S14" s="634"/>
+      <c r="T14" s="635"/>
+      <c r="U14" s="636">
         <f>+BFTC!D5</f>
         <v>0</v>
       </c>
-      <c r="V14" s="635"/>
-      <c r="W14" s="623">
+      <c r="V14" s="637"/>
+      <c r="W14" s="625">
         <f>+BFTC!E5</f>
         <v>0</v>
       </c>
-      <c r="X14" s="623"/>
-      <c r="Y14" s="623"/>
-      <c r="Z14" s="623"/>
-      <c r="AA14" s="623">
+      <c r="X14" s="625"/>
+      <c r="Y14" s="625"/>
+      <c r="Z14" s="625"/>
+      <c r="AA14" s="625">
         <f>+BFTC!F5</f>
         <v>0</v>
       </c>
-      <c r="AB14" s="623"/>
-      <c r="AC14" s="623"/>
-      <c r="AD14" s="623"/>
-      <c r="AE14" s="636">
+      <c r="AB14" s="625"/>
+      <c r="AC14" s="625"/>
+      <c r="AD14" s="625"/>
+      <c r="AE14" s="638">
         <f>AA14*W14</f>
         <v>0</v>
       </c>
-      <c r="AF14" s="636"/>
-      <c r="AG14" s="636"/>
-      <c r="AH14" s="636"/>
-      <c r="AI14" s="636"/>
-      <c r="AJ14" s="623">
+      <c r="AF14" s="638"/>
+      <c r="AG14" s="638"/>
+      <c r="AH14" s="638"/>
+      <c r="AI14" s="638"/>
+      <c r="AJ14" s="625">
         <f>IF(+A14=0,0,HLOOKUP(A14,İcmal!$E$8:$BH$52,43,0))</f>
         <v>0</v>
       </c>
-      <c r="AK14" s="623"/>
-      <c r="AL14" s="623"/>
-      <c r="AM14" s="623"/>
-      <c r="AN14" s="623">
+      <c r="AK14" s="625"/>
+      <c r="AL14" s="625"/>
+      <c r="AM14" s="625"/>
+      <c r="AN14" s="625">
         <f>IF(+A14=0,0,HLOOKUP(A14,İcmal!$E$8:$BH$52,17,0))</f>
         <v>0</v>
       </c>
-      <c r="AO14" s="623"/>
-      <c r="AP14" s="623"/>
-      <c r="AQ14" s="623"/>
-      <c r="AR14" s="623">
+      <c r="AO14" s="625"/>
+      <c r="AP14" s="625"/>
+      <c r="AQ14" s="625"/>
+      <c r="AR14" s="625">
         <f>AJ14+AN14</f>
         <v>0</v>
       </c>
-      <c r="AS14" s="623"/>
-      <c r="AT14" s="623"/>
-      <c r="AU14" s="623"/>
-      <c r="AV14" s="637">
+      <c r="AS14" s="625"/>
+      <c r="AT14" s="625"/>
+      <c r="AU14" s="625"/>
+      <c r="AV14" s="639">
         <f>AA14*AJ14</f>
         <v>0</v>
       </c>
-      <c r="AW14" s="638"/>
-      <c r="AX14" s="638"/>
-      <c r="AY14" s="639"/>
-      <c r="AZ14" s="640">
+      <c r="AW14" s="640"/>
+      <c r="AX14" s="640"/>
+      <c r="AY14" s="641"/>
+      <c r="AZ14" s="642">
         <f t="shared" ref="AZ14" si="0">IF(AE14=0,0,(BD14/AE14))</f>
         <v>0</v>
       </c>
-      <c r="BA14" s="641"/>
-      <c r="BB14" s="641"/>
-      <c r="BC14" s="642"/>
-      <c r="BD14" s="623">
+      <c r="BA14" s="643"/>
+      <c r="BB14" s="643"/>
+      <c r="BC14" s="644"/>
+      <c r="BD14" s="625">
         <f>AA14*AR14</f>
         <v>0</v>
       </c>
-      <c r="BE14" s="623"/>
-      <c r="BF14" s="623"/>
-      <c r="BG14" s="623"/>
-      <c r="BH14" s="623"/>
-      <c r="BI14" s="623"/>
-      <c r="BJ14" s="623"/>
-      <c r="BK14" s="623"/>
-      <c r="BL14" s="624"/>
+      <c r="BE14" s="625"/>
+      <c r="BF14" s="625"/>
+      <c r="BG14" s="625"/>
+      <c r="BH14" s="625"/>
+      <c r="BI14" s="625"/>
+      <c r="BJ14" s="625"/>
+      <c r="BK14" s="625"/>
+      <c r="BL14" s="626"/>
     </row>
     <row r="15" spans="1:64" ht="45" customHeight="1">
-      <c r="A15" s="628" t="str">
+      <c r="A15" s="630" t="str">
         <f>BFTC!B6</f>
         <v>KASKİ-02</v>
       </c>
-      <c r="B15" s="629"/>
-      <c r="C15" s="629"/>
-      <c r="D15" s="630"/>
-      <c r="E15" s="631">
+      <c r="B15" s="631"/>
+      <c r="C15" s="631"/>
+      <c r="D15" s="632"/>
+      <c r="E15" s="633">
         <f>BFTC!C6</f>
         <v>0</v>
       </c>
-      <c r="F15" s="632"/>
-      <c r="G15" s="632"/>
-      <c r="H15" s="632"/>
-      <c r="I15" s="632"/>
-      <c r="J15" s="632"/>
-      <c r="K15" s="632"/>
-      <c r="L15" s="632"/>
-      <c r="M15" s="632"/>
-      <c r="N15" s="632"/>
-      <c r="O15" s="632"/>
-      <c r="P15" s="632"/>
-      <c r="Q15" s="632"/>
-      <c r="R15" s="632"/>
-      <c r="S15" s="632"/>
-      <c r="T15" s="633"/>
-      <c r="U15" s="634">
+      <c r="F15" s="634"/>
+      <c r="G15" s="634"/>
+      <c r="H15" s="634"/>
+      <c r="I15" s="634"/>
+      <c r="J15" s="634"/>
+      <c r="K15" s="634"/>
+      <c r="L15" s="634"/>
+      <c r="M15" s="634"/>
+      <c r="N15" s="634"/>
+      <c r="O15" s="634"/>
+      <c r="P15" s="634"/>
+      <c r="Q15" s="634"/>
+      <c r="R15" s="634"/>
+      <c r="S15" s="634"/>
+      <c r="T15" s="635"/>
+      <c r="U15" s="636">
         <f>+BFTC!D6</f>
         <v>0</v>
       </c>
-      <c r="V15" s="635"/>
-      <c r="W15" s="623">
+      <c r="V15" s="637"/>
+      <c r="W15" s="625">
         <f>+BFTC!E6</f>
         <v>0</v>
       </c>
-      <c r="X15" s="623"/>
-      <c r="Y15" s="623"/>
-      <c r="Z15" s="623"/>
-      <c r="AA15" s="623">
+      <c r="X15" s="625"/>
+      <c r="Y15" s="625"/>
+      <c r="Z15" s="625"/>
+      <c r="AA15" s="625">
         <f>+BFTC!F6</f>
         <v>0</v>
       </c>
-      <c r="AB15" s="623"/>
-      <c r="AC15" s="623"/>
-      <c r="AD15" s="623"/>
-      <c r="AE15" s="636">
+      <c r="AB15" s="625"/>
+      <c r="AC15" s="625"/>
+      <c r="AD15" s="625"/>
+      <c r="AE15" s="638">
         <f t="shared" ref="AE15:AE18" si="1">AA15*W15</f>
         <v>0</v>
       </c>
-      <c r="AF15" s="636"/>
-      <c r="AG15" s="636"/>
-      <c r="AH15" s="636"/>
-      <c r="AI15" s="636"/>
-      <c r="AJ15" s="623">
+      <c r="AF15" s="638"/>
+      <c r="AG15" s="638"/>
+      <c r="AH15" s="638"/>
+      <c r="AI15" s="638"/>
+      <c r="AJ15" s="625">
         <f>IF(+A15=0,0,HLOOKUP(A15,İcmal!$E$8:$BH$52,43,0))</f>
         <v>0</v>
       </c>
-      <c r="AK15" s="623"/>
-      <c r="AL15" s="623"/>
-      <c r="AM15" s="623"/>
-      <c r="AN15" s="637">
+      <c r="AK15" s="625"/>
+      <c r="AL15" s="625"/>
+      <c r="AM15" s="625"/>
+      <c r="AN15" s="639">
         <f>IF(+A15=0,0,HLOOKUP(A15,İcmal!$E$8:$BH$52,17,0))</f>
         <v>0</v>
       </c>
-      <c r="AO15" s="638"/>
-      <c r="AP15" s="638"/>
-      <c r="AQ15" s="639"/>
-      <c r="AR15" s="623">
+      <c r="AO15" s="640"/>
+      <c r="AP15" s="640"/>
+      <c r="AQ15" s="641"/>
+      <c r="AR15" s="625">
         <f t="shared" ref="AR15:AR18" si="2">AJ15+AN15</f>
         <v>0</v>
       </c>
-      <c r="AS15" s="623"/>
-      <c r="AT15" s="623"/>
-      <c r="AU15" s="623"/>
-      <c r="AV15" s="637">
+      <c r="AS15" s="625"/>
+      <c r="AT15" s="625"/>
+      <c r="AU15" s="625"/>
+      <c r="AV15" s="639">
         <f t="shared" ref="AV15:AV18" si="3">AA15*AJ15</f>
         <v>0</v>
       </c>
-      <c r="AW15" s="638"/>
-      <c r="AX15" s="638"/>
-      <c r="AY15" s="639"/>
-      <c r="AZ15" s="640">
+      <c r="AW15" s="640"/>
+      <c r="AX15" s="640"/>
+      <c r="AY15" s="641"/>
+      <c r="AZ15" s="642">
         <f t="shared" ref="AZ15:AZ18" si="4">IF(AE15=0,0,(BD15/AE15))</f>
         <v>0</v>
       </c>
-      <c r="BA15" s="641"/>
-      <c r="BB15" s="641"/>
-      <c r="BC15" s="642"/>
-      <c r="BD15" s="623">
+      <c r="BA15" s="643"/>
+      <c r="BB15" s="643"/>
+      <c r="BC15" s="644"/>
+      <c r="BD15" s="625">
         <f t="shared" ref="BD15:BD18" si="5">AA15*AR15</f>
         <v>0</v>
       </c>
-      <c r="BE15" s="623"/>
-      <c r="BF15" s="623"/>
-      <c r="BG15" s="623"/>
-      <c r="BH15" s="623"/>
-      <c r="BI15" s="623"/>
-      <c r="BJ15" s="623"/>
-      <c r="BK15" s="623"/>
-      <c r="BL15" s="624"/>
+      <c r="BE15" s="625"/>
+      <c r="BF15" s="625"/>
+      <c r="BG15" s="625"/>
+      <c r="BH15" s="625"/>
+      <c r="BI15" s="625"/>
+      <c r="BJ15" s="625"/>
+      <c r="BK15" s="625"/>
+      <c r="BL15" s="626"/>
     </row>
     <row r="16" spans="1:64" ht="45" customHeight="1">
-      <c r="A16" s="628" t="str">
+      <c r="A16" s="630" t="str">
         <f>BFTC!B7</f>
         <v>KASKİ-03</v>
       </c>
-      <c r="B16" s="629"/>
-      <c r="C16" s="629"/>
-      <c r="D16" s="630"/>
-      <c r="E16" s="631">
+      <c r="B16" s="631"/>
+      <c r="C16" s="631"/>
+      <c r="D16" s="632"/>
+      <c r="E16" s="633">
         <f>BFTC!C7</f>
         <v>0</v>
       </c>
-      <c r="F16" s="632"/>
-      <c r="G16" s="632"/>
-      <c r="H16" s="632"/>
-      <c r="I16" s="632"/>
-      <c r="J16" s="632"/>
-      <c r="K16" s="632"/>
-      <c r="L16" s="632"/>
-      <c r="M16" s="632"/>
-      <c r="N16" s="632"/>
-      <c r="O16" s="632"/>
-      <c r="P16" s="632"/>
-      <c r="Q16" s="632"/>
-      <c r="R16" s="632"/>
-      <c r="S16" s="632"/>
-      <c r="T16" s="633"/>
-      <c r="U16" s="634">
+      <c r="F16" s="634"/>
+      <c r="G16" s="634"/>
+      <c r="H16" s="634"/>
+      <c r="I16" s="634"/>
+      <c r="J16" s="634"/>
+      <c r="K16" s="634"/>
+      <c r="L16" s="634"/>
+      <c r="M16" s="634"/>
+      <c r="N16" s="634"/>
+      <c r="O16" s="634"/>
+      <c r="P16" s="634"/>
+      <c r="Q16" s="634"/>
+      <c r="R16" s="634"/>
+      <c r="S16" s="634"/>
+      <c r="T16" s="635"/>
+      <c r="U16" s="636">
         <f>+BFTC!D7</f>
         <v>0</v>
       </c>
-      <c r="V16" s="635"/>
-      <c r="W16" s="623">
+      <c r="V16" s="637"/>
+      <c r="W16" s="625">
         <f>+BFTC!E7</f>
         <v>0</v>
       </c>
-      <c r="X16" s="623"/>
-      <c r="Y16" s="623"/>
-      <c r="Z16" s="623"/>
-      <c r="AA16" s="623">
+      <c r="X16" s="625"/>
+      <c r="Y16" s="625"/>
+      <c r="Z16" s="625"/>
+      <c r="AA16" s="625">
         <f>+BFTC!F7</f>
         <v>0</v>
       </c>
-      <c r="AB16" s="623"/>
-      <c r="AC16" s="623"/>
-      <c r="AD16" s="623"/>
-      <c r="AE16" s="636">
+      <c r="AB16" s="625"/>
+      <c r="AC16" s="625"/>
+      <c r="AD16" s="625"/>
+      <c r="AE16" s="638">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AF16" s="636"/>
-      <c r="AG16" s="636"/>
-      <c r="AH16" s="636"/>
-      <c r="AI16" s="636"/>
-      <c r="AJ16" s="623">
+      <c r="AF16" s="638"/>
+      <c r="AG16" s="638"/>
+      <c r="AH16" s="638"/>
+      <c r="AI16" s="638"/>
+      <c r="AJ16" s="625">
         <f>IF(+A16=0,0,HLOOKUP(A16,İcmal!$E$8:$BH$52,43,0))</f>
         <v>0</v>
       </c>
-      <c r="AK16" s="623"/>
-      <c r="AL16" s="623"/>
-      <c r="AM16" s="623"/>
-      <c r="AN16" s="637">
+      <c r="AK16" s="625"/>
+      <c r="AL16" s="625"/>
+      <c r="AM16" s="625"/>
+      <c r="AN16" s="639">
         <f>IF(+A16=0,0,HLOOKUP(A16,İcmal!$E$8:$BH$52,17,0))</f>
         <v>0</v>
       </c>
-      <c r="AO16" s="638"/>
-      <c r="AP16" s="638"/>
-      <c r="AQ16" s="639"/>
-      <c r="AR16" s="623">
+      <c r="AO16" s="640"/>
+      <c r="AP16" s="640"/>
+      <c r="AQ16" s="641"/>
+      <c r="AR16" s="625">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AS16" s="623"/>
-      <c r="AT16" s="623"/>
-      <c r="AU16" s="623"/>
-      <c r="AV16" s="637">
+      <c r="AS16" s="625"/>
+      <c r="AT16" s="625"/>
+      <c r="AU16" s="625"/>
+      <c r="AV16" s="639">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AW16" s="638"/>
-      <c r="AX16" s="638"/>
-      <c r="AY16" s="639"/>
-      <c r="AZ16" s="640">
+      <c r="AW16" s="640"/>
+      <c r="AX16" s="640"/>
+      <c r="AY16" s="641"/>
+      <c r="AZ16" s="642">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA16" s="641"/>
-      <c r="BB16" s="641"/>
-      <c r="BC16" s="642"/>
-      <c r="BD16" s="623">
+      <c r="BA16" s="643"/>
+      <c r="BB16" s="643"/>
+      <c r="BC16" s="644"/>
+      <c r="BD16" s="625">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BE16" s="623"/>
-      <c r="BF16" s="623"/>
-      <c r="BG16" s="623"/>
-      <c r="BH16" s="623"/>
-      <c r="BI16" s="623"/>
-      <c r="BJ16" s="623"/>
-      <c r="BK16" s="623"/>
-      <c r="BL16" s="624"/>
+      <c r="BE16" s="625"/>
+      <c r="BF16" s="625"/>
+      <c r="BG16" s="625"/>
+      <c r="BH16" s="625"/>
+      <c r="BI16" s="625"/>
+      <c r="BJ16" s="625"/>
+      <c r="BK16" s="625"/>
+      <c r="BL16" s="626"/>
     </row>
     <row r="17" spans="1:66" ht="45" customHeight="1">
-      <c r="A17" s="628" t="str">
+      <c r="A17" s="630" t="str">
         <f>BFTC!B8</f>
         <v>KASKİ-04</v>
       </c>
-      <c r="B17" s="629"/>
-      <c r="C17" s="629"/>
-      <c r="D17" s="630"/>
-      <c r="E17" s="631">
+      <c r="B17" s="631"/>
+      <c r="C17" s="631"/>
+      <c r="D17" s="632"/>
+      <c r="E17" s="633">
         <f>BFTC!C8</f>
         <v>0</v>
       </c>
-      <c r="F17" s="632"/>
-      <c r="G17" s="632"/>
-      <c r="H17" s="632"/>
-      <c r="I17" s="632"/>
-      <c r="J17" s="632"/>
-      <c r="K17" s="632"/>
-      <c r="L17" s="632"/>
-      <c r="M17" s="632"/>
-      <c r="N17" s="632"/>
-      <c r="O17" s="632"/>
-      <c r="P17" s="632"/>
-      <c r="Q17" s="632"/>
-      <c r="R17" s="632"/>
-      <c r="S17" s="632"/>
-      <c r="T17" s="633"/>
-      <c r="U17" s="634">
+      <c r="F17" s="634"/>
+      <c r="G17" s="634"/>
+      <c r="H17" s="634"/>
+      <c r="I17" s="634"/>
+      <c r="J17" s="634"/>
+      <c r="K17" s="634"/>
+      <c r="L17" s="634"/>
+      <c r="M17" s="634"/>
+      <c r="N17" s="634"/>
+      <c r="O17" s="634"/>
+      <c r="P17" s="634"/>
+      <c r="Q17" s="634"/>
+      <c r="R17" s="634"/>
+      <c r="S17" s="634"/>
+      <c r="T17" s="635"/>
+      <c r="U17" s="636">
         <f>+BFTC!D8</f>
         <v>0</v>
       </c>
-      <c r="V17" s="635"/>
-      <c r="W17" s="623">
+      <c r="V17" s="637"/>
+      <c r="W17" s="625">
         <f>+BFTC!E8</f>
         <v>0</v>
       </c>
-      <c r="X17" s="623"/>
-      <c r="Y17" s="623"/>
-      <c r="Z17" s="623"/>
-      <c r="AA17" s="623">
+      <c r="X17" s="625"/>
+      <c r="Y17" s="625"/>
+      <c r="Z17" s="625"/>
+      <c r="AA17" s="625">
         <f>+BFTC!F8</f>
         <v>0</v>
       </c>
-      <c r="AB17" s="623"/>
-      <c r="AC17" s="623"/>
-      <c r="AD17" s="623"/>
-      <c r="AE17" s="636">
+      <c r="AB17" s="625"/>
+      <c r="AC17" s="625"/>
+      <c r="AD17" s="625"/>
+      <c r="AE17" s="638">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AF17" s="636"/>
-      <c r="AG17" s="636"/>
-      <c r="AH17" s="636"/>
-      <c r="AI17" s="636"/>
-      <c r="AJ17" s="623">
+      <c r="AF17" s="638"/>
+      <c r="AG17" s="638"/>
+      <c r="AH17" s="638"/>
+      <c r="AI17" s="638"/>
+      <c r="AJ17" s="625">
         <f>IF(+A17=0,0,HLOOKUP(A17,İcmal!$E$8:$BH$52,43,0))</f>
         <v>0</v>
       </c>
-      <c r="AK17" s="623"/>
-      <c r="AL17" s="623"/>
-      <c r="AM17" s="623"/>
-      <c r="AN17" s="637">
+      <c r="AK17" s="625"/>
+      <c r="AL17" s="625"/>
+      <c r="AM17" s="625"/>
+      <c r="AN17" s="639">
         <f>IF(+A17=0,0,HLOOKUP(A17,İcmal!$E$8:$BH$52,17,0))</f>
         <v>0</v>
       </c>
-      <c r="AO17" s="638"/>
-      <c r="AP17" s="638"/>
-      <c r="AQ17" s="639"/>
-      <c r="AR17" s="623">
+      <c r="AO17" s="640"/>
+      <c r="AP17" s="640"/>
+      <c r="AQ17" s="641"/>
+      <c r="AR17" s="625">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AS17" s="623"/>
-      <c r="AT17" s="623"/>
-      <c r="AU17" s="623"/>
-      <c r="AV17" s="637">
+      <c r="AS17" s="625"/>
+      <c r="AT17" s="625"/>
+      <c r="AU17" s="625"/>
+      <c r="AV17" s="639">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AW17" s="638"/>
-      <c r="AX17" s="638"/>
-      <c r="AY17" s="639"/>
-      <c r="AZ17" s="640">
+      <c r="AW17" s="640"/>
+      <c r="AX17" s="640"/>
+      <c r="AY17" s="641"/>
+      <c r="AZ17" s="642">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA17" s="641"/>
-      <c r="BB17" s="641"/>
-      <c r="BC17" s="642"/>
-      <c r="BD17" s="623">
+      <c r="BA17" s="643"/>
+      <c r="BB17" s="643"/>
+      <c r="BC17" s="644"/>
+      <c r="BD17" s="625">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BE17" s="623"/>
-      <c r="BF17" s="623"/>
-      <c r="BG17" s="623"/>
-      <c r="BH17" s="623"/>
-      <c r="BI17" s="652"/>
-      <c r="BJ17" s="653"/>
-      <c r="BK17" s="653"/>
-      <c r="BL17" s="654"/>
+      <c r="BE17" s="625"/>
+      <c r="BF17" s="625"/>
+      <c r="BG17" s="625"/>
+      <c r="BH17" s="625"/>
+      <c r="BI17" s="654"/>
+      <c r="BJ17" s="655"/>
+      <c r="BK17" s="655"/>
+      <c r="BL17" s="656"/>
     </row>
     <row r="18" spans="1:66" ht="45" customHeight="1">
-      <c r="A18" s="628" t="str">
+      <c r="A18" s="630" t="str">
         <f>BFTC!B9</f>
         <v>KASKİ-05</v>
       </c>
-      <c r="B18" s="629"/>
-      <c r="C18" s="629"/>
-      <c r="D18" s="630"/>
-      <c r="E18" s="631">
+      <c r="B18" s="631"/>
+      <c r="C18" s="631"/>
+      <c r="D18" s="632"/>
+      <c r="E18" s="633">
         <f>BFTC!C9</f>
         <v>0</v>
       </c>
-      <c r="F18" s="632"/>
-      <c r="G18" s="632"/>
-      <c r="H18" s="632"/>
-      <c r="I18" s="632"/>
-      <c r="J18" s="632"/>
-      <c r="K18" s="632"/>
-      <c r="L18" s="632"/>
-      <c r="M18" s="632"/>
-      <c r="N18" s="632"/>
-      <c r="O18" s="632"/>
-      <c r="P18" s="632"/>
-      <c r="Q18" s="632"/>
-      <c r="R18" s="632"/>
-      <c r="S18" s="632"/>
-      <c r="T18" s="633"/>
-      <c r="U18" s="634">
+      <c r="F18" s="634"/>
+      <c r="G18" s="634"/>
+      <c r="H18" s="634"/>
+      <c r="I18" s="634"/>
+      <c r="J18" s="634"/>
+      <c r="K18" s="634"/>
+      <c r="L18" s="634"/>
+      <c r="M18" s="634"/>
+      <c r="N18" s="634"/>
+      <c r="O18" s="634"/>
+      <c r="P18" s="634"/>
+      <c r="Q18" s="634"/>
+      <c r="R18" s="634"/>
+      <c r="S18" s="634"/>
+      <c r="T18" s="635"/>
+      <c r="U18" s="636">
         <f>+BFTC!D9</f>
         <v>0</v>
       </c>
-      <c r="V18" s="635"/>
-      <c r="W18" s="623">
+      <c r="V18" s="637"/>
+      <c r="W18" s="625">
         <f>+BFTC!E9</f>
         <v>0</v>
       </c>
-      <c r="X18" s="623"/>
-      <c r="Y18" s="623"/>
-      <c r="Z18" s="623"/>
-      <c r="AA18" s="623">
+      <c r="X18" s="625"/>
+      <c r="Y18" s="625"/>
+      <c r="Z18" s="625"/>
+      <c r="AA18" s="625">
         <f>+BFTC!F9</f>
         <v>0</v>
       </c>
-      <c r="AB18" s="623"/>
-      <c r="AC18" s="623"/>
-      <c r="AD18" s="623"/>
-      <c r="AE18" s="636">
+      <c r="AB18" s="625"/>
+      <c r="AC18" s="625"/>
+      <c r="AD18" s="625"/>
+      <c r="AE18" s="638">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AF18" s="636"/>
-      <c r="AG18" s="636"/>
-      <c r="AH18" s="636"/>
-      <c r="AI18" s="636"/>
-      <c r="AJ18" s="623">
+      <c r="AF18" s="638"/>
+      <c r="AG18" s="638"/>
+      <c r="AH18" s="638"/>
+      <c r="AI18" s="638"/>
+      <c r="AJ18" s="625">
         <f>IF(+A18=0,0,HLOOKUP(A18,İcmal!$E$8:$BH$52,43,0))</f>
         <v>0</v>
       </c>
-      <c r="AK18" s="623"/>
-      <c r="AL18" s="623"/>
-      <c r="AM18" s="623"/>
-      <c r="AN18" s="637">
+      <c r="AK18" s="625"/>
+      <c r="AL18" s="625"/>
+      <c r="AM18" s="625"/>
+      <c r="AN18" s="639">
         <f>IF(+A18=0,0,HLOOKUP(A18,İcmal!$E$8:$BH$52,17,0))</f>
         <v>0</v>
       </c>
-      <c r="AO18" s="638"/>
-      <c r="AP18" s="638"/>
-      <c r="AQ18" s="639"/>
-      <c r="AR18" s="623">
+      <c r="AO18" s="640"/>
+      <c r="AP18" s="640"/>
+      <c r="AQ18" s="641"/>
+      <c r="AR18" s="625">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AS18" s="623"/>
-      <c r="AT18" s="623"/>
-      <c r="AU18" s="623"/>
-      <c r="AV18" s="637">
+      <c r="AS18" s="625"/>
+      <c r="AT18" s="625"/>
+      <c r="AU18" s="625"/>
+      <c r="AV18" s="639">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AW18" s="638"/>
-      <c r="AX18" s="638"/>
-      <c r="AY18" s="639"/>
-      <c r="AZ18" s="640">
+      <c r="AW18" s="640"/>
+      <c r="AX18" s="640"/>
+      <c r="AY18" s="641"/>
+      <c r="AZ18" s="642">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BA18" s="641"/>
-      <c r="BB18" s="641"/>
-      <c r="BC18" s="642"/>
-      <c r="BD18" s="623">
+      <c r="BA18" s="643"/>
+      <c r="BB18" s="643"/>
+      <c r="BC18" s="644"/>
+      <c r="BD18" s="625">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BE18" s="623"/>
-      <c r="BF18" s="623"/>
-      <c r="BG18" s="623"/>
-      <c r="BH18" s="623"/>
-      <c r="BI18" s="623"/>
-      <c r="BJ18" s="623"/>
-      <c r="BK18" s="623"/>
-      <c r="BL18" s="624"/>
+      <c r="BE18" s="625"/>
+      <c r="BF18" s="625"/>
+      <c r="BG18" s="625"/>
+      <c r="BH18" s="625"/>
+      <c r="BI18" s="625"/>
+      <c r="BJ18" s="625"/>
+      <c r="BK18" s="625"/>
+      <c r="BL18" s="626"/>
     </row>
     <row r="19" spans="1:66" ht="45" customHeight="1">
-      <c r="A19" s="628" t="str">
+      <c r="A19" s="630" t="str">
         <f>BFTC!B10</f>
         <v>KASKİ-06</v>
       </c>
-      <c r="B19" s="629"/>
-      <c r="C19" s="629"/>
-      <c r="D19" s="630"/>
-      <c r="E19" s="631">
+      <c r="B19" s="631"/>
+      <c r="C19" s="631"/>
+      <c r="D19" s="632"/>
+      <c r="E19" s="633">
         <f>BFTC!C10</f>
         <v>0</v>
       </c>
-      <c r="F19" s="632"/>
-      <c r="G19" s="632"/>
-      <c r="H19" s="632"/>
-      <c r="I19" s="632"/>
-      <c r="J19" s="632"/>
-      <c r="K19" s="632"/>
-      <c r="L19" s="632"/>
-      <c r="M19" s="632"/>
-      <c r="N19" s="632"/>
-      <c r="O19" s="632"/>
-      <c r="P19" s="632"/>
-      <c r="Q19" s="632"/>
-      <c r="R19" s="632"/>
-      <c r="S19" s="632"/>
-      <c r="T19" s="633"/>
-      <c r="U19" s="634">
+      <c r="F19" s="634"/>
+      <c r="G19" s="634"/>
+      <c r="H19" s="634"/>
+      <c r="I19" s="634"/>
+      <c r="J19" s="634"/>
+      <c r="K19" s="634"/>
+      <c r="L19" s="634"/>
+      <c r="M19" s="634"/>
+      <c r="N19" s="634"/>
+      <c r="O19" s="634"/>
+      <c r="P19" s="634"/>
+      <c r="Q19" s="634"/>
+      <c r="R19" s="634"/>
+      <c r="S19" s="634"/>
+      <c r="T19" s="635"/>
+      <c r="U19" s="636">
         <f>+BFTC!D10</f>
         <v>0</v>
       </c>
-      <c r="V19" s="635"/>
-      <c r="W19" s="623">
+      <c r="V19" s="637"/>
+      <c r="W19" s="625">
         <f>+BFTC!E10</f>
         <v>0</v>
       </c>
-      <c r="X19" s="623"/>
-      <c r="Y19" s="623"/>
-      <c r="Z19" s="623"/>
-      <c r="AA19" s="623">
+      <c r="X19" s="625"/>
+      <c r="Y19" s="625"/>
+      <c r="Z19" s="625"/>
+      <c r="AA19" s="625">
         <f>+BFTC!F10</f>
         <v>0</v>
       </c>
-      <c r="AB19" s="623"/>
-      <c r="AC19" s="623"/>
-      <c r="AD19" s="623"/>
-      <c r="AE19" s="636">
+      <c r="AB19" s="625"/>
+      <c r="AC19" s="625"/>
+      <c r="AD19" s="625"/>
+      <c r="AE19" s="638">
         <f t="shared" ref="AE19" si="6">AA19*W19</f>
         <v>0</v>
       </c>
-      <c r="AF19" s="636"/>
-      <c r="AG19" s="636"/>
-      <c r="AH19" s="636"/>
-      <c r="AI19" s="636"/>
-      <c r="AJ19" s="623">
+      <c r="AF19" s="638"/>
+      <c r="AG19" s="638"/>
+      <c r="AH19" s="638"/>
+      <c r="AI19" s="638"/>
+      <c r="AJ19" s="625">
         <f>IF(+A19=0,0,HLOOKUP(A19,İcmal!$E$8:$BH$52,43,0))</f>
         <v>0</v>
       </c>
-      <c r="AK19" s="623"/>
-      <c r="AL19" s="623"/>
-      <c r="AM19" s="623"/>
-      <c r="AN19" s="637">
+      <c r="AK19" s="625"/>
+      <c r="AL19" s="625"/>
+      <c r="AM19" s="625"/>
+      <c r="AN19" s="639">
         <f>IF(+A19=0,0,HLOOKUP(A19,İcmal!$E$8:$BH$52,17,0))</f>
         <v>0</v>
       </c>
-      <c r="AO19" s="638"/>
-      <c r="AP19" s="638"/>
-      <c r="AQ19" s="639"/>
-      <c r="AR19" s="623">
+      <c r="AO19" s="640"/>
+      <c r="AP19" s="640"/>
+      <c r="AQ19" s="641"/>
+      <c r="AR19" s="625">
         <f t="shared" ref="AR19" si="7">AJ19+AN19</f>
         <v>0</v>
       </c>
-      <c r="AS19" s="623"/>
-      <c r="AT19" s="623"/>
-      <c r="AU19" s="623"/>
-      <c r="AV19" s="637">
+      <c r="AS19" s="625"/>
+      <c r="AT19" s="625"/>
+      <c r="AU19" s="625"/>
+      <c r="AV19" s="639">
         <f t="shared" ref="AV19" si="8">AA19*AJ19</f>
         <v>0</v>
       </c>
-      <c r="AW19" s="638"/>
-      <c r="AX19" s="638"/>
-      <c r="AY19" s="639"/>
-      <c r="AZ19" s="640">
+      <c r="AW19" s="640"/>
+      <c r="AX19" s="640"/>
+      <c r="AY19" s="641"/>
+      <c r="AZ19" s="642">
         <f t="shared" ref="AZ19" si="9">IF(AE19=0,0,(BD19/AE19))</f>
         <v>0</v>
       </c>
-      <c r="BA19" s="641"/>
-      <c r="BB19" s="641"/>
-      <c r="BC19" s="642"/>
-      <c r="BD19" s="623">
+      <c r="BA19" s="643"/>
+      <c r="BB19" s="643"/>
+      <c r="BC19" s="644"/>
+      <c r="BD19" s="625">
         <f t="shared" ref="BD19" si="10">AA19*AR19</f>
         <v>0</v>
       </c>
-      <c r="BE19" s="623"/>
-      <c r="BF19" s="623"/>
-      <c r="BG19" s="623"/>
-      <c r="BH19" s="623"/>
-      <c r="BI19" s="623"/>
-      <c r="BJ19" s="623"/>
-      <c r="BK19" s="623"/>
-      <c r="BL19" s="624"/>
+      <c r="BE19" s="625"/>
+      <c r="BF19" s="625"/>
+      <c r="BG19" s="625"/>
+      <c r="BH19" s="625"/>
+      <c r="BI19" s="625"/>
+      <c r="BJ19" s="625"/>
+      <c r="BK19" s="625"/>
+      <c r="BL19" s="626"/>
     </row>
     <row r="20" spans="1:66" ht="40.15" customHeight="1">
-      <c r="A20" s="628" t="str">
+      <c r="A20" s="630" t="str">
         <f>BFTC!B11</f>
         <v>KASKİ-07</v>
       </c>
-      <c r="B20" s="629"/>
-      <c r="C20" s="629"/>
-      <c r="D20" s="630"/>
-      <c r="E20" s="631">
+      <c r="B20" s="631"/>
+      <c r="C20" s="631"/>
+      <c r="D20" s="632"/>
+      <c r="E20" s="633">
         <f>BFTC!C11</f>
         <v>0</v>
       </c>
-      <c r="F20" s="632"/>
-      <c r="G20" s="632"/>
-      <c r="H20" s="632"/>
-      <c r="I20" s="632"/>
-      <c r="J20" s="632"/>
-      <c r="K20" s="632"/>
-      <c r="L20" s="632"/>
-      <c r="M20" s="632"/>
-      <c r="N20" s="632"/>
-      <c r="O20" s="632"/>
-      <c r="P20" s="632"/>
-      <c r="Q20" s="632"/>
-      <c r="R20" s="632"/>
-      <c r="S20" s="632"/>
-      <c r="T20" s="633"/>
-      <c r="U20" s="634">
+      <c r="F20" s="634"/>
+      <c r="G20" s="634"/>
+      <c r="H20" s="634"/>
+      <c r="I20" s="634"/>
+      <c r="J20" s="634"/>
+      <c r="K20" s="634"/>
+      <c r="L20" s="634"/>
+      <c r="M20" s="634"/>
+      <c r="N20" s="634"/>
+      <c r="O20" s="634"/>
+      <c r="P20" s="634"/>
+      <c r="Q20" s="634"/>
+      <c r="R20" s="634"/>
+      <c r="S20" s="634"/>
+      <c r="T20" s="635"/>
+      <c r="U20" s="636">
         <f>+BFTC!D11</f>
         <v>0</v>
       </c>
-      <c r="V20" s="635"/>
-      <c r="W20" s="623">
+      <c r="V20" s="637"/>
+      <c r="W20" s="625">
         <f>+BFTC!E11</f>
         <v>0</v>
       </c>
-      <c r="X20" s="623"/>
-      <c r="Y20" s="623"/>
-      <c r="Z20" s="623"/>
-      <c r="AA20" s="623">
+      <c r="X20" s="625"/>
+      <c r="Y20" s="625"/>
+      <c r="Z20" s="625"/>
+      <c r="AA20" s="625">
         <f>+BFTC!F11</f>
         <v>0</v>
       </c>
-      <c r="AB20" s="623"/>
-      <c r="AC20" s="623"/>
-      <c r="AD20" s="623"/>
-      <c r="AE20" s="636">
+      <c r="AB20" s="625"/>
+      <c r="AC20" s="625"/>
+      <c r="AD20" s="625"/>
+      <c r="AE20" s="638">
         <f t="shared" ref="AE20" si="11">AA20*W20</f>
         <v>0</v>
       </c>
-      <c r="AF20" s="636"/>
-      <c r="AG20" s="636"/>
-      <c r="AH20" s="636"/>
-      <c r="AI20" s="636"/>
-      <c r="AJ20" s="623">
+      <c r="AF20" s="638"/>
+      <c r="AG20" s="638"/>
+      <c r="AH20" s="638"/>
+      <c r="AI20" s="638"/>
+      <c r="AJ20" s="625">
         <f>IF(+A20=0,0,HLOOKUP(A20,İcmal!$E$8:$BH$52,43,0))</f>
         <v>0</v>
       </c>
-      <c r="AK20" s="623"/>
-      <c r="AL20" s="623"/>
-      <c r="AM20" s="623"/>
-      <c r="AN20" s="637">
+      <c r="AK20" s="625"/>
+      <c r="AL20" s="625"/>
+      <c r="AM20" s="625"/>
+      <c r="AN20" s="639">
         <f>IF(+A20=0,0,HLOOKUP(A20,İcmal!$E$8:$BH$52,17,0))</f>
         <v>0</v>
       </c>
-      <c r="AO20" s="638"/>
-      <c r="AP20" s="638"/>
-      <c r="AQ20" s="639"/>
-      <c r="AR20" s="623">
+      <c r="AO20" s="640"/>
+      <c r="AP20" s="640"/>
+      <c r="AQ20" s="641"/>
+      <c r="AR20" s="625">
         <f t="shared" ref="AR20" si="12">AJ20+AN20</f>
         <v>0</v>
       </c>
-      <c r="AS20" s="623"/>
-      <c r="AT20" s="623"/>
-      <c r="AU20" s="623"/>
-      <c r="AV20" s="637">
+      <c r="AS20" s="625"/>
+      <c r="AT20" s="625"/>
+      <c r="AU20" s="625"/>
+      <c r="AV20" s="639">
         <f t="shared" ref="AV20" si="13">AA20*AJ20</f>
         <v>0</v>
       </c>
-      <c r="AW20" s="638"/>
-      <c r="AX20" s="638"/>
-      <c r="AY20" s="639"/>
-      <c r="AZ20" s="640">
+      <c r="AW20" s="640"/>
+      <c r="AX20" s="640"/>
+      <c r="AY20" s="641"/>
+      <c r="AZ20" s="642">
         <f t="shared" ref="AZ20" si="14">IF(AE20=0,0,(BD20/AE20))</f>
         <v>0</v>
       </c>
-      <c r="BA20" s="641"/>
-      <c r="BB20" s="641"/>
-      <c r="BC20" s="642"/>
-      <c r="BD20" s="623">
+      <c r="BA20" s="643"/>
+      <c r="BB20" s="643"/>
+      <c r="BC20" s="644"/>
+      <c r="BD20" s="625">
         <f t="shared" ref="BD20" si="15">AA20*AR20</f>
         <v>0</v>
       </c>
-      <c r="BE20" s="623"/>
-      <c r="BF20" s="623"/>
-      <c r="BG20" s="623"/>
-      <c r="BH20" s="623"/>
-      <c r="BI20" s="625"/>
-      <c r="BJ20" s="626"/>
-      <c r="BK20" s="626"/>
-      <c r="BL20" s="627"/>
+      <c r="BE20" s="625"/>
+      <c r="BF20" s="625"/>
+      <c r="BG20" s="625"/>
+      <c r="BH20" s="625"/>
+      <c r="BI20" s="627"/>
+      <c r="BJ20" s="628"/>
+      <c r="BK20" s="628"/>
+      <c r="BL20" s="629"/>
     </row>
     <row r="21" spans="1:66">
-      <c r="A21" s="703"/>
+      <c r="A21" s="705"/>
       <c r="B21" s="510"/>
       <c r="C21" s="510"/>
-      <c r="D21" s="656"/>
-      <c r="E21" s="704"/>
-      <c r="F21" s="706"/>
-      <c r="G21" s="706"/>
-      <c r="H21" s="706"/>
-      <c r="I21" s="706"/>
-      <c r="J21" s="706"/>
-      <c r="K21" s="706"/>
-      <c r="L21" s="706"/>
-      <c r="M21" s="706"/>
-      <c r="N21" s="706"/>
-      <c r="O21" s="706"/>
-      <c r="P21" s="706"/>
-      <c r="Q21" s="706"/>
-      <c r="R21" s="706"/>
-      <c r="S21" s="706"/>
-      <c r="T21" s="705"/>
-      <c r="U21" s="704"/>
-      <c r="V21" s="705"/>
-      <c r="W21" s="625"/>
-      <c r="X21" s="626"/>
-      <c r="Y21" s="626"/>
-      <c r="Z21" s="702"/>
-      <c r="AA21" s="699"/>
-      <c r="AB21" s="700"/>
-      <c r="AC21" s="700"/>
-      <c r="AD21" s="701"/>
-      <c r="AE21" s="625"/>
-      <c r="AF21" s="626"/>
-      <c r="AG21" s="626"/>
-      <c r="AH21" s="626"/>
-      <c r="AI21" s="702"/>
-      <c r="AJ21" s="625"/>
-      <c r="AK21" s="626"/>
-      <c r="AL21" s="626"/>
-      <c r="AM21" s="702"/>
-      <c r="AN21" s="625"/>
-      <c r="AO21" s="626"/>
-      <c r="AP21" s="626"/>
-      <c r="AQ21" s="702"/>
-      <c r="AR21" s="699" t="s">
+      <c r="D21" s="658"/>
+      <c r="E21" s="706"/>
+      <c r="F21" s="708"/>
+      <c r="G21" s="708"/>
+      <c r="H21" s="708"/>
+      <c r="I21" s="708"/>
+      <c r="J21" s="708"/>
+      <c r="K21" s="708"/>
+      <c r="L21" s="708"/>
+      <c r="M21" s="708"/>
+      <c r="N21" s="708"/>
+      <c r="O21" s="708"/>
+      <c r="P21" s="708"/>
+      <c r="Q21" s="708"/>
+      <c r="R21" s="708"/>
+      <c r="S21" s="708"/>
+      <c r="T21" s="707"/>
+      <c r="U21" s="706"/>
+      <c r="V21" s="707"/>
+      <c r="W21" s="627"/>
+      <c r="X21" s="628"/>
+      <c r="Y21" s="628"/>
+      <c r="Z21" s="704"/>
+      <c r="AA21" s="701"/>
+      <c r="AB21" s="702"/>
+      <c r="AC21" s="702"/>
+      <c r="AD21" s="703"/>
+      <c r="AE21" s="627"/>
+      <c r="AF21" s="628"/>
+      <c r="AG21" s="628"/>
+      <c r="AH21" s="628"/>
+      <c r="AI21" s="704"/>
+      <c r="AJ21" s="627"/>
+      <c r="AK21" s="628"/>
+      <c r="AL21" s="628"/>
+      <c r="AM21" s="704"/>
+      <c r="AN21" s="627"/>
+      <c r="AO21" s="628"/>
+      <c r="AP21" s="628"/>
+      <c r="AQ21" s="704"/>
+      <c r="AR21" s="701" t="s">
         <v>153</v>
       </c>
-      <c r="AS21" s="700"/>
-      <c r="AT21" s="700"/>
-      <c r="AU21" s="701"/>
-      <c r="AV21" s="699">
+      <c r="AS21" s="702"/>
+      <c r="AT21" s="702"/>
+      <c r="AU21" s="703"/>
+      <c r="AV21" s="701">
         <f>SUM(AV14:AY20)</f>
         <v>0</v>
       </c>
-      <c r="AW21" s="700"/>
-      <c r="AX21" s="700"/>
-      <c r="AY21" s="701"/>
-      <c r="AZ21" s="699" t="s">
+      <c r="AW21" s="702"/>
+      <c r="AX21" s="702"/>
+      <c r="AY21" s="703"/>
+      <c r="AZ21" s="701" t="s">
         <v>154</v>
       </c>
-      <c r="BA21" s="700"/>
-      <c r="BB21" s="700"/>
-      <c r="BC21" s="701"/>
-      <c r="BD21" s="699">
+      <c r="BA21" s="702"/>
+      <c r="BB21" s="702"/>
+      <c r="BC21" s="703"/>
+      <c r="BD21" s="701">
         <f>SUM(BD14:BH20)</f>
         <v>0</v>
       </c>
-      <c r="BE21" s="700"/>
-      <c r="BF21" s="700"/>
-      <c r="BG21" s="700"/>
-      <c r="BH21" s="701"/>
-      <c r="BI21" s="625"/>
-      <c r="BJ21" s="626"/>
-      <c r="BK21" s="626"/>
-      <c r="BL21" s="627"/>
+      <c r="BE21" s="702"/>
+      <c r="BF21" s="702"/>
+      <c r="BG21" s="702"/>
+      <c r="BH21" s="703"/>
+      <c r="BI21" s="627"/>
+      <c r="BJ21" s="628"/>
+      <c r="BK21" s="628"/>
+      <c r="BL21" s="629"/>
       <c r="BN21" s="40"/>
     </row>
     <row r="22" spans="1:66">
-      <c r="A22" s="696"/>
-      <c r="B22" s="697"/>
-      <c r="C22" s="697"/>
-      <c r="D22" s="697"/>
-      <c r="E22" s="697"/>
-      <c r="F22" s="697"/>
-      <c r="G22" s="697"/>
-      <c r="H22" s="697"/>
-      <c r="I22" s="697"/>
-      <c r="J22" s="697"/>
-      <c r="K22" s="697"/>
-      <c r="L22" s="697"/>
-      <c r="M22" s="697"/>
-      <c r="N22" s="697"/>
-      <c r="O22" s="697"/>
-      <c r="P22" s="697"/>
-      <c r="Q22" s="697"/>
-      <c r="R22" s="697"/>
-      <c r="S22" s="697"/>
-      <c r="T22" s="697"/>
-      <c r="U22" s="697"/>
-      <c r="V22" s="697"/>
-      <c r="W22" s="697"/>
-      <c r="X22" s="697"/>
-      <c r="Y22" s="697"/>
-      <c r="Z22" s="697"/>
-      <c r="AA22" s="697"/>
-      <c r="AB22" s="697"/>
-      <c r="AC22" s="697"/>
-      <c r="AD22" s="697"/>
-      <c r="AE22" s="697"/>
-      <c r="AF22" s="697"/>
-      <c r="AG22" s="697"/>
-      <c r="AH22" s="697"/>
-      <c r="AI22" s="697"/>
-      <c r="AJ22" s="697"/>
-      <c r="AK22" s="697"/>
-      <c r="AL22" s="697"/>
-      <c r="AM22" s="697"/>
-      <c r="AN22" s="697"/>
-      <c r="AO22" s="697"/>
-      <c r="AP22" s="697"/>
-      <c r="AQ22" s="697"/>
-      <c r="AR22" s="697"/>
-      <c r="AS22" s="697"/>
-      <c r="AT22" s="697"/>
-      <c r="AU22" s="697"/>
-      <c r="AV22" s="697"/>
-      <c r="AW22" s="697"/>
-      <c r="AX22" s="697"/>
-      <c r="AY22" s="697"/>
-      <c r="AZ22" s="697"/>
-      <c r="BA22" s="697"/>
-      <c r="BB22" s="697"/>
-      <c r="BC22" s="697"/>
-      <c r="BD22" s="697"/>
-      <c r="BE22" s="697"/>
-      <c r="BF22" s="697"/>
-      <c r="BG22" s="697"/>
-      <c r="BH22" s="697"/>
-      <c r="BI22" s="697"/>
-      <c r="BJ22" s="697"/>
-      <c r="BK22" s="697"/>
-      <c r="BL22" s="698"/>
+      <c r="A22" s="698"/>
+      <c r="B22" s="699"/>
+      <c r="C22" s="699"/>
+      <c r="D22" s="699"/>
+      <c r="E22" s="699"/>
+      <c r="F22" s="699"/>
+      <c r="G22" s="699"/>
+      <c r="H22" s="699"/>
+      <c r="I22" s="699"/>
+      <c r="J22" s="699"/>
+      <c r="K22" s="699"/>
+      <c r="L22" s="699"/>
+      <c r="M22" s="699"/>
+      <c r="N22" s="699"/>
+      <c r="O22" s="699"/>
+      <c r="P22" s="699"/>
+      <c r="Q22" s="699"/>
+      <c r="R22" s="699"/>
+      <c r="S22" s="699"/>
+      <c r="T22" s="699"/>
+      <c r="U22" s="699"/>
+      <c r="V22" s="699"/>
+      <c r="W22" s="699"/>
+      <c r="X22" s="699"/>
+      <c r="Y22" s="699"/>
+      <c r="Z22" s="699"/>
+      <c r="AA22" s="699"/>
+      <c r="AB22" s="699"/>
+      <c r="AC22" s="699"/>
+      <c r="AD22" s="699"/>
+      <c r="AE22" s="699"/>
+      <c r="AF22" s="699"/>
+      <c r="AG22" s="699"/>
+      <c r="AH22" s="699"/>
+      <c r="AI22" s="699"/>
+      <c r="AJ22" s="699"/>
+      <c r="AK22" s="699"/>
+      <c r="AL22" s="699"/>
+      <c r="AM22" s="699"/>
+      <c r="AN22" s="699"/>
+      <c r="AO22" s="699"/>
+      <c r="AP22" s="699"/>
+      <c r="AQ22" s="699"/>
+      <c r="AR22" s="699"/>
+      <c r="AS22" s="699"/>
+      <c r="AT22" s="699"/>
+      <c r="AU22" s="699"/>
+      <c r="AV22" s="699"/>
+      <c r="AW22" s="699"/>
+      <c r="AX22" s="699"/>
+      <c r="AY22" s="699"/>
+      <c r="AZ22" s="699"/>
+      <c r="BA22" s="699"/>
+      <c r="BB22" s="699"/>
+      <c r="BC22" s="699"/>
+      <c r="BD22" s="699"/>
+      <c r="BE22" s="699"/>
+      <c r="BF22" s="699"/>
+      <c r="BG22" s="699"/>
+      <c r="BH22" s="699"/>
+      <c r="BI22" s="699"/>
+      <c r="BJ22" s="699"/>
+      <c r="BK22" s="699"/>
+      <c r="BL22" s="700"/>
     </row>
     <row r="23" spans="1:66" ht="15.75">
-      <c r="A23" s="722" t="s">
+      <c r="A23" s="724" t="s">
         <v>169</v>
       </c>
-      <c r="B23" s="723"/>
-      <c r="C23" s="723"/>
-      <c r="D23" s="723"/>
-      <c r="E23" s="723"/>
-      <c r="F23" s="723"/>
-      <c r="G23" s="723"/>
-      <c r="H23" s="723"/>
-      <c r="I23" s="723"/>
-      <c r="J23" s="723"/>
-      <c r="K23" s="723"/>
-      <c r="L23" s="723"/>
-      <c r="M23" s="723"/>
-      <c r="N23" s="723"/>
-      <c r="O23" s="723"/>
-      <c r="P23" s="723"/>
-      <c r="Q23" s="723"/>
-      <c r="R23" s="723"/>
-      <c r="S23" s="723"/>
-      <c r="T23" s="723"/>
-      <c r="U23" s="723" t="s">
+      <c r="B23" s="725"/>
+      <c r="C23" s="725"/>
+      <c r="D23" s="725"/>
+      <c r="E23" s="725"/>
+      <c r="F23" s="725"/>
+      <c r="G23" s="725"/>
+      <c r="H23" s="725"/>
+      <c r="I23" s="725"/>
+      <c r="J23" s="725"/>
+      <c r="K23" s="725"/>
+      <c r="L23" s="725"/>
+      <c r="M23" s="725"/>
+      <c r="N23" s="725"/>
+      <c r="O23" s="725"/>
+      <c r="P23" s="725"/>
+      <c r="Q23" s="725"/>
+      <c r="R23" s="725"/>
+      <c r="S23" s="725"/>
+      <c r="T23" s="725"/>
+      <c r="U23" s="725" t="s">
         <v>102</v>
       </c>
-      <c r="V23" s="723"/>
-      <c r="W23" s="723"/>
-      <c r="X23" s="723"/>
-      <c r="Y23" s="723"/>
-      <c r="Z23" s="723"/>
-      <c r="AA23" s="723"/>
-      <c r="AB23" s="723"/>
-      <c r="AC23" s="723"/>
-      <c r="AD23" s="723"/>
-      <c r="AE23" s="723"/>
-      <c r="AF23" s="723"/>
-      <c r="AG23" s="723"/>
-      <c r="AH23" s="723"/>
-      <c r="AI23" s="723"/>
-      <c r="AJ23" s="723"/>
-      <c r="AK23" s="723"/>
-      <c r="AL23" s="723"/>
-      <c r="AM23" s="723"/>
-      <c r="AN23" s="723"/>
-      <c r="AO23" s="723"/>
-      <c r="AP23" s="723"/>
-      <c r="AQ23" s="723"/>
-      <c r="AR23" s="723"/>
-      <c r="AS23" s="723" t="s">
+      <c r="V23" s="725"/>
+      <c r="W23" s="725"/>
+      <c r="X23" s="725"/>
+      <c r="Y23" s="725"/>
+      <c r="Z23" s="725"/>
+      <c r="AA23" s="725"/>
+      <c r="AB23" s="725"/>
+      <c r="AC23" s="725"/>
+      <c r="AD23" s="725"/>
+      <c r="AE23" s="725"/>
+      <c r="AF23" s="725"/>
+      <c r="AG23" s="725"/>
+      <c r="AH23" s="725"/>
+      <c r="AI23" s="725"/>
+      <c r="AJ23" s="725"/>
+      <c r="AK23" s="725"/>
+      <c r="AL23" s="725"/>
+      <c r="AM23" s="725"/>
+      <c r="AN23" s="725"/>
+      <c r="AO23" s="725"/>
+      <c r="AP23" s="725"/>
+      <c r="AQ23" s="725"/>
+      <c r="AR23" s="725"/>
+      <c r="AS23" s="725" t="s">
         <v>13</v>
       </c>
-      <c r="AT23" s="723"/>
-      <c r="AU23" s="723"/>
-      <c r="AV23" s="723"/>
-      <c r="AW23" s="723"/>
-      <c r="AX23" s="723"/>
-      <c r="AY23" s="723"/>
-      <c r="AZ23" s="723"/>
-      <c r="BA23" s="723"/>
-      <c r="BB23" s="723"/>
-      <c r="BC23" s="723"/>
-      <c r="BD23" s="723"/>
-      <c r="BE23" s="723"/>
-      <c r="BF23" s="723"/>
-      <c r="BG23" s="723"/>
-      <c r="BH23" s="723"/>
-      <c r="BI23" s="723"/>
-      <c r="BJ23" s="723"/>
-      <c r="BK23" s="723"/>
-      <c r="BL23" s="724"/>
+      <c r="AT23" s="725"/>
+      <c r="AU23" s="725"/>
+      <c r="AV23" s="725"/>
+      <c r="AW23" s="725"/>
+      <c r="AX23" s="725"/>
+      <c r="AY23" s="725"/>
+      <c r="AZ23" s="725"/>
+      <c r="BA23" s="725"/>
+      <c r="BB23" s="725"/>
+      <c r="BC23" s="725"/>
+      <c r="BD23" s="725"/>
+      <c r="BE23" s="725"/>
+      <c r="BF23" s="725"/>
+      <c r="BG23" s="725"/>
+      <c r="BH23" s="725"/>
+      <c r="BI23" s="725"/>
+      <c r="BJ23" s="725"/>
+      <c r="BK23" s="725"/>
+      <c r="BL23" s="726"/>
     </row>
     <row r="24" spans="1:66" ht="14.45" customHeight="1">
       <c r="A24" s="104"/>
-      <c r="B24" s="725">
+      <c r="B24" s="727">
         <f>Bilgiler!D14</f>
         <v>0</v>
       </c>
-      <c r="C24" s="725"/>
-      <c r="D24" s="725"/>
-      <c r="E24" s="725"/>
-      <c r="F24" s="725"/>
-      <c r="G24" s="725"/>
-      <c r="H24" s="725"/>
-      <c r="I24" s="725"/>
-      <c r="J24" s="725"/>
-      <c r="K24" s="725"/>
-      <c r="L24" s="725"/>
-      <c r="M24" s="725"/>
-      <c r="N24" s="725"/>
-      <c r="O24" s="725"/>
-      <c r="P24" s="725"/>
-      <c r="Q24" s="725"/>
-      <c r="R24" s="725"/>
-      <c r="S24" s="725"/>
-      <c r="T24" s="726"/>
-      <c r="U24" s="727"/>
-      <c r="V24" s="728"/>
-      <c r="W24" s="728"/>
-      <c r="X24" s="728"/>
-      <c r="Y24" s="728"/>
-      <c r="Z24" s="728"/>
-      <c r="AA24" s="728"/>
-      <c r="AB24" s="728"/>
-      <c r="AC24" s="728"/>
-      <c r="AD24" s="728"/>
-      <c r="AE24" s="728"/>
-      <c r="AF24" s="728"/>
-      <c r="AG24" s="728"/>
-      <c r="AH24" s="728"/>
-      <c r="AI24" s="728"/>
-      <c r="AJ24" s="728"/>
-      <c r="AK24" s="728"/>
-      <c r="AL24" s="728"/>
-      <c r="AM24" s="728"/>
-      <c r="AN24" s="728"/>
-      <c r="AO24" s="728"/>
-      <c r="AP24" s="728"/>
-      <c r="AQ24" s="728"/>
-      <c r="AR24" s="729"/>
-      <c r="AS24" s="707">
+      <c r="C24" s="727"/>
+      <c r="D24" s="727"/>
+      <c r="E24" s="727"/>
+      <c r="F24" s="727"/>
+      <c r="G24" s="727"/>
+      <c r="H24" s="727"/>
+      <c r="I24" s="727"/>
+      <c r="J24" s="727"/>
+      <c r="K24" s="727"/>
+      <c r="L24" s="727"/>
+      <c r="M24" s="727"/>
+      <c r="N24" s="727"/>
+      <c r="O24" s="727"/>
+      <c r="P24" s="727"/>
+      <c r="Q24" s="727"/>
+      <c r="R24" s="727"/>
+      <c r="S24" s="727"/>
+      <c r="T24" s="728"/>
+      <c r="U24" s="729"/>
+      <c r="V24" s="730"/>
+      <c r="W24" s="730"/>
+      <c r="X24" s="730"/>
+      <c r="Y24" s="730"/>
+      <c r="Z24" s="730"/>
+      <c r="AA24" s="730"/>
+      <c r="AB24" s="730"/>
+      <c r="AC24" s="730"/>
+      <c r="AD24" s="730"/>
+      <c r="AE24" s="730"/>
+      <c r="AF24" s="730"/>
+      <c r="AG24" s="730"/>
+      <c r="AH24" s="730"/>
+      <c r="AI24" s="730"/>
+      <c r="AJ24" s="730"/>
+      <c r="AK24" s="730"/>
+      <c r="AL24" s="730"/>
+      <c r="AM24" s="730"/>
+      <c r="AN24" s="730"/>
+      <c r="AO24" s="730"/>
+      <c r="AP24" s="730"/>
+      <c r="AQ24" s="730"/>
+      <c r="AR24" s="731"/>
+      <c r="AS24" s="709">
         <f>Bilgiler!D3</f>
         <v>0</v>
       </c>
-      <c r="AT24" s="708"/>
-      <c r="AU24" s="708"/>
-      <c r="AV24" s="708"/>
-      <c r="AW24" s="708"/>
-      <c r="AX24" s="708"/>
-      <c r="AY24" s="708"/>
-      <c r="AZ24" s="708"/>
-      <c r="BA24" s="708"/>
-      <c r="BB24" s="708"/>
-      <c r="BC24" s="708"/>
-      <c r="BD24" s="708"/>
-      <c r="BE24" s="708"/>
-      <c r="BF24" s="708"/>
-      <c r="BG24" s="708"/>
-      <c r="BH24" s="708"/>
-      <c r="BI24" s="708"/>
-      <c r="BJ24" s="708"/>
-      <c r="BK24" s="708"/>
-      <c r="BL24" s="709"/>
+      <c r="AT24" s="710"/>
+      <c r="AU24" s="710"/>
+      <c r="AV24" s="710"/>
+      <c r="AW24" s="710"/>
+      <c r="AX24" s="710"/>
+      <c r="AY24" s="710"/>
+      <c r="AZ24" s="710"/>
+      <c r="BA24" s="710"/>
+      <c r="BB24" s="710"/>
+      <c r="BC24" s="710"/>
+      <c r="BD24" s="710"/>
+      <c r="BE24" s="710"/>
+      <c r="BF24" s="710"/>
+      <c r="BG24" s="710"/>
+      <c r="BH24" s="710"/>
+      <c r="BI24" s="710"/>
+      <c r="BJ24" s="710"/>
+      <c r="BK24" s="710"/>
+      <c r="BL24" s="711"/>
     </row>
     <row r="25" spans="1:66" ht="14.45" customHeight="1">
       <c r="A25" s="105"/>
       <c r="B25" s="103"/>
-      <c r="C25" s="717">
+      <c r="C25" s="719">
         <f>Bilgiler!D15</f>
         <v>0</v>
       </c>
-      <c r="D25" s="717"/>
-      <c r="E25" s="717"/>
-      <c r="F25" s="717"/>
-      <c r="G25" s="717"/>
-      <c r="H25" s="717"/>
-      <c r="I25" s="717"/>
-      <c r="J25" s="717"/>
-      <c r="K25" s="717"/>
-      <c r="L25" s="717"/>
-      <c r="M25" s="717"/>
-      <c r="N25" s="717"/>
-      <c r="O25" s="717"/>
-      <c r="P25" s="717"/>
-      <c r="Q25" s="717"/>
-      <c r="R25" s="717"/>
-      <c r="S25" s="717"/>
-      <c r="T25" s="718"/>
-      <c r="U25" s="730"/>
-      <c r="V25" s="731"/>
-      <c r="W25" s="731"/>
-      <c r="X25" s="731"/>
-      <c r="Y25" s="731"/>
-      <c r="Z25" s="731"/>
-      <c r="AA25" s="731"/>
-      <c r="AB25" s="731"/>
-      <c r="AC25" s="731"/>
-      <c r="AD25" s="731"/>
-      <c r="AE25" s="731"/>
-      <c r="AF25" s="731"/>
-      <c r="AG25" s="731"/>
-      <c r="AH25" s="731"/>
-      <c r="AI25" s="731"/>
-      <c r="AJ25" s="731"/>
-      <c r="AK25" s="731"/>
-      <c r="AL25" s="731"/>
-      <c r="AM25" s="731"/>
-      <c r="AN25" s="731"/>
-      <c r="AO25" s="731"/>
-      <c r="AP25" s="731"/>
-      <c r="AQ25" s="731"/>
-      <c r="AR25" s="732"/>
-      <c r="AS25" s="710"/>
-      <c r="AT25" s="711"/>
-      <c r="AU25" s="711"/>
-      <c r="AV25" s="711"/>
-      <c r="AW25" s="711"/>
-      <c r="AX25" s="711"/>
-      <c r="AY25" s="711"/>
-      <c r="AZ25" s="711"/>
-      <c r="BA25" s="711"/>
-      <c r="BB25" s="711"/>
-      <c r="BC25" s="711"/>
-      <c r="BD25" s="711"/>
-      <c r="BE25" s="711"/>
-      <c r="BF25" s="711"/>
-      <c r="BG25" s="711"/>
-      <c r="BH25" s="711"/>
-      <c r="BI25" s="711"/>
-      <c r="BJ25" s="711"/>
-      <c r="BK25" s="711"/>
-      <c r="BL25" s="712"/>
+      <c r="D25" s="719"/>
+      <c r="E25" s="719"/>
+      <c r="F25" s="719"/>
+      <c r="G25" s="719"/>
+      <c r="H25" s="719"/>
+      <c r="I25" s="719"/>
+      <c r="J25" s="719"/>
+      <c r="K25" s="719"/>
+      <c r="L25" s="719"/>
+      <c r="M25" s="719"/>
+      <c r="N25" s="719"/>
+      <c r="O25" s="719"/>
+      <c r="P25" s="719"/>
+      <c r="Q25" s="719"/>
+      <c r="R25" s="719"/>
+      <c r="S25" s="719"/>
+      <c r="T25" s="720"/>
+      <c r="U25" s="732"/>
+      <c r="V25" s="733"/>
+      <c r="W25" s="733"/>
+      <c r="X25" s="733"/>
+      <c r="Y25" s="733"/>
+      <c r="Z25" s="733"/>
+      <c r="AA25" s="733"/>
+      <c r="AB25" s="733"/>
+      <c r="AC25" s="733"/>
+      <c r="AD25" s="733"/>
+      <c r="AE25" s="733"/>
+      <c r="AF25" s="733"/>
+      <c r="AG25" s="733"/>
+      <c r="AH25" s="733"/>
+      <c r="AI25" s="733"/>
+      <c r="AJ25" s="733"/>
+      <c r="AK25" s="733"/>
+      <c r="AL25" s="733"/>
+      <c r="AM25" s="733"/>
+      <c r="AN25" s="733"/>
+      <c r="AO25" s="733"/>
+      <c r="AP25" s="733"/>
+      <c r="AQ25" s="733"/>
+      <c r="AR25" s="734"/>
+      <c r="AS25" s="712"/>
+      <c r="AT25" s="713"/>
+      <c r="AU25" s="713"/>
+      <c r="AV25" s="713"/>
+      <c r="AW25" s="713"/>
+      <c r="AX25" s="713"/>
+      <c r="AY25" s="713"/>
+      <c r="AZ25" s="713"/>
+      <c r="BA25" s="713"/>
+      <c r="BB25" s="713"/>
+      <c r="BC25" s="713"/>
+      <c r="BD25" s="713"/>
+      <c r="BE25" s="713"/>
+      <c r="BF25" s="713"/>
+      <c r="BG25" s="713"/>
+      <c r="BH25" s="713"/>
+      <c r="BI25" s="713"/>
+      <c r="BJ25" s="713"/>
+      <c r="BK25" s="713"/>
+      <c r="BL25" s="714"/>
     </row>
     <row r="26" spans="1:66" ht="14.45" customHeight="1">
       <c r="A26" s="105"/>
@@ -24386,50 +23347,50 @@
       <c r="R26" s="103"/>
       <c r="S26" s="103"/>
       <c r="T26" s="98"/>
-      <c r="U26" s="730"/>
-      <c r="V26" s="731"/>
-      <c r="W26" s="731"/>
-      <c r="X26" s="731"/>
-      <c r="Y26" s="731"/>
-      <c r="Z26" s="731"/>
-      <c r="AA26" s="731"/>
-      <c r="AB26" s="731"/>
-      <c r="AC26" s="731"/>
-      <c r="AD26" s="731"/>
-      <c r="AE26" s="731"/>
-      <c r="AF26" s="731"/>
-      <c r="AG26" s="731"/>
-      <c r="AH26" s="731"/>
-      <c r="AI26" s="731"/>
-      <c r="AJ26" s="731"/>
-      <c r="AK26" s="731"/>
-      <c r="AL26" s="731"/>
-      <c r="AM26" s="731"/>
-      <c r="AN26" s="731"/>
-      <c r="AO26" s="731"/>
-      <c r="AP26" s="731"/>
-      <c r="AQ26" s="731"/>
-      <c r="AR26" s="732"/>
-      <c r="AS26" s="710"/>
-      <c r="AT26" s="711"/>
-      <c r="AU26" s="711"/>
-      <c r="AV26" s="711"/>
-      <c r="AW26" s="711"/>
-      <c r="AX26" s="711"/>
-      <c r="AY26" s="711"/>
-      <c r="AZ26" s="711"/>
-      <c r="BA26" s="711"/>
-      <c r="BB26" s="711"/>
-      <c r="BC26" s="711"/>
-      <c r="BD26" s="711"/>
-      <c r="BE26" s="711"/>
-      <c r="BF26" s="711"/>
-      <c r="BG26" s="711"/>
-      <c r="BH26" s="711"/>
-      <c r="BI26" s="711"/>
-      <c r="BJ26" s="711"/>
-      <c r="BK26" s="711"/>
-      <c r="BL26" s="712"/>
+      <c r="U26" s="732"/>
+      <c r="V26" s="733"/>
+      <c r="W26" s="733"/>
+      <c r="X26" s="733"/>
+      <c r="Y26" s="733"/>
+      <c r="Z26" s="733"/>
+      <c r="AA26" s="733"/>
+      <c r="AB26" s="733"/>
+      <c r="AC26" s="733"/>
+      <c r="AD26" s="733"/>
+      <c r="AE26" s="733"/>
+      <c r="AF26" s="733"/>
+      <c r="AG26" s="733"/>
+      <c r="AH26" s="733"/>
+      <c r="AI26" s="733"/>
+      <c r="AJ26" s="733"/>
+      <c r="AK26" s="733"/>
+      <c r="AL26" s="733"/>
+      <c r="AM26" s="733"/>
+      <c r="AN26" s="733"/>
+      <c r="AO26" s="733"/>
+      <c r="AP26" s="733"/>
+      <c r="AQ26" s="733"/>
+      <c r="AR26" s="734"/>
+      <c r="AS26" s="712"/>
+      <c r="AT26" s="713"/>
+      <c r="AU26" s="713"/>
+      <c r="AV26" s="713"/>
+      <c r="AW26" s="713"/>
+      <c r="AX26" s="713"/>
+      <c r="AY26" s="713"/>
+      <c r="AZ26" s="713"/>
+      <c r="BA26" s="713"/>
+      <c r="BB26" s="713"/>
+      <c r="BC26" s="713"/>
+      <c r="BD26" s="713"/>
+      <c r="BE26" s="713"/>
+      <c r="BF26" s="713"/>
+      <c r="BG26" s="713"/>
+      <c r="BH26" s="713"/>
+      <c r="BI26" s="713"/>
+      <c r="BJ26" s="713"/>
+      <c r="BK26" s="713"/>
+      <c r="BL26" s="714"/>
     </row>
     <row r="27" spans="1:66" ht="14.45" customHeight="1">
       <c r="A27" s="104"/>
@@ -24452,50 +23413,50 @@
       <c r="R27" s="102"/>
       <c r="S27" s="102"/>
       <c r="T27" s="99"/>
-      <c r="U27" s="716"/>
-      <c r="V27" s="717"/>
-      <c r="W27" s="717"/>
-      <c r="X27" s="717"/>
-      <c r="Y27" s="717"/>
-      <c r="Z27" s="717"/>
-      <c r="AA27" s="717"/>
-      <c r="AB27" s="717"/>
-      <c r="AC27" s="717"/>
-      <c r="AD27" s="717"/>
-      <c r="AE27" s="717"/>
-      <c r="AF27" s="717"/>
-      <c r="AG27" s="717"/>
-      <c r="AH27" s="717"/>
-      <c r="AI27" s="717"/>
-      <c r="AJ27" s="717"/>
-      <c r="AK27" s="717"/>
-      <c r="AL27" s="717"/>
-      <c r="AM27" s="717"/>
-      <c r="AN27" s="717"/>
-      <c r="AO27" s="717"/>
-      <c r="AP27" s="717"/>
-      <c r="AQ27" s="717"/>
-      <c r="AR27" s="718"/>
-      <c r="AS27" s="710"/>
-      <c r="AT27" s="711"/>
-      <c r="AU27" s="711"/>
-      <c r="AV27" s="711"/>
-      <c r="AW27" s="711"/>
-      <c r="AX27" s="711"/>
-      <c r="AY27" s="711"/>
-      <c r="AZ27" s="711"/>
-      <c r="BA27" s="711"/>
-      <c r="BB27" s="711"/>
-      <c r="BC27" s="711"/>
-      <c r="BD27" s="711"/>
-      <c r="BE27" s="711"/>
-      <c r="BF27" s="711"/>
-      <c r="BG27" s="711"/>
-      <c r="BH27" s="711"/>
-      <c r="BI27" s="711"/>
-      <c r="BJ27" s="711"/>
-      <c r="BK27" s="711"/>
-      <c r="BL27" s="712"/>
+      <c r="U27" s="718"/>
+      <c r="V27" s="719"/>
+      <c r="W27" s="719"/>
+      <c r="X27" s="719"/>
+      <c r="Y27" s="719"/>
+      <c r="Z27" s="719"/>
+      <c r="AA27" s="719"/>
+      <c r="AB27" s="719"/>
+      <c r="AC27" s="719"/>
+      <c r="AD27" s="719"/>
+      <c r="AE27" s="719"/>
+      <c r="AF27" s="719"/>
+      <c r="AG27" s="719"/>
+      <c r="AH27" s="719"/>
+      <c r="AI27" s="719"/>
+      <c r="AJ27" s="719"/>
+      <c r="AK27" s="719"/>
+      <c r="AL27" s="719"/>
+      <c r="AM27" s="719"/>
+      <c r="AN27" s="719"/>
+      <c r="AO27" s="719"/>
+      <c r="AP27" s="719"/>
+      <c r="AQ27" s="719"/>
+      <c r="AR27" s="720"/>
+      <c r="AS27" s="712"/>
+      <c r="AT27" s="713"/>
+      <c r="AU27" s="713"/>
+      <c r="AV27" s="713"/>
+      <c r="AW27" s="713"/>
+      <c r="AX27" s="713"/>
+      <c r="AY27" s="713"/>
+      <c r="AZ27" s="713"/>
+      <c r="BA27" s="713"/>
+      <c r="BB27" s="713"/>
+      <c r="BC27" s="713"/>
+      <c r="BD27" s="713"/>
+      <c r="BE27" s="713"/>
+      <c r="BF27" s="713"/>
+      <c r="BG27" s="713"/>
+      <c r="BH27" s="713"/>
+      <c r="BI27" s="713"/>
+      <c r="BJ27" s="713"/>
+      <c r="BK27" s="713"/>
+      <c r="BL27" s="714"/>
     </row>
     <row r="28" spans="1:66" ht="14.45" customHeight="1">
       <c r="A28" s="106"/>
@@ -24518,50 +23479,50 @@
       <c r="R28" s="102"/>
       <c r="S28" s="102"/>
       <c r="T28" s="99"/>
-      <c r="U28" s="716"/>
-      <c r="V28" s="717"/>
-      <c r="W28" s="717"/>
-      <c r="X28" s="717"/>
-      <c r="Y28" s="717"/>
-      <c r="Z28" s="717"/>
-      <c r="AA28" s="717"/>
-      <c r="AB28" s="717"/>
-      <c r="AC28" s="717"/>
-      <c r="AD28" s="717"/>
-      <c r="AE28" s="717"/>
-      <c r="AF28" s="717"/>
-      <c r="AG28" s="717"/>
-      <c r="AH28" s="717"/>
-      <c r="AI28" s="717"/>
-      <c r="AJ28" s="717"/>
-      <c r="AK28" s="717"/>
-      <c r="AL28" s="717"/>
-      <c r="AM28" s="717"/>
-      <c r="AN28" s="717"/>
-      <c r="AO28" s="717"/>
-      <c r="AP28" s="717"/>
-      <c r="AQ28" s="717"/>
-      <c r="AR28" s="718"/>
-      <c r="AS28" s="710"/>
-      <c r="AT28" s="711"/>
-      <c r="AU28" s="711"/>
-      <c r="AV28" s="711"/>
-      <c r="AW28" s="711"/>
-      <c r="AX28" s="711"/>
-      <c r="AY28" s="711"/>
-      <c r="AZ28" s="711"/>
-      <c r="BA28" s="711"/>
-      <c r="BB28" s="711"/>
-      <c r="BC28" s="711"/>
-      <c r="BD28" s="711"/>
-      <c r="BE28" s="711"/>
-      <c r="BF28" s="711"/>
-      <c r="BG28" s="711"/>
-      <c r="BH28" s="711"/>
-      <c r="BI28" s="711"/>
-      <c r="BJ28" s="711"/>
-      <c r="BK28" s="711"/>
-      <c r="BL28" s="712"/>
+      <c r="U28" s="718"/>
+      <c r="V28" s="719"/>
+      <c r="W28" s="719"/>
+      <c r="X28" s="719"/>
+      <c r="Y28" s="719"/>
+      <c r="Z28" s="719"/>
+      <c r="AA28" s="719"/>
+      <c r="AB28" s="719"/>
+      <c r="AC28" s="719"/>
+      <c r="AD28" s="719"/>
+      <c r="AE28" s="719"/>
+      <c r="AF28" s="719"/>
+      <c r="AG28" s="719"/>
+      <c r="AH28" s="719"/>
+      <c r="AI28" s="719"/>
+      <c r="AJ28" s="719"/>
+      <c r="AK28" s="719"/>
+      <c r="AL28" s="719"/>
+      <c r="AM28" s="719"/>
+      <c r="AN28" s="719"/>
+      <c r="AO28" s="719"/>
+      <c r="AP28" s="719"/>
+      <c r="AQ28" s="719"/>
+      <c r="AR28" s="720"/>
+      <c r="AS28" s="712"/>
+      <c r="AT28" s="713"/>
+      <c r="AU28" s="713"/>
+      <c r="AV28" s="713"/>
+      <c r="AW28" s="713"/>
+      <c r="AX28" s="713"/>
+      <c r="AY28" s="713"/>
+      <c r="AZ28" s="713"/>
+      <c r="BA28" s="713"/>
+      <c r="BB28" s="713"/>
+      <c r="BC28" s="713"/>
+      <c r="BD28" s="713"/>
+      <c r="BE28" s="713"/>
+      <c r="BF28" s="713"/>
+      <c r="BG28" s="713"/>
+      <c r="BH28" s="713"/>
+      <c r="BI28" s="713"/>
+      <c r="BJ28" s="713"/>
+      <c r="BK28" s="713"/>
+      <c r="BL28" s="714"/>
     </row>
     <row r="29" spans="1:66" ht="15" customHeight="1" thickBot="1">
       <c r="A29" s="107"/>
@@ -24584,50 +23545,50 @@
       <c r="R29" s="100"/>
       <c r="S29" s="100"/>
       <c r="T29" s="101"/>
-      <c r="U29" s="719"/>
-      <c r="V29" s="720"/>
-      <c r="W29" s="720"/>
-      <c r="X29" s="720"/>
-      <c r="Y29" s="720"/>
-      <c r="Z29" s="720"/>
-      <c r="AA29" s="720"/>
-      <c r="AB29" s="720"/>
-      <c r="AC29" s="720"/>
-      <c r="AD29" s="720"/>
-      <c r="AE29" s="720"/>
-      <c r="AF29" s="720"/>
-      <c r="AG29" s="720"/>
-      <c r="AH29" s="720"/>
-      <c r="AI29" s="720"/>
-      <c r="AJ29" s="720"/>
-      <c r="AK29" s="720"/>
-      <c r="AL29" s="720"/>
-      <c r="AM29" s="720"/>
-      <c r="AN29" s="720"/>
-      <c r="AO29" s="720"/>
-      <c r="AP29" s="720"/>
-      <c r="AQ29" s="720"/>
-      <c r="AR29" s="721"/>
-      <c r="AS29" s="713"/>
-      <c r="AT29" s="714"/>
-      <c r="AU29" s="714"/>
-      <c r="AV29" s="714"/>
-      <c r="AW29" s="714"/>
-      <c r="AX29" s="714"/>
-      <c r="AY29" s="714"/>
-      <c r="AZ29" s="714"/>
-      <c r="BA29" s="714"/>
-      <c r="BB29" s="714"/>
-      <c r="BC29" s="714"/>
-      <c r="BD29" s="714"/>
-      <c r="BE29" s="714"/>
-      <c r="BF29" s="714"/>
-      <c r="BG29" s="714"/>
-      <c r="BH29" s="714"/>
-      <c r="BI29" s="714"/>
-      <c r="BJ29" s="714"/>
-      <c r="BK29" s="714"/>
-      <c r="BL29" s="715"/>
+      <c r="U29" s="721"/>
+      <c r="V29" s="722"/>
+      <c r="W29" s="722"/>
+      <c r="X29" s="722"/>
+      <c r="Y29" s="722"/>
+      <c r="Z29" s="722"/>
+      <c r="AA29" s="722"/>
+      <c r="AB29" s="722"/>
+      <c r="AC29" s="722"/>
+      <c r="AD29" s="722"/>
+      <c r="AE29" s="722"/>
+      <c r="AF29" s="722"/>
+      <c r="AG29" s="722"/>
+      <c r="AH29" s="722"/>
+      <c r="AI29" s="722"/>
+      <c r="AJ29" s="722"/>
+      <c r="AK29" s="722"/>
+      <c r="AL29" s="722"/>
+      <c r="AM29" s="722"/>
+      <c r="AN29" s="722"/>
+      <c r="AO29" s="722"/>
+      <c r="AP29" s="722"/>
+      <c r="AQ29" s="722"/>
+      <c r="AR29" s="723"/>
+      <c r="AS29" s="715"/>
+      <c r="AT29" s="716"/>
+      <c r="AU29" s="716"/>
+      <c r="AV29" s="716"/>
+      <c r="AW29" s="716"/>
+      <c r="AX29" s="716"/>
+      <c r="AY29" s="716"/>
+      <c r="AZ29" s="716"/>
+      <c r="BA29" s="716"/>
+      <c r="BB29" s="716"/>
+      <c r="BC29" s="716"/>
+      <c r="BD29" s="716"/>
+      <c r="BE29" s="716"/>
+      <c r="BF29" s="716"/>
+      <c r="BG29" s="716"/>
+      <c r="BH29" s="716"/>
+      <c r="BI29" s="716"/>
+      <c r="BJ29" s="716"/>
+      <c r="BK29" s="716"/>
+      <c r="BL29" s="717"/>
     </row>
     <row r="30" spans="1:66" ht="15.75" thickTop="1"/>
   </sheetData>
@@ -24837,44 +23798,44 @@
     <row r="2" spans="1:18" ht="19.5" customHeight="1">
       <c r="A2" s="111"/>
       <c r="B2" s="112"/>
-      <c r="C2" s="784">
+      <c r="C2" s="786">
         <f>Bilgiler!D1</f>
         <v>0</v>
       </c>
-      <c r="D2" s="784"/>
-      <c r="E2" s="784"/>
-      <c r="F2" s="784"/>
-      <c r="G2" s="784"/>
-      <c r="H2" s="784"/>
-      <c r="I2" s="785"/>
+      <c r="D2" s="786"/>
+      <c r="E2" s="786"/>
+      <c r="F2" s="786"/>
+      <c r="G2" s="786"/>
+      <c r="H2" s="786"/>
+      <c r="I2" s="787"/>
     </row>
     <row r="3" spans="1:18" ht="21.75" customHeight="1">
       <c r="A3" s="111" t="s">
         <v>185</v>
       </c>
       <c r="B3" s="112"/>
-      <c r="C3" s="784"/>
-      <c r="D3" s="784"/>
-      <c r="E3" s="784"/>
-      <c r="F3" s="784"/>
-      <c r="G3" s="784"/>
-      <c r="H3" s="784"/>
-      <c r="I3" s="785"/>
+      <c r="C3" s="786"/>
+      <c r="D3" s="786"/>
+      <c r="E3" s="786"/>
+      <c r="F3" s="786"/>
+      <c r="G3" s="786"/>
+      <c r="H3" s="786"/>
+      <c r="I3" s="787"/>
     </row>
     <row r="4" spans="1:18" s="115" customFormat="1" ht="30" customHeight="1">
       <c r="A4" s="113" t="s">
         <v>186</v>
       </c>
       <c r="B4" s="114"/>
-      <c r="C4" s="784" t="s">
+      <c r="C4" s="786" t="s">
         <v>187</v>
       </c>
-      <c r="D4" s="784"/>
-      <c r="E4" s="784"/>
-      <c r="F4" s="784"/>
-      <c r="G4" s="784"/>
-      <c r="H4" s="784"/>
-      <c r="I4" s="785"/>
+      <c r="D4" s="786"/>
+      <c r="E4" s="786"/>
+      <c r="F4" s="786"/>
+      <c r="G4" s="786"/>
+      <c r="H4" s="786"/>
+      <c r="I4" s="787"/>
       <c r="Q4"/>
       <c r="R4"/>
     </row>
@@ -24883,16 +23844,16 @@
       <c r="I5" s="19"/>
     </row>
     <row r="6" spans="1:18" ht="18" customHeight="1">
-      <c r="A6" s="786">
+      <c r="A6" s="788">
         <f>Bilgiler!D2</f>
         <v>0</v>
       </c>
-      <c r="B6" s="787"/>
-      <c r="C6" s="787"/>
-      <c r="D6" s="787"/>
-      <c r="E6" s="787"/>
-      <c r="F6" s="787"/>
-      <c r="G6" s="787"/>
+      <c r="B6" s="789"/>
+      <c r="C6" s="789"/>
+      <c r="D6" s="789"/>
+      <c r="E6" s="789"/>
+      <c r="F6" s="789"/>
+      <c r="G6" s="789"/>
       <c r="H6" s="2" t="s">
         <v>8</v>
       </c>
@@ -24902,13 +23863,13 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="18" customHeight="1">
-      <c r="A7" s="786"/>
-      <c r="B7" s="787"/>
-      <c r="C7" s="787"/>
-      <c r="D7" s="787"/>
-      <c r="E7" s="787"/>
-      <c r="F7" s="787"/>
-      <c r="G7" s="787"/>
+      <c r="A7" s="788"/>
+      <c r="B7" s="789"/>
+      <c r="C7" s="789"/>
+      <c r="D7" s="789"/>
+      <c r="E7" s="789"/>
+      <c r="F7" s="789"/>
+      <c r="G7" s="789"/>
       <c r="H7" s="2" t="s">
         <v>18</v>
       </c>
@@ -25013,7 +23974,7 @@
       </c>
     </row>
     <row r="10" spans="1:18" ht="22.5" customHeight="1">
-      <c r="A10" s="788" t="s">
+      <c r="A10" s="790" t="s">
         <v>191</v>
       </c>
       <c r="B10" s="255"/>
@@ -25054,7 +24015,7 @@
       </c>
     </row>
     <row r="11" spans="1:18" ht="30" customHeight="1">
-      <c r="A11" s="789">
+      <c r="A11" s="791">
         <f>Çarşaf!AV21</f>
         <v>0</v>
       </c>
@@ -25068,7 +24029,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="254"/>
-      <c r="I11" s="790"/>
+      <c r="I11" s="792"/>
       <c r="L11" s="133" t="s">
         <v>214</v>
       </c>
@@ -25095,30 +24056,30 @@
       </c>
     </row>
     <row r="12" spans="1:18">
-      <c r="A12" s="735" t="s">
+      <c r="A12" s="737" t="s">
         <v>222</v>
       </c>
-      <c r="B12" s="736"/>
-      <c r="C12" s="736"/>
-      <c r="D12" s="736"/>
-      <c r="E12" s="739">
+      <c r="B12" s="738"/>
+      <c r="C12" s="738"/>
+      <c r="D12" s="738"/>
+      <c r="E12" s="741">
         <f>Bilgiler!D25</f>
         <v>0</v>
       </c>
-      <c r="F12" s="740">
+      <c r="F12" s="742">
         <f>Bilgiler!D26</f>
         <v>0</v>
       </c>
-      <c r="G12" s="741"/>
-      <c r="H12" s="741"/>
-      <c r="I12" s="742"/>
+      <c r="G12" s="743"/>
+      <c r="H12" s="743"/>
+      <c r="I12" s="744"/>
       <c r="R12" s="140"/>
     </row>
     <row r="13" spans="1:18">
-      <c r="A13" s="737"/>
-      <c r="B13" s="738"/>
-      <c r="C13" s="738"/>
-      <c r="D13" s="738"/>
+      <c r="A13" s="739"/>
+      <c r="B13" s="740"/>
+      <c r="C13" s="740"/>
+      <c r="D13" s="740"/>
       <c r="E13" s="559"/>
       <c r="F13" s="559"/>
       <c r="G13" s="559"/>
@@ -25127,17 +24088,17 @@
       <c r="R13" s="140"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1">
-      <c r="A14" s="743" t="s">
+      <c r="A14" s="745" t="s">
         <v>194</v>
       </c>
-      <c r="B14" s="744"/>
-      <c r="C14" s="744"/>
-      <c r="D14" s="744"/>
-      <c r="E14" s="744"/>
-      <c r="F14" s="744"/>
-      <c r="G14" s="744"/>
-      <c r="H14" s="744"/>
-      <c r="I14" s="745"/>
+      <c r="B14" s="746"/>
+      <c r="C14" s="746"/>
+      <c r="D14" s="746"/>
+      <c r="E14" s="746"/>
+      <c r="F14" s="746"/>
+      <c r="G14" s="746"/>
+      <c r="H14" s="746"/>
+      <c r="I14" s="747"/>
       <c r="L14" s="377" t="s">
         <v>217</v>
       </c>
@@ -25146,52 +24107,52 @@
         <v>219</v>
       </c>
       <c r="O14" s="34"/>
-      <c r="P14" s="733" t="s">
+      <c r="P14" s="735" t="s">
         <v>204</v>
       </c>
-      <c r="Q14" s="733"/>
+      <c r="Q14" s="735"/>
       <c r="R14" s="149">
         <f>SUM(R8:R11)</f>
         <v>0.28000000000000003</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="23.25" customHeight="1">
-      <c r="A15" s="743" t="s">
+      <c r="A15" s="745" t="s">
         <v>195</v>
       </c>
-      <c r="B15" s="744"/>
-      <c r="C15" s="744"/>
-      <c r="D15" s="744"/>
-      <c r="E15" s="744"/>
-      <c r="F15" s="744"/>
-      <c r="G15" s="744"/>
-      <c r="H15" s="744"/>
-      <c r="I15" s="745"/>
+      <c r="B15" s="746"/>
+      <c r="C15" s="746"/>
+      <c r="D15" s="746"/>
+      <c r="E15" s="746"/>
+      <c r="F15" s="746"/>
+      <c r="G15" s="746"/>
+      <c r="H15" s="746"/>
+      <c r="I15" s="747"/>
       <c r="L15" s="377"/>
       <c r="M15" s="141"/>
       <c r="N15" s="355"/>
       <c r="O15" s="34"/>
-      <c r="P15" s="733" t="s">
+      <c r="P15" s="735" t="s">
         <v>220</v>
       </c>
-      <c r="Q15" s="733"/>
+      <c r="Q15" s="735"/>
       <c r="R15" s="150">
         <f>N16*(R14-1)</f>
         <v>-0.64800000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="23.25" customHeight="1">
-      <c r="A16" s="743" t="s">
+      <c r="A16" s="745" t="s">
         <v>196</v>
       </c>
-      <c r="B16" s="744"/>
-      <c r="C16" s="744"/>
-      <c r="D16" s="744"/>
-      <c r="E16" s="744"/>
-      <c r="F16" s="744"/>
-      <c r="G16" s="744"/>
-      <c r="H16" s="744"/>
-      <c r="I16" s="745"/>
+      <c r="B16" s="746"/>
+      <c r="C16" s="746"/>
+      <c r="D16" s="746"/>
+      <c r="E16" s="746"/>
+      <c r="F16" s="746"/>
+      <c r="G16" s="746"/>
+      <c r="H16" s="746"/>
+      <c r="I16" s="747"/>
       <c r="L16" s="254">
         <f>A11</f>
         <v>0</v>
@@ -25201,56 +24162,56 @@
         <v>0.9</v>
       </c>
       <c r="O16" s="34"/>
-      <c r="P16" s="733"/>
-      <c r="Q16" s="733"/>
+      <c r="P16" s="735"/>
+      <c r="Q16" s="735"/>
       <c r="R16" s="142"/>
     </row>
     <row r="17" spans="1:18" ht="23.25" customHeight="1">
-      <c r="A17" s="743" t="s">
+      <c r="A17" s="745" t="s">
         <v>197</v>
       </c>
-      <c r="B17" s="744"/>
-      <c r="C17" s="744"/>
-      <c r="D17" s="744"/>
-      <c r="E17" s="744"/>
-      <c r="F17" s="744"/>
-      <c r="G17" s="744"/>
-      <c r="H17" s="744"/>
-      <c r="I17" s="745"/>
+      <c r="B17" s="746"/>
+      <c r="C17" s="746"/>
+      <c r="D17" s="746"/>
+      <c r="E17" s="746"/>
+      <c r="F17" s="746"/>
+      <c r="G17" s="746"/>
+      <c r="H17" s="746"/>
+      <c r="I17" s="747"/>
       <c r="L17" s="255"/>
       <c r="M17" s="121"/>
       <c r="N17" s="255"/>
       <c r="O17" s="34"/>
-      <c r="P17" s="734" t="s">
+      <c r="P17" s="736" t="s">
         <v>221</v>
       </c>
-      <c r="Q17" s="734"/>
+      <c r="Q17" s="736"/>
       <c r="R17" s="135">
         <f>L16*R15</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="23.25" customHeight="1">
-      <c r="A18" s="764"/>
-      <c r="B18" s="765"/>
-      <c r="C18" s="765"/>
-      <c r="D18" s="765"/>
-      <c r="E18" s="765"/>
-      <c r="F18" s="765"/>
-      <c r="G18" s="765"/>
-      <c r="H18" s="765"/>
-      <c r="I18" s="766"/>
+      <c r="A18" s="766"/>
+      <c r="B18" s="767"/>
+      <c r="C18" s="767"/>
+      <c r="D18" s="767"/>
+      <c r="E18" s="767"/>
+      <c r="F18" s="767"/>
+      <c r="G18" s="767"/>
+      <c r="H18" s="767"/>
+      <c r="I18" s="768"/>
     </row>
     <row r="19" spans="1:18">
-      <c r="A19" s="764"/>
-      <c r="B19" s="765"/>
-      <c r="C19" s="765"/>
-      <c r="D19" s="765"/>
-      <c r="E19" s="765"/>
-      <c r="F19" s="765"/>
-      <c r="G19" s="765"/>
-      <c r="H19" s="765"/>
-      <c r="I19" s="766"/>
+      <c r="A19" s="766"/>
+      <c r="B19" s="767"/>
+      <c r="C19" s="767"/>
+      <c r="D19" s="767"/>
+      <c r="E19" s="767"/>
+      <c r="F19" s="767"/>
+      <c r="G19" s="767"/>
+      <c r="H19" s="767"/>
+      <c r="I19" s="768"/>
     </row>
     <row r="20" spans="1:18" ht="22.5" customHeight="1">
       <c r="A20" s="119" t="s">
@@ -25314,11 +24275,11 @@
       <c r="I22" s="124"/>
     </row>
     <row r="23" spans="1:18" ht="21.75" customHeight="1">
-      <c r="A23" s="735" t="s">
+      <c r="A23" s="737" t="s">
         <v>209</v>
       </c>
-      <c r="B23" s="736"/>
-      <c r="C23" s="736"/>
+      <c r="B23" s="738"/>
+      <c r="C23" s="738"/>
       <c r="D23" s="131">
         <f>Bilgiler!D25</f>
         <v>0</v>
@@ -25357,15 +24318,15 @@
       <c r="B25" s="73" t="s">
         <v>203</v>
       </c>
-      <c r="C25" s="781">
+      <c r="C25" s="783">
         <v>0.9</v>
       </c>
-      <c r="D25" s="781"/>
-      <c r="E25" s="781"/>
-      <c r="F25" s="781"/>
-      <c r="G25" s="781"/>
-      <c r="H25" s="781"/>
-      <c r="I25" s="782"/>
+      <c r="D25" s="783"/>
+      <c r="E25" s="783"/>
+      <c r="F25" s="783"/>
+      <c r="G25" s="783"/>
+      <c r="H25" s="783"/>
+      <c r="I25" s="784"/>
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="125" t="s">
@@ -25374,16 +24335,16 @@
       <c r="B26" s="73" t="s">
         <v>203</v>
       </c>
-      <c r="C26" s="767">
+      <c r="C26" s="769">
         <f>(N8+(0*(P8/O8)))+(N9*(P9/O9))+(N10*(P10/O10))+(N11*(P11/O11))</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="D26" s="767"/>
-      <c r="E26" s="767"/>
-      <c r="F26" s="767"/>
-      <c r="G26" s="767"/>
-      <c r="H26" s="767"/>
-      <c r="I26" s="768"/>
+      <c r="D26" s="769"/>
+      <c r="E26" s="769"/>
+      <c r="F26" s="769"/>
+      <c r="G26" s="769"/>
+      <c r="H26" s="769"/>
+      <c r="I26" s="770"/>
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="126" t="s">
@@ -25392,16 +24353,16 @@
       <c r="B27" s="73" t="s">
         <v>203</v>
       </c>
-      <c r="C27" s="767">
+      <c r="C27" s="769">
         <f>C25*(C26-1)</f>
         <v>-0.64800000000000002</v>
       </c>
-      <c r="D27" s="767"/>
-      <c r="E27" s="767"/>
-      <c r="F27" s="767"/>
-      <c r="G27" s="767"/>
-      <c r="H27" s="767"/>
-      <c r="I27" s="768"/>
+      <c r="D27" s="769"/>
+      <c r="E27" s="769"/>
+      <c r="F27" s="769"/>
+      <c r="G27" s="769"/>
+      <c r="H27" s="769"/>
+      <c r="I27" s="770"/>
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="125" t="s">
@@ -25434,18 +24395,18 @@
         <f>Bilgiler!D26</f>
         <v>0</v>
       </c>
-      <c r="C30" s="783" t="s">
+      <c r="C30" s="785" t="s">
         <v>223</v>
       </c>
-      <c r="D30" s="783"/>
-      <c r="E30" s="783"/>
-      <c r="F30" s="769">
+      <c r="D30" s="785"/>
+      <c r="E30" s="785"/>
+      <c r="F30" s="771">
         <f>C28</f>
         <v>0</v>
       </c>
-      <c r="G30" s="769"/>
-      <c r="H30" s="769"/>
-      <c r="I30" s="770"/>
+      <c r="G30" s="771"/>
+      <c r="H30" s="771"/>
+      <c r="I30" s="772"/>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="22"/>
@@ -25460,100 +24421,100 @@
       <c r="I33" s="19"/>
     </row>
     <row r="34" spans="1:9" ht="15" customHeight="1">
-      <c r="A34" s="771" t="s">
+      <c r="A34" s="773" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="772"/>
-      <c r="C34" s="772"/>
-      <c r="D34" s="772"/>
-      <c r="E34" s="773"/>
-      <c r="F34" s="777" t="str">
+      <c r="B34" s="774"/>
+      <c r="C34" s="774"/>
+      <c r="D34" s="774"/>
+      <c r="E34" s="775"/>
+      <c r="F34" s="779" t="str">
         <f>Çarşaf!A23</f>
         <v>KONTROL</v>
       </c>
-      <c r="G34" s="772"/>
-      <c r="H34" s="772"/>
-      <c r="I34" s="778"/>
+      <c r="G34" s="774"/>
+      <c r="H34" s="774"/>
+      <c r="I34" s="780"/>
     </row>
     <row r="35" spans="1:9" ht="15" customHeight="1">
-      <c r="A35" s="774"/>
-      <c r="B35" s="775"/>
-      <c r="C35" s="775"/>
-      <c r="D35" s="775"/>
-      <c r="E35" s="776"/>
-      <c r="F35" s="779"/>
-      <c r="G35" s="775"/>
-      <c r="H35" s="775"/>
-      <c r="I35" s="780"/>
+      <c r="A35" s="776"/>
+      <c r="B35" s="777"/>
+      <c r="C35" s="777"/>
+      <c r="D35" s="777"/>
+      <c r="E35" s="778"/>
+      <c r="F35" s="781"/>
+      <c r="G35" s="777"/>
+      <c r="H35" s="777"/>
+      <c r="I35" s="782"/>
     </row>
     <row r="36" spans="1:9" ht="15" customHeight="1">
-      <c r="A36" s="746">
+      <c r="A36" s="748">
         <f>Bilgiler!D3</f>
         <v>0</v>
       </c>
-      <c r="B36" s="747"/>
-      <c r="C36" s="747"/>
-      <c r="D36" s="747"/>
-      <c r="E36" s="748"/>
-      <c r="F36" s="752"/>
-      <c r="G36" s="753"/>
-      <c r="H36" s="753"/>
-      <c r="I36" s="754"/>
+      <c r="B36" s="749"/>
+      <c r="C36" s="749"/>
+      <c r="D36" s="749"/>
+      <c r="E36" s="750"/>
+      <c r="F36" s="754"/>
+      <c r="G36" s="755"/>
+      <c r="H36" s="755"/>
+      <c r="I36" s="756"/>
     </row>
     <row r="37" spans="1:9" ht="15" customHeight="1">
-      <c r="A37" s="746"/>
-      <c r="B37" s="747"/>
-      <c r="C37" s="747"/>
-      <c r="D37" s="747"/>
-      <c r="E37" s="748"/>
-      <c r="F37" s="755"/>
-      <c r="G37" s="756"/>
-      <c r="H37" s="756"/>
-      <c r="I37" s="757"/>
+      <c r="A37" s="748"/>
+      <c r="B37" s="749"/>
+      <c r="C37" s="749"/>
+      <c r="D37" s="749"/>
+      <c r="E37" s="750"/>
+      <c r="F37" s="757"/>
+      <c r="G37" s="758"/>
+      <c r="H37" s="758"/>
+      <c r="I37" s="759"/>
     </row>
     <row r="38" spans="1:9" ht="15" customHeight="1">
-      <c r="A38" s="746"/>
-      <c r="B38" s="747"/>
-      <c r="C38" s="747"/>
-      <c r="D38" s="747"/>
-      <c r="E38" s="748"/>
-      <c r="F38" s="755"/>
-      <c r="G38" s="756"/>
-      <c r="H38" s="756"/>
-      <c r="I38" s="757"/>
+      <c r="A38" s="748"/>
+      <c r="B38" s="749"/>
+      <c r="C38" s="749"/>
+      <c r="D38" s="749"/>
+      <c r="E38" s="750"/>
+      <c r="F38" s="757"/>
+      <c r="G38" s="758"/>
+      <c r="H38" s="758"/>
+      <c r="I38" s="759"/>
     </row>
     <row r="39" spans="1:9" ht="15" customHeight="1">
-      <c r="A39" s="746"/>
-      <c r="B39" s="747"/>
-      <c r="C39" s="747"/>
-      <c r="D39" s="747"/>
-      <c r="E39" s="748"/>
-      <c r="F39" s="758"/>
-      <c r="G39" s="759"/>
-      <c r="H39" s="759"/>
-      <c r="I39" s="760"/>
+      <c r="A39" s="748"/>
+      <c r="B39" s="749"/>
+      <c r="C39" s="749"/>
+      <c r="D39" s="749"/>
+      <c r="E39" s="750"/>
+      <c r="F39" s="760"/>
+      <c r="G39" s="761"/>
+      <c r="H39" s="761"/>
+      <c r="I39" s="762"/>
     </row>
     <row r="40" spans="1:9" ht="15" customHeight="1">
-      <c r="A40" s="746"/>
-      <c r="B40" s="747"/>
-      <c r="C40" s="747"/>
-      <c r="D40" s="747"/>
-      <c r="E40" s="748"/>
-      <c r="F40" s="758"/>
-      <c r="G40" s="759"/>
-      <c r="H40" s="759"/>
-      <c r="I40" s="760"/>
+      <c r="A40" s="748"/>
+      <c r="B40" s="749"/>
+      <c r="C40" s="749"/>
+      <c r="D40" s="749"/>
+      <c r="E40" s="750"/>
+      <c r="F40" s="760"/>
+      <c r="G40" s="761"/>
+      <c r="H40" s="761"/>
+      <c r="I40" s="762"/>
     </row>
     <row r="41" spans="1:9" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A41" s="749"/>
-      <c r="B41" s="750"/>
-      <c r="C41" s="750"/>
-      <c r="D41" s="750"/>
-      <c r="E41" s="751"/>
-      <c r="F41" s="761"/>
-      <c r="G41" s="762"/>
-      <c r="H41" s="762"/>
-      <c r="I41" s="763"/>
+      <c r="A41" s="751"/>
+      <c r="B41" s="752"/>
+      <c r="C41" s="752"/>
+      <c r="D41" s="752"/>
+      <c r="E41" s="753"/>
+      <c r="F41" s="763"/>
+      <c r="G41" s="764"/>
+      <c r="H41" s="764"/>
+      <c r="I41" s="765"/>
     </row>
     <row r="42" spans="1:9" ht="15.75" thickTop="1"/>
   </sheetData>
